--- a/projections/kicker_2026_combined.xlsx
+++ b/projections/kicker_2026_combined.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,6 +518,16 @@
           <t>diff_vs_espn</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>vlahakis</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>williams</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -584,6 +594,8 @@
       <c r="T2" t="n">
         <v>-20.46</v>
       </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -650,6 +662,8 @@
       <c r="T3" t="n">
         <v>-14.02</v>
       </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -716,6 +730,8 @@
       <c r="T4" t="n">
         <v>-11.11</v>
       </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -782,6 +798,8 @@
       <c r="T5" t="n">
         <v>-15.71</v>
       </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -848,6 +866,8 @@
       <c r="T6" t="n">
         <v>-2.62</v>
       </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -914,6 +934,8 @@
       <c r="T7" t="n">
         <v>13.24</v>
       </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -980,6 +1002,8 @@
       <c r="T8" t="n">
         <v>-17.49</v>
       </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1046,6 +1070,8 @@
       <c r="T9" t="n">
         <v>4.2</v>
       </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1112,6 +1138,8 @@
       <c r="T10" t="n">
         <v>-18.25</v>
       </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1178,6 +1206,8 @@
       <c r="T11" t="n">
         <v>-6.69</v>
       </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1244,6 +1274,8 @@
       <c r="T12" t="n">
         <v>-7.64</v>
       </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1310,6 +1342,8 @@
       <c r="T13" t="n">
         <v>2.37</v>
       </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1376,6 +1410,8 @@
       <c r="T14" t="n">
         <v>3.33</v>
       </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1442,6 +1478,8 @@
       <c r="T15" t="n">
         <v>-5.76</v>
       </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1508,6 +1546,8 @@
       <c r="T16" t="n">
         <v>0.75</v>
       </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1574,6 +1614,8 @@
       <c r="T17" t="n">
         <v>-4.91</v>
       </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1640,6 +1682,8 @@
       <c r="T18" t="n">
         <v>-4.63</v>
       </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1706,6 +1750,8 @@
       <c r="T19" t="n">
         <v>-11.07</v>
       </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1772,6 +1818,8 @@
       <c r="T20" t="n">
         <v>-9</v>
       </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1838,6 +1886,8 @@
       <c r="T21" t="n">
         <v>-6.89</v>
       </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1904,6 +1954,8 @@
       <c r="T22" t="n">
         <v>1.69</v>
       </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1970,6 +2022,8 @@
       <c r="T23" t="n">
         <v>-7.9</v>
       </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2036,6 +2090,8 @@
       <c r="T24" t="n">
         <v>4.7</v>
       </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2102,6 +2158,8 @@
       <c r="T25" t="n">
         <v>-11</v>
       </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2168,6 +2226,8 @@
       <c r="T26" t="n">
         <v>1.15</v>
       </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2234,6 +2294,8 @@
       <c r="T27" t="n">
         <v>-9.69</v>
       </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2300,6 +2362,8 @@
       <c r="T28" t="n">
         <v>1.18</v>
       </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2366,6 +2430,8 @@
       <c r="T29" t="n">
         <v>-3.06</v>
       </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2432,6 +2498,8 @@
       <c r="T30" t="n">
         <v>-1.11</v>
       </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2498,6 +2566,8 @@
       <c r="T31" t="n">
         <v>-0.7</v>
       </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2564,6 +2634,8 @@
       <c r="T32" t="n">
         <v>-2.06</v>
       </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2630,6 +2702,8 @@
       <c r="T33" t="n">
         <v>-3.68</v>
       </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2642,7 +2716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U545"/>
+  <dimension ref="A1:W545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2751,6 +2825,16 @@
           <t>total_projected_fp</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>fantasy_pts_floor</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>fantasy_pts_ceiling</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2822,6 +2906,12 @@
       <c r="U2" t="n">
         <v>6.744</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16.055</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2893,6 +2983,12 @@
       <c r="U3" t="n">
         <v>7.284</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>16.958</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2964,6 +3060,12 @@
       <c r="U4" t="n">
         <v>7.371</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>17.107</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3035,6 +3137,12 @@
       <c r="U5" t="n">
         <v>7.176</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>16.78</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3106,6 +3214,12 @@
       <c r="U6" t="n">
         <v>7.546</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>17.392</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3177,6 +3291,12 @@
       <c r="U7" t="n">
         <v>7.264</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>16.922</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3248,6 +3368,12 @@
       <c r="U8" t="n">
         <v>7.281</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>16.953</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3319,6 +3445,12 @@
       <c r="U9" t="n">
         <v>7.061</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>16.589</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3390,6 +3522,12 @@
       <c r="U10" t="n">
         <v>6.706</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>15.99</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3461,6 +3599,12 @@
       <c r="U11" t="n">
         <v>6.964</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>16.414</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3532,6 +3676,12 @@
       <c r="U12" t="n">
         <v>7.262</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>16.926</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3603,6 +3753,12 @@
       <c r="U13" t="n">
         <v>7.52</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>17.355</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3674,6 +3830,12 @@
       <c r="U14" t="n">
         <v>7.266</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>16.932</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3745,6 +3907,12 @@
       <c r="U15" t="n">
         <v>7.117</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>16.677</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3816,6 +3984,12 @@
       <c r="U16" t="n">
         <v>7.12</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>16.682</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3887,6 +4061,12 @@
       <c r="U17" t="n">
         <v>7.39</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>17.138</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3958,6 +4138,12 @@
       <c r="U18" t="n">
         <v>7.484</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17.289</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4029,6 +4215,12 @@
       <c r="U19" t="n">
         <v>7.938</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18.049</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4100,6 +4292,12 @@
       <c r="U20" t="n">
         <v>8.201000000000001</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>18.483</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4171,6 +4369,12 @@
       <c r="U21" t="n">
         <v>7.789</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>17.809</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4242,6 +4446,12 @@
       <c r="U22" t="n">
         <v>8.228999999999999</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>18.528</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4313,6 +4523,12 @@
       <c r="U23" t="n">
         <v>8.654999999999999</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>19.195</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4384,6 +4600,12 @@
       <c r="U24" t="n">
         <v>9.042999999999999</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>19.776</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4455,6 +4677,12 @@
       <c r="U25" t="n">
         <v>8.455</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>18.885</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4526,6 +4754,12 @@
       <c r="U26" t="n">
         <v>8.523</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>18.991</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4597,6 +4831,12 @@
       <c r="U27" t="n">
         <v>8.685</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>19.241</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4668,6 +4908,12 @@
       <c r="U28" t="n">
         <v>8.603999999999999</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>19.124</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4739,6 +4985,12 @@
       <c r="U29" t="n">
         <v>7.774</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>17.784</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4810,6 +5062,12 @@
       <c r="U30" t="n">
         <v>8.384</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>18.774</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4881,6 +5139,12 @@
       <c r="U31" t="n">
         <v>8.086</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>18.29</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4952,6 +5216,12 @@
       <c r="U32" t="n">
         <v>8.074999999999999</v>
       </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>18.281</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5023,6 +5293,12 @@
       <c r="U33" t="n">
         <v>9.105</v>
       </c>
+      <c r="V33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>19.866</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5094,6 +5370,12 @@
       <c r="U34" t="n">
         <v>7.977</v>
       </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>18.115</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5165,6 +5447,12 @@
       <c r="U35" t="n">
         <v>8.733000000000001</v>
       </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>19.317</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5236,6 +5524,12 @@
       <c r="U36" t="n">
         <v>8.007</v>
       </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>18.149</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5307,6 +5601,12 @@
       <c r="U37" t="n">
         <v>7.566</v>
       </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>17.426</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5378,6 +5678,12 @@
       <c r="U38" t="n">
         <v>7.997</v>
       </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>18.135</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5449,6 +5755,12 @@
       <c r="U39" t="n">
         <v>7.789</v>
       </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>17.798</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5520,6 +5832,12 @@
       <c r="U40" t="n">
         <v>7.708</v>
       </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>17.663</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5591,6 +5909,12 @@
       <c r="U41" t="n">
         <v>7.532</v>
       </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>17.375</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5662,6 +5986,12 @@
       <c r="U42" t="n">
         <v>6.87</v>
       </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>16.271</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5733,6 +6063,12 @@
       <c r="U43" t="n">
         <v>6.847</v>
       </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>16.232</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5804,6 +6140,12 @@
       <c r="U44" t="n">
         <v>7.833</v>
       </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>17.869</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5875,6 +6217,12 @@
       <c r="U45" t="n">
         <v>7.792</v>
       </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>17.798</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5946,6 +6294,12 @@
       <c r="U46" t="n">
         <v>7.646</v>
       </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>17.558</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6017,6 +6371,12 @@
       <c r="U47" t="n">
         <v>8.096</v>
       </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>18.285</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6088,6 +6448,12 @@
       <c r="U48" t="n">
         <v>6.837</v>
       </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>16.215</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6159,6 +6525,12 @@
       <c r="U49" t="n">
         <v>7.808</v>
       </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>17.814</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6230,6 +6602,12 @@
       <c r="U50" t="n">
         <v>7.718</v>
       </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>17.673</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6301,6 +6679,12 @@
       <c r="U51" t="n">
         <v>8.029</v>
       </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>18.176</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6372,6 +6756,12 @@
       <c r="U52" t="n">
         <v>7.494</v>
       </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>17.314</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6443,6 +6833,12 @@
       <c r="U53" t="n">
         <v>7.788</v>
       </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>17.703</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6514,6 +6910,12 @@
       <c r="U54" t="n">
         <v>7.705</v>
       </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>17.572</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6585,6 +6987,12 @@
       <c r="U55" t="n">
         <v>7.582</v>
       </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>17.362</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6656,6 +7064,12 @@
       <c r="U56" t="n">
         <v>8.093</v>
       </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>18.204</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6727,6 +7141,12 @@
       <c r="U57" t="n">
         <v>7.957</v>
       </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>17.982</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6798,6 +7218,12 @@
       <c r="U58" t="n">
         <v>8.196</v>
       </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>18.372</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6869,6 +7295,12 @@
       <c r="U59" t="n">
         <v>7.765</v>
       </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>17.67</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6940,6 +7372,12 @@
       <c r="U60" t="n">
         <v>7.65</v>
       </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>17.481</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7011,6 +7449,12 @@
       <c r="U61" t="n">
         <v>8.26</v>
       </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>18.473</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7082,6 +7526,12 @@
       <c r="U62" t="n">
         <v>8.188000000000001</v>
       </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>18.358</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7153,6 +7603,12 @@
       <c r="U63" t="n">
         <v>7.413</v>
       </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>17.092</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7224,6 +7680,12 @@
       <c r="U64" t="n">
         <v>8.255000000000001</v>
       </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>18.466</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7295,6 +7757,12 @@
       <c r="U65" t="n">
         <v>7.56</v>
       </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>17.334</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7366,6 +7834,12 @@
       <c r="U66" t="n">
         <v>8.109999999999999</v>
       </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>18.233</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7437,6 +7911,12 @@
       <c r="U67" t="n">
         <v>8.19</v>
       </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>18.361</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7508,6 +7988,12 @@
       <c r="U68" t="n">
         <v>7.821</v>
       </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>17.757</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7579,6 +8065,12 @@
       <c r="U69" t="n">
         <v>7.946</v>
       </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>17.966</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7650,6 +8142,12 @@
       <c r="U70" t="n">
         <v>8.978999999999999</v>
       </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>20.057</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7721,6 +8219,12 @@
       <c r="U71" t="n">
         <v>8.978999999999999</v>
       </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>20.046</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7792,6 +8296,12 @@
       <c r="U72" t="n">
         <v>8.833</v>
       </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>19.815</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7863,6 +8373,12 @@
       <c r="U73" t="n">
         <v>8.692</v>
       </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>19.577</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7934,6 +8450,12 @@
       <c r="U74" t="n">
         <v>9.353</v>
       </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>20.644</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8005,6 +8527,12 @@
       <c r="U75" t="n">
         <v>8.742000000000001</v>
       </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>19.672</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8076,6 +8604,12 @@
       <c r="U76" t="n">
         <v>8.592000000000001</v>
       </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>19.424</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8147,6 +8681,12 @@
       <c r="U77" t="n">
         <v>8.856</v>
       </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>19.846</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8218,6 +8758,12 @@
       <c r="U78" t="n">
         <v>8.759</v>
       </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>19.699</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8289,6 +8835,12 @@
       <c r="U79" t="n">
         <v>9.098000000000001</v>
       </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>20.24</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8360,6 +8912,12 @@
       <c r="U80" t="n">
         <v>8.993</v>
       </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>20.073</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8431,6 +8989,12 @@
       <c r="U81" t="n">
         <v>8.975</v>
       </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>20.03</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8502,6 +9066,12 @@
       <c r="U82" t="n">
         <v>8.542999999999999</v>
       </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>19.337</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8573,6 +9143,12 @@
       <c r="U83" t="n">
         <v>8.880000000000001</v>
       </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>19.888</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8644,6 +9220,12 @@
       <c r="U84" t="n">
         <v>8.779</v>
       </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
+        <v>19.714</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8715,6 +9297,12 @@
       <c r="U85" t="n">
         <v>9.227</v>
       </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>20.442</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8786,6 +9374,12 @@
       <c r="U86" t="n">
         <v>8.826000000000001</v>
       </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>19.806</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8857,6 +9451,12 @@
       <c r="U87" t="n">
         <v>7.986</v>
       </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>18.053</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8928,6 +9528,12 @@
       <c r="U88" t="n">
         <v>7.832</v>
       </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>17.798</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8999,6 +9605,12 @@
       <c r="U89" t="n">
         <v>7.808</v>
       </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>17.761</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9070,6 +9682,12 @@
       <c r="U90" t="n">
         <v>8.275</v>
       </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>18.504</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9141,6 +9759,12 @@
       <c r="U91" t="n">
         <v>7.945</v>
       </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>17.984</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9212,6 +9836,12 @@
       <c r="U92" t="n">
         <v>8.045</v>
       </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>18.149</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9283,6 +9913,12 @@
       <c r="U93" t="n">
         <v>8.096</v>
       </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>18.221</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9354,6 +9990,12 @@
       <c r="U94" t="n">
         <v>7.406</v>
       </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>17.108</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9425,6 +10067,12 @@
       <c r="U95" t="n">
         <v>8.292</v>
       </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>18.532</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9496,6 +10144,12 @@
       <c r="U96" t="n">
         <v>7.987</v>
       </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>18.05</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9567,6 +10221,12 @@
       <c r="U97" t="n">
         <v>8.06</v>
       </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>18.171</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9638,6 +10298,12 @@
       <c r="U98" t="n">
         <v>7.82</v>
       </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>17.779</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9709,6 +10375,12 @@
       <c r="U99" t="n">
         <v>7.902</v>
       </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>17.915</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9780,6 +10452,12 @@
       <c r="U100" t="n">
         <v>7.849</v>
       </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>17.827</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9851,6 +10529,12 @@
       <c r="U101" t="n">
         <v>8.294</v>
       </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>18.536</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9922,6 +10606,12 @@
       <c r="U102" t="n">
         <v>8.382</v>
       </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>18.678</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9993,6 +10683,12 @@
       <c r="U103" t="n">
         <v>7.432</v>
       </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>17.15</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10064,6 +10760,12 @@
       <c r="U104" t="n">
         <v>8.224</v>
       </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>18.542</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10135,6 +10837,12 @@
       <c r="U105" t="n">
         <v>7.673</v>
       </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>17.65</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10206,6 +10914,12 @@
       <c r="U106" t="n">
         <v>8.423999999999999</v>
       </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>18.868</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10277,6 +10991,12 @@
       <c r="U107" t="n">
         <v>8.185</v>
       </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>18.487</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10348,6 +11068,12 @@
       <c r="U108" t="n">
         <v>8.18</v>
       </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>18.479</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10419,6 +11145,12 @@
       <c r="U109" t="n">
         <v>8.007999999999999</v>
       </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>18.206</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10490,6 +11222,12 @@
       <c r="U110" t="n">
         <v>8.552</v>
       </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>19.066</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10561,6 +11299,12 @@
       <c r="U111" t="n">
         <v>7.838</v>
       </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>17.928</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10632,6 +11376,12 @@
       <c r="U112" t="n">
         <v>8.108000000000001</v>
       </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>18.363</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10703,6 +11453,12 @@
       <c r="U113" t="n">
         <v>8.096</v>
       </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>18.342</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10774,6 +11530,12 @@
       <c r="U114" t="n">
         <v>8.369</v>
       </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>18.781</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10845,6 +11607,12 @@
       <c r="U115" t="n">
         <v>8.146000000000001</v>
       </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>18.427</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10916,6 +11684,12 @@
       <c r="U116" t="n">
         <v>8.356</v>
       </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="n">
+        <v>18.76</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10987,6 +11761,12 @@
       <c r="U117" t="n">
         <v>7.52</v>
       </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" t="n">
+        <v>17.404</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11058,6 +11838,12 @@
       <c r="U118" t="n">
         <v>8.847</v>
       </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>19.516</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11129,6 +11915,12 @@
       <c r="U119" t="n">
         <v>8.467000000000001</v>
       </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>18.933</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11200,6 +11992,12 @@
       <c r="U120" t="n">
         <v>8.077</v>
       </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>18.313</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11271,6 +12069,12 @@
       <c r="U121" t="n">
         <v>8.907999999999999</v>
       </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>20.028</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11342,6 +12146,12 @@
       <c r="U122" t="n">
         <v>9.031000000000001</v>
       </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>20.229</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11413,6 +12223,12 @@
       <c r="U123" t="n">
         <v>8.762</v>
       </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>19.792</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11484,6 +12300,12 @@
       <c r="U124" t="n">
         <v>7.855</v>
       </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>18.299</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11555,6 +12377,12 @@
       <c r="U125" t="n">
         <v>8.499000000000001</v>
       </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>19.361</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11626,6 +12454,12 @@
       <c r="U126" t="n">
         <v>8.432</v>
       </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>19.251</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11697,6 +12531,12 @@
       <c r="U127" t="n">
         <v>8.737</v>
       </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" t="n">
+        <v>19.751</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11768,6 +12608,12 @@
       <c r="U128" t="n">
         <v>8.289</v>
       </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>19.018</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11839,6 +12685,12 @@
       <c r="U129" t="n">
         <v>8.319000000000001</v>
       </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>19.066</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11910,6 +12762,12 @@
       <c r="U130" t="n">
         <v>8.962999999999999</v>
       </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>20.12</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11981,6 +12839,12 @@
       <c r="U131" t="n">
         <v>8.762</v>
       </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>19.792</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12052,6 +12916,12 @@
       <c r="U132" t="n">
         <v>9.085000000000001</v>
       </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>20.315</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12123,6 +12993,12 @@
       <c r="U133" t="n">
         <v>9.002000000000001</v>
       </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>20.181</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12194,6 +13070,12 @@
       <c r="U134" t="n">
         <v>9.191000000000001</v>
       </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>20.487</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12265,6 +13147,12 @@
       <c r="U135" t="n">
         <v>8.987</v>
       </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>20.156</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12336,6 +13224,12 @@
       <c r="U136" t="n">
         <v>8.605</v>
       </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" t="n">
+        <v>19.536</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12407,6 +13301,12 @@
       <c r="U137" t="n">
         <v>8.263</v>
       </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>18.975</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12478,6 +13378,12 @@
       <c r="U138" t="n">
         <v>6.572</v>
       </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>15.397</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12549,6 +13455,12 @@
       <c r="U139" t="n">
         <v>6.839</v>
       </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>15.843</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12620,6 +13532,12 @@
       <c r="U140" t="n">
         <v>7.521</v>
       </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>16.971</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12691,6 +13609,12 @@
       <c r="U141" t="n">
         <v>7.361</v>
       </c>
+      <c r="V141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>16.71</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12762,6 +13686,12 @@
       <c r="U142" t="n">
         <v>7.416</v>
       </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>16.799</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12833,6 +13763,12 @@
       <c r="U143" t="n">
         <v>7.146</v>
       </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>16.355</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12904,6 +13840,12 @@
       <c r="U144" t="n">
         <v>6.827</v>
       </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>15.824</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12975,6 +13917,12 @@
       <c r="U145" t="n">
         <v>7.546</v>
       </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>17.012</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13046,6 +13994,12 @@
       <c r="U146" t="n">
         <v>6.609</v>
       </c>
+      <c r="V146" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" t="n">
+        <v>15.463</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13117,6 +14071,12 @@
       <c r="U147" t="n">
         <v>7.198</v>
       </c>
+      <c r="V147" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" t="n">
+        <v>16.441</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13188,6 +14148,12 @@
       <c r="U148" t="n">
         <v>6.958</v>
       </c>
+      <c r="V148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" t="n">
+        <v>16.041</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13259,6 +14225,12 @@
       <c r="U149" t="n">
         <v>7.271</v>
       </c>
+      <c r="V149" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" t="n">
+        <v>16.561</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13330,6 +14302,12 @@
       <c r="U150" t="n">
         <v>6.861</v>
       </c>
+      <c r="V150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" t="n">
+        <v>15.878</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13401,6 +14379,12 @@
       <c r="U151" t="n">
         <v>7.294</v>
       </c>
+      <c r="V151" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" t="n">
+        <v>16.598</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13472,6 +14456,12 @@
       <c r="U152" t="n">
         <v>6.693</v>
       </c>
+      <c r="V152" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" t="n">
+        <v>15.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13543,6 +14533,12 @@
       <c r="U153" t="n">
         <v>7.437</v>
       </c>
+      <c r="V153" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" t="n">
+        <v>16.834</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13614,6 +14610,12 @@
       <c r="U154" t="n">
         <v>7.489</v>
       </c>
+      <c r="V154" t="n">
+        <v>0</v>
+      </c>
+      <c r="W154" t="n">
+        <v>16.921</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13685,6 +14687,12 @@
       <c r="U155" t="n">
         <v>8.177</v>
       </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" t="n">
+        <v>18.431</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13756,6 +14764,12 @@
       <c r="U156" t="n">
         <v>7.708</v>
       </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" t="n">
+        <v>17.661</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13827,6 +14841,12 @@
       <c r="U157" t="n">
         <v>8.372999999999999</v>
       </c>
+      <c r="V157" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" t="n">
+        <v>18.752</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13898,6 +14918,12 @@
       <c r="U158" t="n">
         <v>8.173999999999999</v>
       </c>
+      <c r="V158" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" t="n">
+        <v>18.426</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13969,6 +14995,12 @@
       <c r="U159" t="n">
         <v>8.012</v>
       </c>
+      <c r="V159" t="n">
+        <v>0</v>
+      </c>
+      <c r="W159" t="n">
+        <v>18.162</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14040,6 +15072,12 @@
       <c r="U160" t="n">
         <v>8.153</v>
       </c>
+      <c r="V160" t="n">
+        <v>0</v>
+      </c>
+      <c r="W160" t="n">
+        <v>18.393</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14111,6 +15149,12 @@
       <c r="U161" t="n">
         <v>8.130000000000001</v>
       </c>
+      <c r="V161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
+        <v>18.356</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14182,6 +15226,12 @@
       <c r="U162" t="n">
         <v>7.894</v>
       </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>17.969</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14253,6 +15303,12 @@
       <c r="U163" t="n">
         <v>8.323</v>
       </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>18.67</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14324,6 +15380,12 @@
       <c r="U164" t="n">
         <v>8.058999999999999</v>
       </c>
+      <c r="V164" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" t="n">
+        <v>18.238</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14395,6 +15457,12 @@
       <c r="U165" t="n">
         <v>8.222</v>
       </c>
+      <c r="V165" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" t="n">
+        <v>18.503</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14466,6 +15534,12 @@
       <c r="U166" t="n">
         <v>8.262</v>
       </c>
+      <c r="V166" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" t="n">
+        <v>18.57</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14537,6 +15611,12 @@
       <c r="U167" t="n">
         <v>8.212999999999999</v>
       </c>
+      <c r="V167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" t="n">
+        <v>18.489</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14608,6 +15688,12 @@
       <c r="U168" t="n">
         <v>8.179</v>
       </c>
+      <c r="V168" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" t="n">
+        <v>18.434</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14679,6 +15765,12 @@
       <c r="U169" t="n">
         <v>8.148</v>
       </c>
+      <c r="V169" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" t="n">
+        <v>18.386</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14750,6 +15842,12 @@
       <c r="U170" t="n">
         <v>7.971</v>
       </c>
+      <c r="V170" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" t="n">
+        <v>18.094</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14821,6 +15919,12 @@
       <c r="U171" t="n">
         <v>8.301</v>
       </c>
+      <c r="V171" t="n">
+        <v>0</v>
+      </c>
+      <c r="W171" t="n">
+        <v>18.636</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -14892,6 +15996,12 @@
       <c r="U172" t="n">
         <v>7.984</v>
       </c>
+      <c r="V172" t="n">
+        <v>0</v>
+      </c>
+      <c r="W172" t="n">
+        <v>18.087</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14963,6 +16073,12 @@
       <c r="U173" t="n">
         <v>8.025</v>
       </c>
+      <c r="V173" t="n">
+        <v>0</v>
+      </c>
+      <c r="W173" t="n">
+        <v>18.144</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -15034,6 +16150,12 @@
       <c r="U174" t="n">
         <v>7.877</v>
       </c>
+      <c r="V174" t="n">
+        <v>0</v>
+      </c>
+      <c r="W174" t="n">
+        <v>17.909</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -15105,6 +16227,12 @@
       <c r="U175" t="n">
         <v>8.212999999999999</v>
       </c>
+      <c r="V175" t="n">
+        <v>0</v>
+      </c>
+      <c r="W175" t="n">
+        <v>18.456</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -15176,6 +16304,12 @@
       <c r="U176" t="n">
         <v>8.099</v>
       </c>
+      <c r="V176" t="n">
+        <v>0</v>
+      </c>
+      <c r="W176" t="n">
+        <v>18.273</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -15247,6 +16381,12 @@
       <c r="U177" t="n">
         <v>8.125999999999999</v>
       </c>
+      <c r="V177" t="n">
+        <v>0</v>
+      </c>
+      <c r="W177" t="n">
+        <v>18.314</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -15318,6 +16458,12 @@
       <c r="U178" t="n">
         <v>8.050000000000001</v>
       </c>
+      <c r="V178" t="n">
+        <v>0</v>
+      </c>
+      <c r="W178" t="n">
+        <v>18.192</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15389,6 +16535,12 @@
       <c r="U179" t="n">
         <v>8.128</v>
       </c>
+      <c r="V179" t="n">
+        <v>0</v>
+      </c>
+      <c r="W179" t="n">
+        <v>18.319</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15460,6 +16612,12 @@
       <c r="U180" t="n">
         <v>7.971</v>
       </c>
+      <c r="V180" t="n">
+        <v>0</v>
+      </c>
+      <c r="W180" t="n">
+        <v>18.062</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -15531,6 +16689,12 @@
       <c r="U181" t="n">
         <v>7.985</v>
       </c>
+      <c r="V181" t="n">
+        <v>0</v>
+      </c>
+      <c r="W181" t="n">
+        <v>18.085</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15602,6 +16766,12 @@
       <c r="U182" t="n">
         <v>8.227</v>
       </c>
+      <c r="V182" t="n">
+        <v>0</v>
+      </c>
+      <c r="W182" t="n">
+        <v>18.478</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15673,6 +16843,12 @@
       <c r="U183" t="n">
         <v>7.748</v>
       </c>
+      <c r="V183" t="n">
+        <v>0</v>
+      </c>
+      <c r="W183" t="n">
+        <v>17.7</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -15744,6 +16920,12 @@
       <c r="U184" t="n">
         <v>7.566</v>
       </c>
+      <c r="V184" t="n">
+        <v>0</v>
+      </c>
+      <c r="W184" t="n">
+        <v>17.399</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -15815,6 +16997,12 @@
       <c r="U185" t="n">
         <v>7.806</v>
       </c>
+      <c r="V185" t="n">
+        <v>0</v>
+      </c>
+      <c r="W185" t="n">
+        <v>17.794</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -15886,6 +17074,12 @@
       <c r="U186" t="n">
         <v>7.977</v>
       </c>
+      <c r="V186" t="n">
+        <v>0</v>
+      </c>
+      <c r="W186" t="n">
+        <v>18.074</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -15957,6 +17151,12 @@
       <c r="U187" t="n">
         <v>8.159000000000001</v>
       </c>
+      <c r="V187" t="n">
+        <v>0</v>
+      </c>
+      <c r="W187" t="n">
+        <v>18.367</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -16028,6 +17228,12 @@
       <c r="U188" t="n">
         <v>7.373</v>
       </c>
+      <c r="V188" t="n">
+        <v>0</v>
+      </c>
+      <c r="W188" t="n">
+        <v>17.082</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -16099,6 +17305,12 @@
       <c r="U189" t="n">
         <v>8.327</v>
       </c>
+      <c r="V189" t="n">
+        <v>0</v>
+      </c>
+      <c r="W189" t="n">
+        <v>18.839</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -16170,6 +17382,12 @@
       <c r="U190" t="n">
         <v>8.269</v>
       </c>
+      <c r="V190" t="n">
+        <v>0</v>
+      </c>
+      <c r="W190" t="n">
+        <v>18.735</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -16241,6 +17459,12 @@
       <c r="U191" t="n">
         <v>8.356</v>
       </c>
+      <c r="V191" t="n">
+        <v>0</v>
+      </c>
+      <c r="W191" t="n">
+        <v>18.884</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -16312,6 +17536,12 @@
       <c r="U192" t="n">
         <v>8.000999999999999</v>
       </c>
+      <c r="V192" t="n">
+        <v>0</v>
+      </c>
+      <c r="W192" t="n">
+        <v>18.29</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -16383,6 +17613,12 @@
       <c r="U193" t="n">
         <v>8.49</v>
       </c>
+      <c r="V193" t="n">
+        <v>0</v>
+      </c>
+      <c r="W193" t="n">
+        <v>19.096</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -16454,6 +17690,12 @@
       <c r="U194" t="n">
         <v>8.183</v>
       </c>
+      <c r="V194" t="n">
+        <v>0</v>
+      </c>
+      <c r="W194" t="n">
+        <v>18.606</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -16525,6 +17767,12 @@
       <c r="U195" t="n">
         <v>7.762</v>
       </c>
+      <c r="V195" t="n">
+        <v>0</v>
+      </c>
+      <c r="W195" t="n">
+        <v>17.911</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -16596,6 +17844,12 @@
       <c r="U196" t="n">
         <v>8.202999999999999</v>
       </c>
+      <c r="V196" t="n">
+        <v>0</v>
+      </c>
+      <c r="W196" t="n">
+        <v>18.626</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -16667,6 +17921,12 @@
       <c r="U197" t="n">
         <v>8.17</v>
       </c>
+      <c r="V197" t="n">
+        <v>0</v>
+      </c>
+      <c r="W197" t="n">
+        <v>18.584</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -16738,6 +17998,12 @@
       <c r="U198" t="n">
         <v>7.638</v>
       </c>
+      <c r="V198" t="n">
+        <v>0</v>
+      </c>
+      <c r="W198" t="n">
+        <v>17.709</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -16809,6 +18075,12 @@
       <c r="U199" t="n">
         <v>7.822</v>
       </c>
+      <c r="V199" t="n">
+        <v>0</v>
+      </c>
+      <c r="W199" t="n">
+        <v>18.014</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -16880,6 +18152,12 @@
       <c r="U200" t="n">
         <v>7.996</v>
       </c>
+      <c r="V200" t="n">
+        <v>0</v>
+      </c>
+      <c r="W200" t="n">
+        <v>18.301</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -16951,6 +18229,12 @@
       <c r="U201" t="n">
         <v>7.706</v>
       </c>
+      <c r="V201" t="n">
+        <v>0</v>
+      </c>
+      <c r="W201" t="n">
+        <v>17.818</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -17022,6 +18306,12 @@
       <c r="U202" t="n">
         <v>8.108000000000001</v>
       </c>
+      <c r="V202" t="n">
+        <v>0</v>
+      </c>
+      <c r="W202" t="n">
+        <v>18.483</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -17093,6 +18383,12 @@
       <c r="U203" t="n">
         <v>8.458</v>
       </c>
+      <c r="V203" t="n">
+        <v>0</v>
+      </c>
+      <c r="W203" t="n">
+        <v>19.045</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -17164,6 +18460,12 @@
       <c r="U204" t="n">
         <v>8.183</v>
       </c>
+      <c r="V204" t="n">
+        <v>0</v>
+      </c>
+      <c r="W204" t="n">
+        <v>18.604</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -17235,6 +18537,12 @@
       <c r="U205" t="n">
         <v>7.977</v>
       </c>
+      <c r="V205" t="n">
+        <v>0</v>
+      </c>
+      <c r="W205" t="n">
+        <v>18.269</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -17306,6 +18614,12 @@
       <c r="U206" t="n">
         <v>8.515000000000001</v>
       </c>
+      <c r="V206" t="n">
+        <v>0</v>
+      </c>
+      <c r="W206" t="n">
+        <v>18.979</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -17377,6 +18691,12 @@
       <c r="U207" t="n">
         <v>8.497999999999999</v>
       </c>
+      <c r="V207" t="n">
+        <v>0</v>
+      </c>
+      <c r="W207" t="n">
+        <v>18.929</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -17448,6 +18768,12 @@
       <c r="U208" t="n">
         <v>8.446</v>
       </c>
+      <c r="V208" t="n">
+        <v>0</v>
+      </c>
+      <c r="W208" t="n">
+        <v>18.835</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -17519,6 +18845,12 @@
       <c r="U209" t="n">
         <v>8.302</v>
       </c>
+      <c r="V209" t="n">
+        <v>0</v>
+      </c>
+      <c r="W209" t="n">
+        <v>18.631</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -17590,6 +18922,12 @@
       <c r="U210" t="n">
         <v>8.595000000000001</v>
       </c>
+      <c r="V210" t="n">
+        <v>0</v>
+      </c>
+      <c r="W210" t="n">
+        <v>19.069</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -17661,6 +18999,12 @@
       <c r="U211" t="n">
         <v>8.566000000000001</v>
       </c>
+      <c r="V211" t="n">
+        <v>0</v>
+      </c>
+      <c r="W211" t="n">
+        <v>19.015</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -17732,6 +19076,12 @@
       <c r="U212" t="n">
         <v>8.616</v>
       </c>
+      <c r="V212" t="n">
+        <v>0</v>
+      </c>
+      <c r="W212" t="n">
+        <v>19.144</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -17803,6 +19153,12 @@
       <c r="U213" t="n">
         <v>8.446999999999999</v>
       </c>
+      <c r="V213" t="n">
+        <v>0</v>
+      </c>
+      <c r="W213" t="n">
+        <v>18.856</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -17874,6 +19230,12 @@
       <c r="U214" t="n">
         <v>8.353999999999999</v>
       </c>
+      <c r="V214" t="n">
+        <v>0</v>
+      </c>
+      <c r="W214" t="n">
+        <v>18.69</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -17945,6 +19307,12 @@
       <c r="U215" t="n">
         <v>8.608000000000001</v>
       </c>
+      <c r="V215" t="n">
+        <v>0</v>
+      </c>
+      <c r="W215" t="n">
+        <v>19.12</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -18016,6 +19384,12 @@
       <c r="U216" t="n">
         <v>8.677</v>
       </c>
+      <c r="V216" t="n">
+        <v>0</v>
+      </c>
+      <c r="W216" t="n">
+        <v>19.207</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -18087,6 +19461,12 @@
       <c r="U217" t="n">
         <v>8.148</v>
       </c>
+      <c r="V217" t="n">
+        <v>0</v>
+      </c>
+      <c r="W217" t="n">
+        <v>18.382</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -18158,6 +19538,12 @@
       <c r="U218" t="n">
         <v>8.837999999999999</v>
       </c>
+      <c r="V218" t="n">
+        <v>0</v>
+      </c>
+      <c r="W218" t="n">
+        <v>19.472</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -18229,6 +19615,12 @@
       <c r="U219" t="n">
         <v>8.43</v>
       </c>
+      <c r="V219" t="n">
+        <v>0</v>
+      </c>
+      <c r="W219" t="n">
+        <v>18.834</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -18300,6 +19692,12 @@
       <c r="U220" t="n">
         <v>8.333</v>
       </c>
+      <c r="V220" t="n">
+        <v>0</v>
+      </c>
+      <c r="W220" t="n">
+        <v>18.684</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -18371,6 +19769,12 @@
       <c r="U221" t="n">
         <v>8.554</v>
       </c>
+      <c r="V221" t="n">
+        <v>0</v>
+      </c>
+      <c r="W221" t="n">
+        <v>19.024</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -18442,6 +19846,12 @@
       <c r="U222" t="n">
         <v>8.295</v>
       </c>
+      <c r="V222" t="n">
+        <v>0</v>
+      </c>
+      <c r="W222" t="n">
+        <v>18.609</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -18513,6 +19923,12 @@
       <c r="U223" t="n">
         <v>8.202999999999999</v>
       </c>
+      <c r="V223" t="n">
+        <v>0</v>
+      </c>
+      <c r="W223" t="n">
+        <v>18.514</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -18584,6 +20000,12 @@
       <c r="U224" t="n">
         <v>7.675</v>
       </c>
+      <c r="V224" t="n">
+        <v>0</v>
+      </c>
+      <c r="W224" t="n">
+        <v>17.671</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -18655,6 +20077,12 @@
       <c r="U225" t="n">
         <v>7.984</v>
       </c>
+      <c r="V225" t="n">
+        <v>0</v>
+      </c>
+      <c r="W225" t="n">
+        <v>18.167</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -18726,6 +20154,12 @@
       <c r="U226" t="n">
         <v>8.179</v>
       </c>
+      <c r="V226" t="n">
+        <v>0</v>
+      </c>
+      <c r="W226" t="n">
+        <v>18.495</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -18797,6 +20231,12 @@
       <c r="U227" t="n">
         <v>7.985</v>
       </c>
+      <c r="V227" t="n">
+        <v>0</v>
+      </c>
+      <c r="W227" t="n">
+        <v>18.165</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -18868,6 +20308,12 @@
       <c r="U228" t="n">
         <v>7.907</v>
       </c>
+      <c r="V228" t="n">
+        <v>0</v>
+      </c>
+      <c r="W228" t="n">
+        <v>18.054</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -18939,6 +20385,12 @@
       <c r="U229" t="n">
         <v>7.887</v>
       </c>
+      <c r="V229" t="n">
+        <v>0</v>
+      </c>
+      <c r="W229" t="n">
+        <v>18.015</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -19010,6 +20462,12 @@
       <c r="U230" t="n">
         <v>8.137</v>
       </c>
+      <c r="V230" t="n">
+        <v>0</v>
+      </c>
+      <c r="W230" t="n">
+        <v>18.42</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -19081,6 +20539,12 @@
       <c r="U231" t="n">
         <v>8.292999999999999</v>
       </c>
+      <c r="V231" t="n">
+        <v>0</v>
+      </c>
+      <c r="W231" t="n">
+        <v>18.655</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -19152,6 +20616,12 @@
       <c r="U232" t="n">
         <v>8.284000000000001</v>
       </c>
+      <c r="V232" t="n">
+        <v>0</v>
+      </c>
+      <c r="W232" t="n">
+        <v>18.637</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -19223,6 +20693,12 @@
       <c r="U233" t="n">
         <v>8.401</v>
       </c>
+      <c r="V233" t="n">
+        <v>0</v>
+      </c>
+      <c r="W233" t="n">
+        <v>18.845</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -19294,6 +20770,12 @@
       <c r="U234" t="n">
         <v>7.82</v>
       </c>
+      <c r="V234" t="n">
+        <v>0</v>
+      </c>
+      <c r="W234" t="n">
+        <v>17.897</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -19365,6 +20847,12 @@
       <c r="U235" t="n">
         <v>8.269</v>
       </c>
+      <c r="V235" t="n">
+        <v>0</v>
+      </c>
+      <c r="W235" t="n">
+        <v>18.618</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -19436,6 +20924,12 @@
       <c r="U236" t="n">
         <v>7.864</v>
       </c>
+      <c r="V236" t="n">
+        <v>0</v>
+      </c>
+      <c r="W236" t="n">
+        <v>17.98</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -19507,6 +21001,12 @@
       <c r="U237" t="n">
         <v>8.029999999999999</v>
       </c>
+      <c r="V237" t="n">
+        <v>0</v>
+      </c>
+      <c r="W237" t="n">
+        <v>18.241</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -19578,6 +21078,12 @@
       <c r="U238" t="n">
         <v>8.333</v>
       </c>
+      <c r="V238" t="n">
+        <v>0</v>
+      </c>
+      <c r="W238" t="n">
+        <v>18.732</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -19649,6 +21155,12 @@
       <c r="U239" t="n">
         <v>8.154999999999999</v>
       </c>
+      <c r="V239" t="n">
+        <v>0</v>
+      </c>
+      <c r="W239" t="n">
+        <v>18.438</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -19720,6 +21232,12 @@
       <c r="U240" t="n">
         <v>7.878</v>
       </c>
+      <c r="V240" t="n">
+        <v>0</v>
+      </c>
+      <c r="W240" t="n">
+        <v>18.055</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -19791,6 +21309,12 @@
       <c r="U241" t="n">
         <v>8.316000000000001</v>
       </c>
+      <c r="V241" t="n">
+        <v>0</v>
+      </c>
+      <c r="W241" t="n">
+        <v>18.771</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -19862,6 +21386,12 @@
       <c r="U242" t="n">
         <v>8.118</v>
       </c>
+      <c r="V242" t="n">
+        <v>0</v>
+      </c>
+      <c r="W242" t="n">
+        <v>18.448</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -19933,6 +21463,12 @@
       <c r="U243" t="n">
         <v>8.417999999999999</v>
       </c>
+      <c r="V243" t="n">
+        <v>0</v>
+      </c>
+      <c r="W243" t="n">
+        <v>18.939</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -20004,6 +21540,12 @@
       <c r="U244" t="n">
         <v>7.912</v>
       </c>
+      <c r="V244" t="n">
+        <v>0</v>
+      </c>
+      <c r="W244" t="n">
+        <v>18.107</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -20075,6 +21617,12 @@
       <c r="U245" t="n">
         <v>7.485</v>
       </c>
+      <c r="V245" t="n">
+        <v>0</v>
+      </c>
+      <c r="W245" t="n">
+        <v>17.402</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -20146,6 +21694,12 @@
       <c r="U246" t="n">
         <v>7.563</v>
       </c>
+      <c r="V246" t="n">
+        <v>0</v>
+      </c>
+      <c r="W246" t="n">
+        <v>17.534</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -20217,6 +21771,12 @@
       <c r="U247" t="n">
         <v>8.114000000000001</v>
       </c>
+      <c r="V247" t="n">
+        <v>0</v>
+      </c>
+      <c r="W247" t="n">
+        <v>18.443</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -20288,6 +21848,12 @@
       <c r="U248" t="n">
         <v>8.109</v>
       </c>
+      <c r="V248" t="n">
+        <v>0</v>
+      </c>
+      <c r="W248" t="n">
+        <v>18.433</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -20359,6 +21925,12 @@
       <c r="U249" t="n">
         <v>8.193</v>
       </c>
+      <c r="V249" t="n">
+        <v>0</v>
+      </c>
+      <c r="W249" t="n">
+        <v>18.573</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -20430,6 +22002,12 @@
       <c r="U250" t="n">
         <v>8.058</v>
       </c>
+      <c r="V250" t="n">
+        <v>0</v>
+      </c>
+      <c r="W250" t="n">
+        <v>18.35</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -20501,6 +22079,12 @@
       <c r="U251" t="n">
         <v>8.07</v>
       </c>
+      <c r="V251" t="n">
+        <v>0</v>
+      </c>
+      <c r="W251" t="n">
+        <v>18.371</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -20572,6 +22156,12 @@
       <c r="U252" t="n">
         <v>8.265000000000001</v>
       </c>
+      <c r="V252" t="n">
+        <v>0</v>
+      </c>
+      <c r="W252" t="n">
+        <v>18.687</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -20643,6 +22233,12 @@
       <c r="U253" t="n">
         <v>8.103999999999999</v>
       </c>
+      <c r="V253" t="n">
+        <v>0</v>
+      </c>
+      <c r="W253" t="n">
+        <v>18.426</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -20714,6 +22310,12 @@
       <c r="U254" t="n">
         <v>8.628</v>
       </c>
+      <c r="V254" t="n">
+        <v>0</v>
+      </c>
+      <c r="W254" t="n">
+        <v>19.277</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -20785,6 +22387,12 @@
       <c r="U255" t="n">
         <v>7.566</v>
       </c>
+      <c r="V255" t="n">
+        <v>0</v>
+      </c>
+      <c r="W255" t="n">
+        <v>17.533</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -20856,6 +22464,12 @@
       <c r="U256" t="n">
         <v>8.526</v>
       </c>
+      <c r="V256" t="n">
+        <v>0</v>
+      </c>
+      <c r="W256" t="n">
+        <v>19.113</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -20927,6 +22541,12 @@
       <c r="U257" t="n">
         <v>8.747999999999999</v>
       </c>
+      <c r="V257" t="n">
+        <v>0</v>
+      </c>
+      <c r="W257" t="n">
+        <v>19.343</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -20998,6 +22618,12 @@
       <c r="U258" t="n">
         <v>8.691000000000001</v>
       </c>
+      <c r="V258" t="n">
+        <v>0</v>
+      </c>
+      <c r="W258" t="n">
+        <v>19.263</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -21069,6 +22695,12 @@
       <c r="U259" t="n">
         <v>7.76</v>
       </c>
+      <c r="V259" t="n">
+        <v>0</v>
+      </c>
+      <c r="W259" t="n">
+        <v>17.792</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -21140,6 +22772,12 @@
       <c r="U260" t="n">
         <v>7.488</v>
       </c>
+      <c r="V260" t="n">
+        <v>0</v>
+      </c>
+      <c r="W260" t="n">
+        <v>17.356</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -21211,6 +22849,12 @@
       <c r="U261" t="n">
         <v>8.301</v>
       </c>
+      <c r="V261" t="n">
+        <v>0</v>
+      </c>
+      <c r="W261" t="n">
+        <v>18.662</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -21282,6 +22926,12 @@
       <c r="U262" t="n">
         <v>9.243</v>
       </c>
+      <c r="V262" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="W262" t="n">
+        <v>20.079</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -21353,6 +23003,12 @@
       <c r="U263" t="n">
         <v>8.412000000000001</v>
       </c>
+      <c r="V263" t="n">
+        <v>0</v>
+      </c>
+      <c r="W263" t="n">
+        <v>18.83</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -21424,6 +23080,12 @@
       <c r="U264" t="n">
         <v>8.179</v>
       </c>
+      <c r="V264" t="n">
+        <v>0</v>
+      </c>
+      <c r="W264" t="n">
+        <v>18.477</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -21495,6 +23157,12 @@
       <c r="U265" t="n">
         <v>8.843999999999999</v>
       </c>
+      <c r="V265" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="W265" t="n">
+        <v>19.469</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -21566,6 +23234,12 @@
       <c r="U266" t="n">
         <v>8.951000000000001</v>
       </c>
+      <c r="V266" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="W266" t="n">
+        <v>19.637</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -21637,6 +23311,12 @@
       <c r="U267" t="n">
         <v>8.718999999999999</v>
       </c>
+      <c r="V267" t="n">
+        <v>0</v>
+      </c>
+      <c r="W267" t="n">
+        <v>19.299</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -21708,6 +23388,12 @@
       <c r="U268" t="n">
         <v>8.616</v>
       </c>
+      <c r="V268" t="n">
+        <v>0</v>
+      </c>
+      <c r="W268" t="n">
+        <v>19.143</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -21779,6 +23465,12 @@
       <c r="U269" t="n">
         <v>8.353999999999999</v>
       </c>
+      <c r="V269" t="n">
+        <v>0</v>
+      </c>
+      <c r="W269" t="n">
+        <v>18.738</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -21850,6 +23542,12 @@
       <c r="U270" t="n">
         <v>8.816000000000001</v>
       </c>
+      <c r="V270" t="n">
+        <v>0</v>
+      </c>
+      <c r="W270" t="n">
+        <v>19.448</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -21921,6 +23619,12 @@
       <c r="U271" t="n">
         <v>7.693</v>
       </c>
+      <c r="V271" t="n">
+        <v>0</v>
+      </c>
+      <c r="W271" t="n">
+        <v>17.685</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -21992,6 +23696,12 @@
       <c r="U272" t="n">
         <v>8.609</v>
       </c>
+      <c r="V272" t="n">
+        <v>0</v>
+      </c>
+      <c r="W272" t="n">
+        <v>19.133</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -22063,6 +23773,12 @@
       <c r="U273" t="n">
         <v>8.394</v>
       </c>
+      <c r="V273" t="n">
+        <v>0</v>
+      </c>
+      <c r="W273" t="n">
+        <v>18.807</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -22134,6 +23850,12 @@
       <c r="U274" t="n">
         <v>8.166</v>
       </c>
+      <c r="V274" t="n">
+        <v>0</v>
+      </c>
+      <c r="W274" t="n">
+        <v>18.416</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -22205,6 +23927,12 @@
       <c r="U275" t="n">
         <v>8.141</v>
       </c>
+      <c r="V275" t="n">
+        <v>0</v>
+      </c>
+      <c r="W275" t="n">
+        <v>18.376</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -22276,6 +24004,12 @@
       <c r="U276" t="n">
         <v>8.929</v>
       </c>
+      <c r="V276" t="n">
+        <v>0</v>
+      </c>
+      <c r="W276" t="n">
+        <v>19.62</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -22347,6 +24081,12 @@
       <c r="U277" t="n">
         <v>8.436</v>
       </c>
+      <c r="V277" t="n">
+        <v>0</v>
+      </c>
+      <c r="W277" t="n">
+        <v>18.848</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -22418,6 +24158,12 @@
       <c r="U278" t="n">
         <v>8.795</v>
       </c>
+      <c r="V278" t="n">
+        <v>0</v>
+      </c>
+      <c r="W278" t="n">
+        <v>19.41</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -22489,6 +24235,12 @@
       <c r="U279" t="n">
         <v>8.807</v>
       </c>
+      <c r="V279" t="n">
+        <v>0</v>
+      </c>
+      <c r="W279" t="n">
+        <v>19.427</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -22560,6 +24312,12 @@
       <c r="U280" t="n">
         <v>7.937</v>
       </c>
+      <c r="V280" t="n">
+        <v>0</v>
+      </c>
+      <c r="W280" t="n">
+        <v>18.051</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -22631,6 +24389,12 @@
       <c r="U281" t="n">
         <v>8.311999999999999</v>
       </c>
+      <c r="V281" t="n">
+        <v>0</v>
+      </c>
+      <c r="W281" t="n">
+        <v>18.65</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -22702,6 +24466,12 @@
       <c r="U282" t="n">
         <v>8.318</v>
       </c>
+      <c r="V282" t="n">
+        <v>0</v>
+      </c>
+      <c r="W282" t="n">
+        <v>18.66</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -22773,6 +24543,12 @@
       <c r="U283" t="n">
         <v>8.853999999999999</v>
       </c>
+      <c r="V283" t="n">
+        <v>0</v>
+      </c>
+      <c r="W283" t="n">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -22844,6 +24620,12 @@
       <c r="U284" t="n">
         <v>8.615</v>
       </c>
+      <c r="V284" t="n">
+        <v>0</v>
+      </c>
+      <c r="W284" t="n">
+        <v>19.128</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -22915,6 +24697,12 @@
       <c r="U285" t="n">
         <v>8.531000000000001</v>
       </c>
+      <c r="V285" t="n">
+        <v>0</v>
+      </c>
+      <c r="W285" t="n">
+        <v>18.992</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -22986,6 +24774,12 @@
       <c r="U286" t="n">
         <v>8.422000000000001</v>
       </c>
+      <c r="V286" t="n">
+        <v>0</v>
+      </c>
+      <c r="W286" t="n">
+        <v>18.83</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -23057,6 +24851,12 @@
       <c r="U287" t="n">
         <v>7.548</v>
       </c>
+      <c r="V287" t="n">
+        <v>0</v>
+      </c>
+      <c r="W287" t="n">
+        <v>17.408</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -23128,6 +24928,12 @@
       <c r="U288" t="n">
         <v>8.414</v>
       </c>
+      <c r="V288" t="n">
+        <v>0</v>
+      </c>
+      <c r="W288" t="n">
+        <v>18.817</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -23199,6 +25005,12 @@
       <c r="U289" t="n">
         <v>8.507</v>
       </c>
+      <c r="V289" t="n">
+        <v>0</v>
+      </c>
+      <c r="W289" t="n">
+        <v>18.956</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -23270,6 +25082,12 @@
       <c r="U290" t="n">
         <v>8.494</v>
       </c>
+      <c r="V290" t="n">
+        <v>0</v>
+      </c>
+      <c r="W290" t="n">
+        <v>18.936</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -23341,6 +25159,12 @@
       <c r="U291" t="n">
         <v>8.173</v>
       </c>
+      <c r="V291" t="n">
+        <v>0</v>
+      </c>
+      <c r="W291" t="n">
+        <v>18.339</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -23412,6 +25236,12 @@
       <c r="U292" t="n">
         <v>8.228999999999999</v>
       </c>
+      <c r="V292" t="n">
+        <v>0</v>
+      </c>
+      <c r="W292" t="n">
+        <v>18.428</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -23483,6 +25313,12 @@
       <c r="U293" t="n">
         <v>8.25</v>
       </c>
+      <c r="V293" t="n">
+        <v>0</v>
+      </c>
+      <c r="W293" t="n">
+        <v>18.461</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -23554,6 +25390,12 @@
       <c r="U294" t="n">
         <v>8.284000000000001</v>
       </c>
+      <c r="V294" t="n">
+        <v>0</v>
+      </c>
+      <c r="W294" t="n">
+        <v>18.513</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -23625,6 +25467,12 @@
       <c r="U295" t="n">
         <v>7.632</v>
       </c>
+      <c r="V295" t="n">
+        <v>0</v>
+      </c>
+      <c r="W295" t="n">
+        <v>17.455</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -23696,6 +25544,12 @@
       <c r="U296" t="n">
         <v>8.577</v>
       </c>
+      <c r="V296" t="n">
+        <v>0</v>
+      </c>
+      <c r="W296" t="n">
+        <v>18.976</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -23767,6 +25621,12 @@
       <c r="U297" t="n">
         <v>8.182</v>
       </c>
+      <c r="V297" t="n">
+        <v>0</v>
+      </c>
+      <c r="W297" t="n">
+        <v>18.356</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -23838,6 +25698,12 @@
       <c r="U298" t="n">
         <v>7.962</v>
       </c>
+      <c r="V298" t="n">
+        <v>0</v>
+      </c>
+      <c r="W298" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -23909,6 +25775,12 @@
       <c r="U299" t="n">
         <v>8.555</v>
       </c>
+      <c r="V299" t="n">
+        <v>0</v>
+      </c>
+      <c r="W299" t="n">
+        <v>18.945</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -23980,6 +25852,12 @@
       <c r="U300" t="n">
         <v>8.625</v>
       </c>
+      <c r="V300" t="n">
+        <v>0</v>
+      </c>
+      <c r="W300" t="n">
+        <v>19.045</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -24051,6 +25929,12 @@
       <c r="U301" t="n">
         <v>8.148</v>
       </c>
+      <c r="V301" t="n">
+        <v>0</v>
+      </c>
+      <c r="W301" t="n">
+        <v>18.3</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -24122,6 +26006,12 @@
       <c r="U302" t="n">
         <v>8.119</v>
       </c>
+      <c r="V302" t="n">
+        <v>0</v>
+      </c>
+      <c r="W302" t="n">
+        <v>18.253</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -24193,6 +26083,12 @@
       <c r="U303" t="n">
         <v>8.512</v>
       </c>
+      <c r="V303" t="n">
+        <v>0</v>
+      </c>
+      <c r="W303" t="n">
+        <v>18.873</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -24264,6 +26160,12 @@
       <c r="U304" t="n">
         <v>8.173999999999999</v>
       </c>
+      <c r="V304" t="n">
+        <v>0</v>
+      </c>
+      <c r="W304" t="n">
+        <v>18.331</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -24335,6 +26237,12 @@
       <c r="U305" t="n">
         <v>7.92</v>
       </c>
+      <c r="V305" t="n">
+        <v>0</v>
+      </c>
+      <c r="W305" t="n">
+        <v>17.926</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -24406,6 +26314,12 @@
       <c r="U306" t="n">
         <v>8.371</v>
       </c>
+      <c r="V306" t="n">
+        <v>0</v>
+      </c>
+      <c r="W306" t="n">
+        <v>18.657</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -24477,6 +26391,12 @@
       <c r="U307" t="n">
         <v>8.247999999999999</v>
       </c>
+      <c r="V307" t="n">
+        <v>0</v>
+      </c>
+      <c r="W307" t="n">
+        <v>18.46</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -24548,6 +26468,12 @@
       <c r="U308" t="n">
         <v>7.194</v>
       </c>
+      <c r="V308" t="n">
+        <v>0</v>
+      </c>
+      <c r="W308" t="n">
+        <v>16.728</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -24619,6 +26545,12 @@
       <c r="U309" t="n">
         <v>7.885</v>
       </c>
+      <c r="V309" t="n">
+        <v>0</v>
+      </c>
+      <c r="W309" t="n">
+        <v>17.863</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -24690,6 +26622,12 @@
       <c r="U310" t="n">
         <v>7.589</v>
       </c>
+      <c r="V310" t="n">
+        <v>0</v>
+      </c>
+      <c r="W310" t="n">
+        <v>17.381</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -24761,6 +26699,12 @@
       <c r="U311" t="n">
         <v>7.702</v>
       </c>
+      <c r="V311" t="n">
+        <v>0</v>
+      </c>
+      <c r="W311" t="n">
+        <v>17.556</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -24832,6 +26776,12 @@
       <c r="U312" t="n">
         <v>7.748</v>
       </c>
+      <c r="V312" t="n">
+        <v>0</v>
+      </c>
+      <c r="W312" t="n">
+        <v>17.635</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -24903,6 +26853,12 @@
       <c r="U313" t="n">
         <v>7.841</v>
       </c>
+      <c r="V313" t="n">
+        <v>0</v>
+      </c>
+      <c r="W313" t="n">
+        <v>17.788</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -24974,6 +26930,12 @@
       <c r="U314" t="n">
         <v>7.6</v>
       </c>
+      <c r="V314" t="n">
+        <v>0</v>
+      </c>
+      <c r="W314" t="n">
+        <v>17.399</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -25045,6 +27007,12 @@
       <c r="U315" t="n">
         <v>7.739</v>
       </c>
+      <c r="V315" t="n">
+        <v>0</v>
+      </c>
+      <c r="W315" t="n">
+        <v>17.624</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -25116,6 +27084,12 @@
       <c r="U316" t="n">
         <v>7.636</v>
       </c>
+      <c r="V316" t="n">
+        <v>0</v>
+      </c>
+      <c r="W316" t="n">
+        <v>17.457</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -25187,6 +27161,12 @@
       <c r="U317" t="n">
         <v>7.854</v>
       </c>
+      <c r="V317" t="n">
+        <v>0</v>
+      </c>
+      <c r="W317" t="n">
+        <v>17.809</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -25258,6 +27238,12 @@
       <c r="U318" t="n">
         <v>7.766</v>
       </c>
+      <c r="V318" t="n">
+        <v>0</v>
+      </c>
+      <c r="W318" t="n">
+        <v>17.669</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -25329,6 +27315,12 @@
       <c r="U319" t="n">
         <v>7.765</v>
       </c>
+      <c r="V319" t="n">
+        <v>0</v>
+      </c>
+      <c r="W319" t="n">
+        <v>17.667</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -25400,6 +27392,12 @@
       <c r="U320" t="n">
         <v>7.513</v>
       </c>
+      <c r="V320" t="n">
+        <v>0</v>
+      </c>
+      <c r="W320" t="n">
+        <v>17.253</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -25471,6 +27469,12 @@
       <c r="U321" t="n">
         <v>7.736</v>
       </c>
+      <c r="V321" t="n">
+        <v>0</v>
+      </c>
+      <c r="W321" t="n">
+        <v>17.617</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -25542,6 +27546,12 @@
       <c r="U322" t="n">
         <v>7.08</v>
       </c>
+      <c r="V322" t="n">
+        <v>0</v>
+      </c>
+      <c r="W322" t="n">
+        <v>16.537</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -25613,6 +27623,12 @@
       <c r="U323" t="n">
         <v>7.12</v>
       </c>
+      <c r="V323" t="n">
+        <v>0</v>
+      </c>
+      <c r="W323" t="n">
+        <v>16.607</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -25684,6 +27700,12 @@
       <c r="U324" t="n">
         <v>7.839</v>
       </c>
+      <c r="V324" t="n">
+        <v>0</v>
+      </c>
+      <c r="W324" t="n">
+        <v>17.785</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -25755,6 +27777,12 @@
       <c r="U325" t="n">
         <v>8.364000000000001</v>
       </c>
+      <c r="V325" t="n">
+        <v>0</v>
+      </c>
+      <c r="W325" t="n">
+        <v>18.742</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -25826,6 +27854,12 @@
       <c r="U326" t="n">
         <v>8.488</v>
       </c>
+      <c r="V326" t="n">
+        <v>0</v>
+      </c>
+      <c r="W326" t="n">
+        <v>18.927</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -25897,6 +27931,12 @@
       <c r="U327" t="n">
         <v>8.500999999999999</v>
       </c>
+      <c r="V327" t="n">
+        <v>0</v>
+      </c>
+      <c r="W327" t="n">
+        <v>18.955</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -25968,6 +28008,12 @@
       <c r="U328" t="n">
         <v>8.032</v>
       </c>
+      <c r="V328" t="n">
+        <v>0</v>
+      </c>
+      <c r="W328" t="n">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -26039,6 +28085,12 @@
       <c r="U329" t="n">
         <v>8.550000000000001</v>
       </c>
+      <c r="V329" t="n">
+        <v>0</v>
+      </c>
+      <c r="W329" t="n">
+        <v>19.042</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -26110,6 +28162,12 @@
       <c r="U330" t="n">
         <v>7.63</v>
       </c>
+      <c r="V330" t="n">
+        <v>0</v>
+      </c>
+      <c r="W330" t="n">
+        <v>17.549</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -26181,6 +28239,12 @@
       <c r="U331" t="n">
         <v>8.173</v>
       </c>
+      <c r="V331" t="n">
+        <v>0</v>
+      </c>
+      <c r="W331" t="n">
+        <v>18.435</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -26252,6 +28316,12 @@
       <c r="U332" t="n">
         <v>8.602</v>
       </c>
+      <c r="V332" t="n">
+        <v>0</v>
+      </c>
+      <c r="W332" t="n">
+        <v>19.126</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -26323,6 +28393,12 @@
       <c r="U333" t="n">
         <v>8.523</v>
       </c>
+      <c r="V333" t="n">
+        <v>0</v>
+      </c>
+      <c r="W333" t="n">
+        <v>18.983</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -26394,6 +28470,12 @@
       <c r="U334" t="n">
         <v>8.209</v>
       </c>
+      <c r="V334" t="n">
+        <v>0</v>
+      </c>
+      <c r="W334" t="n">
+        <v>18.492</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -26465,6 +28547,12 @@
       <c r="U335" t="n">
         <v>8.27</v>
       </c>
+      <c r="V335" t="n">
+        <v>0</v>
+      </c>
+      <c r="W335" t="n">
+        <v>18.594</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -26536,6 +28624,12 @@
       <c r="U336" t="n">
         <v>8.696999999999999</v>
       </c>
+      <c r="V336" t="n">
+        <v>0</v>
+      </c>
+      <c r="W336" t="n">
+        <v>19.265</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -26607,6 +28701,12 @@
       <c r="U337" t="n">
         <v>8.476000000000001</v>
       </c>
+      <c r="V337" t="n">
+        <v>0</v>
+      </c>
+      <c r="W337" t="n">
+        <v>18.927</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -26678,6 +28778,12 @@
       <c r="U338" t="n">
         <v>7.631</v>
       </c>
+      <c r="V338" t="n">
+        <v>0</v>
+      </c>
+      <c r="W338" t="n">
+        <v>17.551</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -26749,6 +28855,12 @@
       <c r="U339" t="n">
         <v>8.414999999999999</v>
       </c>
+      <c r="V339" t="n">
+        <v>0</v>
+      </c>
+      <c r="W339" t="n">
+        <v>18.819</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -26820,6 +28932,12 @@
       <c r="U340" t="n">
         <v>8.225</v>
       </c>
+      <c r="V340" t="n">
+        <v>0</v>
+      </c>
+      <c r="W340" t="n">
+        <v>18.523</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -26891,6 +29009,12 @@
       <c r="U341" t="n">
         <v>8.122999999999999</v>
       </c>
+      <c r="V341" t="n">
+        <v>0</v>
+      </c>
+      <c r="W341" t="n">
+        <v>18.353</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -26962,6 +29086,12 @@
       <c r="U342" t="n">
         <v>7.323</v>
       </c>
+      <c r="V342" t="n">
+        <v>0</v>
+      </c>
+      <c r="W342" t="n">
+        <v>16.968</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -27033,6 +29163,12 @@
       <c r="U343" t="n">
         <v>7.094</v>
       </c>
+      <c r="V343" t="n">
+        <v>0</v>
+      </c>
+      <c r="W343" t="n">
+        <v>16.592</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -27104,6 +29240,12 @@
       <c r="U344" t="n">
         <v>7.202</v>
       </c>
+      <c r="V344" t="n">
+        <v>0</v>
+      </c>
+      <c r="W344" t="n">
+        <v>16.769</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -27175,6 +29317,12 @@
       <c r="U345" t="n">
         <v>7.201</v>
       </c>
+      <c r="V345" t="n">
+        <v>0</v>
+      </c>
+      <c r="W345" t="n">
+        <v>16.766</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -27246,6 +29394,12 @@
       <c r="U346" t="n">
         <v>7.193</v>
       </c>
+      <c r="V346" t="n">
+        <v>0</v>
+      </c>
+      <c r="W346" t="n">
+        <v>16.76</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -27317,6 +29471,12 @@
       <c r="U347" t="n">
         <v>6.948</v>
       </c>
+      <c r="V347" t="n">
+        <v>0</v>
+      </c>
+      <c r="W347" t="n">
+        <v>16.343</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -27388,6 +29548,12 @@
       <c r="U348" t="n">
         <v>7.244</v>
       </c>
+      <c r="V348" t="n">
+        <v>0</v>
+      </c>
+      <c r="W348" t="n">
+        <v>16.845</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -27459,6 +29625,12 @@
       <c r="U349" t="n">
         <v>7.246</v>
       </c>
+      <c r="V349" t="n">
+        <v>0</v>
+      </c>
+      <c r="W349" t="n">
+        <v>16.848</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -27530,6 +29702,12 @@
       <c r="U350" t="n">
         <v>6.989</v>
       </c>
+      <c r="V350" t="n">
+        <v>0</v>
+      </c>
+      <c r="W350" t="n">
+        <v>16.409</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -27601,6 +29779,12 @@
       <c r="U351" t="n">
         <v>7.295</v>
       </c>
+      <c r="V351" t="n">
+        <v>0</v>
+      </c>
+      <c r="W351" t="n">
+        <v>16.931</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -27672,6 +29856,12 @@
       <c r="U352" t="n">
         <v>6.595</v>
       </c>
+      <c r="V352" t="n">
+        <v>0</v>
+      </c>
+      <c r="W352" t="n">
+        <v>15.739</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -27743,6 +29933,12 @@
       <c r="U353" t="n">
         <v>7.088</v>
       </c>
+      <c r="V353" t="n">
+        <v>0</v>
+      </c>
+      <c r="W353" t="n">
+        <v>16.579</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -27814,6 +30010,12 @@
       <c r="U354" t="n">
         <v>7.095</v>
       </c>
+      <c r="V354" t="n">
+        <v>0</v>
+      </c>
+      <c r="W354" t="n">
+        <v>16.588</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -27885,6 +30087,12 @@
       <c r="U355" t="n">
         <v>7.374</v>
       </c>
+      <c r="V355" t="n">
+        <v>0</v>
+      </c>
+      <c r="W355" t="n">
+        <v>17.052</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -27956,6 +30164,12 @@
       <c r="U356" t="n">
         <v>7.182</v>
       </c>
+      <c r="V356" t="n">
+        <v>0</v>
+      </c>
+      <c r="W356" t="n">
+        <v>16.741</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -28027,6 +30241,12 @@
       <c r="U357" t="n">
         <v>7.07</v>
       </c>
+      <c r="V357" t="n">
+        <v>0</v>
+      </c>
+      <c r="W357" t="n">
+        <v>16.547</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -28098,6 +30318,12 @@
       <c r="U358" t="n">
         <v>7.08</v>
       </c>
+      <c r="V358" t="n">
+        <v>0</v>
+      </c>
+      <c r="W358" t="n">
+        <v>16.568</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -28169,6 +30395,12 @@
       <c r="U359" t="n">
         <v>7.427</v>
       </c>
+      <c r="V359" t="n">
+        <v>0</v>
+      </c>
+      <c r="W359" t="n">
+        <v>16.985</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -28240,6 +30472,12 @@
       <c r="U360" t="n">
         <v>6.898</v>
       </c>
+      <c r="V360" t="n">
+        <v>0</v>
+      </c>
+      <c r="W360" t="n">
+        <v>16.107</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -28311,6 +30549,12 @@
       <c r="U361" t="n">
         <v>7.059</v>
       </c>
+      <c r="V361" t="n">
+        <v>0</v>
+      </c>
+      <c r="W361" t="n">
+        <v>16.378</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -28382,6 +30626,12 @@
       <c r="U362" t="n">
         <v>7.031</v>
       </c>
+      <c r="V362" t="n">
+        <v>0</v>
+      </c>
+      <c r="W362" t="n">
+        <v>16.33</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -28453,6 +30703,12 @@
       <c r="U363" t="n">
         <v>7.016</v>
       </c>
+      <c r="V363" t="n">
+        <v>0</v>
+      </c>
+      <c r="W363" t="n">
+        <v>16.3</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -28524,6 +30780,12 @@
       <c r="U364" t="n">
         <v>7.038</v>
       </c>
+      <c r="V364" t="n">
+        <v>0</v>
+      </c>
+      <c r="W364" t="n">
+        <v>16.343</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -28595,6 +30857,12 @@
       <c r="U365" t="n">
         <v>7.177</v>
       </c>
+      <c r="V365" t="n">
+        <v>0</v>
+      </c>
+      <c r="W365" t="n">
+        <v>16.573</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -28666,6 +30934,12 @@
       <c r="U366" t="n">
         <v>7.338</v>
       </c>
+      <c r="V366" t="n">
+        <v>0</v>
+      </c>
+      <c r="W366" t="n">
+        <v>16.84</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -28737,6 +31011,12 @@
       <c r="U367" t="n">
         <v>6.914</v>
       </c>
+      <c r="V367" t="n">
+        <v>0</v>
+      </c>
+      <c r="W367" t="n">
+        <v>16.136</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -28808,6 +31088,12 @@
       <c r="U368" t="n">
         <v>7.463</v>
       </c>
+      <c r="V368" t="n">
+        <v>0</v>
+      </c>
+      <c r="W368" t="n">
+        <v>17.046</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -28879,6 +31165,12 @@
       <c r="U369" t="n">
         <v>6.657</v>
       </c>
+      <c r="V369" t="n">
+        <v>0</v>
+      </c>
+      <c r="W369" t="n">
+        <v>15.703</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -28950,6 +31242,12 @@
       <c r="U370" t="n">
         <v>7.443</v>
       </c>
+      <c r="V370" t="n">
+        <v>0</v>
+      </c>
+      <c r="W370" t="n">
+        <v>17.009</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -29021,6 +31319,12 @@
       <c r="U371" t="n">
         <v>7.126</v>
       </c>
+      <c r="V371" t="n">
+        <v>0</v>
+      </c>
+      <c r="W371" t="n">
+        <v>16.489</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -29092,6 +31396,12 @@
       <c r="U372" t="n">
         <v>7.273</v>
       </c>
+      <c r="V372" t="n">
+        <v>0</v>
+      </c>
+      <c r="W372" t="n">
+        <v>16.732</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -29163,6 +31473,12 @@
       <c r="U373" t="n">
         <v>7.196</v>
       </c>
+      <c r="V373" t="n">
+        <v>0</v>
+      </c>
+      <c r="W373" t="n">
+        <v>16.606</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -29234,6 +31550,12 @@
       <c r="U374" t="n">
         <v>7.325</v>
       </c>
+      <c r="V374" t="n">
+        <v>0</v>
+      </c>
+      <c r="W374" t="n">
+        <v>16.817</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -29305,6 +31627,12 @@
       <c r="U375" t="n">
         <v>6.628</v>
       </c>
+      <c r="V375" t="n">
+        <v>0</v>
+      </c>
+      <c r="W375" t="n">
+        <v>15.647</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -29376,6 +31704,12 @@
       <c r="U376" t="n">
         <v>8.537000000000001</v>
       </c>
+      <c r="V376" t="n">
+        <v>0</v>
+      </c>
+      <c r="W376" t="n">
+        <v>19.145</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -29447,6 +31781,12 @@
       <c r="U377" t="n">
         <v>8.420999999999999</v>
       </c>
+      <c r="V377" t="n">
+        <v>0</v>
+      </c>
+      <c r="W377" t="n">
+        <v>18.956</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -29518,6 +31858,12 @@
       <c r="U378" t="n">
         <v>8.337999999999999</v>
       </c>
+      <c r="V378" t="n">
+        <v>0</v>
+      </c>
+      <c r="W378" t="n">
+        <v>18.822</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -29589,6 +31935,12 @@
       <c r="U379" t="n">
         <v>8.398</v>
       </c>
+      <c r="V379" t="n">
+        <v>0</v>
+      </c>
+      <c r="W379" t="n">
+        <v>18.911</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -29660,6 +32012,12 @@
       <c r="U380" t="n">
         <v>8.313000000000001</v>
       </c>
+      <c r="V380" t="n">
+        <v>0</v>
+      </c>
+      <c r="W380" t="n">
+        <v>18.781</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -29731,6 +32089,12 @@
       <c r="U381" t="n">
         <v>7.841</v>
       </c>
+      <c r="V381" t="n">
+        <v>0</v>
+      </c>
+      <c r="W381" t="n">
+        <v>18.006</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -29802,6 +32166,12 @@
       <c r="U382" t="n">
         <v>8.513999999999999</v>
       </c>
+      <c r="V382" t="n">
+        <v>0</v>
+      </c>
+      <c r="W382" t="n">
+        <v>19.105</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -29873,6 +32243,12 @@
       <c r="U383" t="n">
         <v>7.654</v>
       </c>
+      <c r="V383" t="n">
+        <v>0</v>
+      </c>
+      <c r="W383" t="n">
+        <v>17.7</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -29944,6 +32320,12 @@
       <c r="U384" t="n">
         <v>7.885</v>
       </c>
+      <c r="V384" t="n">
+        <v>0</v>
+      </c>
+      <c r="W384" t="n">
+        <v>18.08</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -30015,6 +32397,12 @@
       <c r="U385" t="n">
         <v>8.567</v>
       </c>
+      <c r="V385" t="n">
+        <v>0</v>
+      </c>
+      <c r="W385" t="n">
+        <v>19.19</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -30086,6 +32474,12 @@
       <c r="U386" t="n">
         <v>8.162000000000001</v>
       </c>
+      <c r="V386" t="n">
+        <v>0</v>
+      </c>
+      <c r="W386" t="n">
+        <v>18.534</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -30157,6 +32551,12 @@
       <c r="U387" t="n">
         <v>8.257</v>
       </c>
+      <c r="V387" t="n">
+        <v>0</v>
+      </c>
+      <c r="W387" t="n">
+        <v>18.69</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -30228,6 +32628,12 @@
       <c r="U388" t="n">
         <v>8.071</v>
       </c>
+      <c r="V388" t="n">
+        <v>0</v>
+      </c>
+      <c r="W388" t="n">
+        <v>18.386</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -30299,6 +32705,12 @@
       <c r="U389" t="n">
         <v>8.132</v>
       </c>
+      <c r="V389" t="n">
+        <v>0</v>
+      </c>
+      <c r="W389" t="n">
+        <v>18.482</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -30370,6 +32782,12 @@
       <c r="U390" t="n">
         <v>7.636</v>
       </c>
+      <c r="V390" t="n">
+        <v>0</v>
+      </c>
+      <c r="W390" t="n">
+        <v>17.671</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -30441,6 +32859,12 @@
       <c r="U391" t="n">
         <v>8.269</v>
       </c>
+      <c r="V391" t="n">
+        <v>0</v>
+      </c>
+      <c r="W391" t="n">
+        <v>18.71</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -30512,6 +32936,12 @@
       <c r="U392" t="n">
         <v>8.446</v>
       </c>
+      <c r="V392" t="n">
+        <v>0</v>
+      </c>
+      <c r="W392" t="n">
+        <v>18.996</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -30583,6 +33013,12 @@
       <c r="U393" t="n">
         <v>7.309</v>
       </c>
+      <c r="V393" t="n">
+        <v>0</v>
+      </c>
+      <c r="W393" t="n">
+        <v>17.053</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -30654,6 +33090,12 @@
       <c r="U394" t="n">
         <v>6.706</v>
       </c>
+      <c r="V394" t="n">
+        <v>0</v>
+      </c>
+      <c r="W394" t="n">
+        <v>16.022</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -30725,6 +33167,12 @@
       <c r="U395" t="n">
         <v>6.791</v>
       </c>
+      <c r="V395" t="n">
+        <v>0</v>
+      </c>
+      <c r="W395" t="n">
+        <v>16.171</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -30796,6 +33244,12 @@
       <c r="U396" t="n">
         <v>7.12</v>
       </c>
+      <c r="V396" t="n">
+        <v>0</v>
+      </c>
+      <c r="W396" t="n">
+        <v>16.729</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -30867,6 +33321,12 @@
       <c r="U397" t="n">
         <v>7.126</v>
       </c>
+      <c r="V397" t="n">
+        <v>0</v>
+      </c>
+      <c r="W397" t="n">
+        <v>16.743</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -30938,6 +33398,12 @@
       <c r="U398" t="n">
         <v>7.269</v>
       </c>
+      <c r="V398" t="n">
+        <v>0</v>
+      </c>
+      <c r="W398" t="n">
+        <v>16.988</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -31009,6 +33475,12 @@
       <c r="U399" t="n">
         <v>7.4</v>
       </c>
+      <c r="V399" t="n">
+        <v>0</v>
+      </c>
+      <c r="W399" t="n">
+        <v>17.202</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -31080,6 +33552,12 @@
       <c r="U400" t="n">
         <v>7.859</v>
       </c>
+      <c r="V400" t="n">
+        <v>0</v>
+      </c>
+      <c r="W400" t="n">
+        <v>17.958</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -31151,6 +33629,12 @@
       <c r="U401" t="n">
         <v>7.615</v>
       </c>
+      <c r="V401" t="n">
+        <v>0</v>
+      </c>
+      <c r="W401" t="n">
+        <v>17.561</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -31222,6 +33706,12 @@
       <c r="U402" t="n">
         <v>7.041</v>
       </c>
+      <c r="V402" t="n">
+        <v>0</v>
+      </c>
+      <c r="W402" t="n">
+        <v>16.6</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -31293,6 +33783,12 @@
       <c r="U403" t="n">
         <v>6.759</v>
       </c>
+      <c r="V403" t="n">
+        <v>0</v>
+      </c>
+      <c r="W403" t="n">
+        <v>16.11</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -31364,6 +33860,12 @@
       <c r="U404" t="n">
         <v>6.949</v>
       </c>
+      <c r="V404" t="n">
+        <v>0</v>
+      </c>
+      <c r="W404" t="n">
+        <v>16.452</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -31435,6 +33937,12 @@
       <c r="U405" t="n">
         <v>6.877</v>
       </c>
+      <c r="V405" t="n">
+        <v>0</v>
+      </c>
+      <c r="W405" t="n">
+        <v>16.307</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -31506,6 +34014,12 @@
       <c r="U406" t="n">
         <v>6.911</v>
       </c>
+      <c r="V406" t="n">
+        <v>0</v>
+      </c>
+      <c r="W406" t="n">
+        <v>16.364</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -31577,6 +34091,12 @@
       <c r="U407" t="n">
         <v>7.537</v>
       </c>
+      <c r="V407" t="n">
+        <v>0</v>
+      </c>
+      <c r="W407" t="n">
+        <v>17.433</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -31648,6 +34168,12 @@
       <c r="U408" t="n">
         <v>7.862</v>
       </c>
+      <c r="V408" t="n">
+        <v>0</v>
+      </c>
+      <c r="W408" t="n">
+        <v>17.964</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -31719,6 +34245,12 @@
       <c r="U409" t="n">
         <v>6.988</v>
       </c>
+      <c r="V409" t="n">
+        <v>0</v>
+      </c>
+      <c r="W409" t="n">
+        <v>16.503</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -31790,6 +34322,12 @@
       <c r="U410" t="n">
         <v>7.539</v>
       </c>
+      <c r="V410" t="n">
+        <v>0</v>
+      </c>
+      <c r="W410" t="n">
+        <v>17.259</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -31861,6 +34399,12 @@
       <c r="U411" t="n">
         <v>7.982</v>
       </c>
+      <c r="V411" t="n">
+        <v>0</v>
+      </c>
+      <c r="W411" t="n">
+        <v>17.972</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -31932,6 +34476,12 @@
       <c r="U412" t="n">
         <v>7.644</v>
       </c>
+      <c r="V412" t="n">
+        <v>0</v>
+      </c>
+      <c r="W412" t="n">
+        <v>17.423</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -32003,6 +34553,12 @@
       <c r="U413" t="n">
         <v>7.215</v>
       </c>
+      <c r="V413" t="n">
+        <v>0</v>
+      </c>
+      <c r="W413" t="n">
+        <v>16.724</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -32074,6 +34630,12 @@
       <c r="U414" t="n">
         <v>7.484</v>
       </c>
+      <c r="V414" t="n">
+        <v>0</v>
+      </c>
+      <c r="W414" t="n">
+        <v>17.168</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -32145,6 +34707,12 @@
       <c r="U415" t="n">
         <v>7.792</v>
       </c>
+      <c r="V415" t="n">
+        <v>0</v>
+      </c>
+      <c r="W415" t="n">
+        <v>17.657</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -32216,6 +34784,12 @@
       <c r="U416" t="n">
         <v>7.932</v>
       </c>
+      <c r="V416" t="n">
+        <v>0</v>
+      </c>
+      <c r="W416" t="n">
+        <v>17.887</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -32287,6 +34861,12 @@
       <c r="U417" t="n">
         <v>7.787</v>
       </c>
+      <c r="V417" t="n">
+        <v>0</v>
+      </c>
+      <c r="W417" t="n">
+        <v>17.658</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -32358,6 +34938,12 @@
       <c r="U418" t="n">
         <v>7.893</v>
       </c>
+      <c r="V418" t="n">
+        <v>0</v>
+      </c>
+      <c r="W418" t="n">
+        <v>17.831</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -32429,6 +35015,12 @@
       <c r="U419" t="n">
         <v>7.594</v>
       </c>
+      <c r="V419" t="n">
+        <v>0</v>
+      </c>
+      <c r="W419" t="n">
+        <v>17.345</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -32500,6 +35092,12 @@
       <c r="U420" t="n">
         <v>7.12</v>
       </c>
+      <c r="V420" t="n">
+        <v>0</v>
+      </c>
+      <c r="W420" t="n">
+        <v>16.565</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -32571,6 +35169,12 @@
       <c r="U421" t="n">
         <v>7.822</v>
       </c>
+      <c r="V421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W421" t="n">
+        <v>17.711</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -32642,6 +35246,12 @@
       <c r="U422" t="n">
         <v>7.367</v>
       </c>
+      <c r="V422" t="n">
+        <v>0</v>
+      </c>
+      <c r="W422" t="n">
+        <v>16.971</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -32713,6 +35323,12 @@
       <c r="U423" t="n">
         <v>7.704</v>
       </c>
+      <c r="V423" t="n">
+        <v>0</v>
+      </c>
+      <c r="W423" t="n">
+        <v>17.526</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -32784,6 +35400,12 @@
       <c r="U424" t="n">
         <v>7.886</v>
       </c>
+      <c r="V424" t="n">
+        <v>0</v>
+      </c>
+      <c r="W424" t="n">
+        <v>17.813</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -32855,6 +35477,12 @@
       <c r="U425" t="n">
         <v>7.531</v>
       </c>
+      <c r="V425" t="n">
+        <v>0</v>
+      </c>
+      <c r="W425" t="n">
+        <v>17.246</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -32926,6 +35554,12 @@
       <c r="U426" t="n">
         <v>7.88</v>
       </c>
+      <c r="V426" t="n">
+        <v>0</v>
+      </c>
+      <c r="W426" t="n">
+        <v>17.812</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -32997,6 +35631,12 @@
       <c r="U427" t="n">
         <v>7.875</v>
       </c>
+      <c r="V427" t="n">
+        <v>0</v>
+      </c>
+      <c r="W427" t="n">
+        <v>18.072</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -33068,6 +35708,12 @@
       <c r="U428" t="n">
         <v>7.915</v>
       </c>
+      <c r="V428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W428" t="n">
+        <v>18.139</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -33139,6 +35785,12 @@
       <c r="U429" t="n">
         <v>7.777</v>
       </c>
+      <c r="V429" t="n">
+        <v>0</v>
+      </c>
+      <c r="W429" t="n">
+        <v>17.914</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -33210,6 +35862,12 @@
       <c r="U430" t="n">
         <v>7.197</v>
       </c>
+      <c r="V430" t="n">
+        <v>0</v>
+      </c>
+      <c r="W430" t="n">
+        <v>16.955</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -33281,6 +35939,12 @@
       <c r="U431" t="n">
         <v>8.103999999999999</v>
       </c>
+      <c r="V431" t="n">
+        <v>0</v>
+      </c>
+      <c r="W431" t="n">
+        <v>18.447</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -33352,6 +36016,12 @@
       <c r="U432" t="n">
         <v>8.096</v>
       </c>
+      <c r="V432" t="n">
+        <v>0</v>
+      </c>
+      <c r="W432" t="n">
+        <v>18.439</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -33423,6 +36093,12 @@
       <c r="U433" t="n">
         <v>7.676</v>
       </c>
+      <c r="V433" t="n">
+        <v>0</v>
+      </c>
+      <c r="W433" t="n">
+        <v>17.746</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -33494,6 +36170,12 @@
       <c r="U434" t="n">
         <v>8.045</v>
       </c>
+      <c r="V434" t="n">
+        <v>0</v>
+      </c>
+      <c r="W434" t="n">
+        <v>18.343</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -33565,6 +36247,12 @@
       <c r="U435" t="n">
         <v>7.746</v>
       </c>
+      <c r="V435" t="n">
+        <v>0</v>
+      </c>
+      <c r="W435" t="n">
+        <v>17.865</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -33636,6 +36324,12 @@
       <c r="U436" t="n">
         <v>7.61</v>
       </c>
+      <c r="V436" t="n">
+        <v>0</v>
+      </c>
+      <c r="W436" t="n">
+        <v>17.643</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -33707,6 +36401,12 @@
       <c r="U437" t="n">
         <v>8.009</v>
       </c>
+      <c r="V437" t="n">
+        <v>0</v>
+      </c>
+      <c r="W437" t="n">
+        <v>18.298</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -33778,6 +36478,12 @@
       <c r="U438" t="n">
         <v>7.455</v>
       </c>
+      <c r="V438" t="n">
+        <v>0</v>
+      </c>
+      <c r="W438" t="n">
+        <v>17.387</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -33849,6 +36555,12 @@
       <c r="U439" t="n">
         <v>7.923</v>
       </c>
+      <c r="V439" t="n">
+        <v>0</v>
+      </c>
+      <c r="W439" t="n">
+        <v>18.141</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -33920,6 +36632,12 @@
       <c r="U440" t="n">
         <v>7.779</v>
       </c>
+      <c r="V440" t="n">
+        <v>0</v>
+      </c>
+      <c r="W440" t="n">
+        <v>17.917</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -33991,6 +36709,12 @@
       <c r="U441" t="n">
         <v>7.513</v>
       </c>
+      <c r="V441" t="n">
+        <v>0</v>
+      </c>
+      <c r="W441" t="n">
+        <v>17.483</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -34062,6 +36786,12 @@
       <c r="U442" t="n">
         <v>7.761</v>
       </c>
+      <c r="V442" t="n">
+        <v>0</v>
+      </c>
+      <c r="W442" t="n">
+        <v>17.883</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -34133,6 +36863,12 @@
       <c r="U443" t="n">
         <v>7.582</v>
       </c>
+      <c r="V443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W443" t="n">
+        <v>17.596</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -34204,6 +36940,12 @@
       <c r="U444" t="n">
         <v>7.109</v>
       </c>
+      <c r="V444" t="n">
+        <v>0</v>
+      </c>
+      <c r="W444" t="n">
+        <v>16.602</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -34275,6 +37017,12 @@
       <c r="U445" t="n">
         <v>7.078</v>
       </c>
+      <c r="V445" t="n">
+        <v>0</v>
+      </c>
+      <c r="W445" t="n">
+        <v>16.549</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -34346,6 +37094,12 @@
       <c r="U446" t="n">
         <v>6.81</v>
       </c>
+      <c r="V446" t="n">
+        <v>0</v>
+      </c>
+      <c r="W446" t="n">
+        <v>16.103</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -34417,6 +37171,12 @@
       <c r="U447" t="n">
         <v>7.234</v>
       </c>
+      <c r="V447" t="n">
+        <v>0</v>
+      </c>
+      <c r="W447" t="n">
+        <v>16.812</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -34488,6 +37248,12 @@
       <c r="U448" t="n">
         <v>6.59</v>
       </c>
+      <c r="V448" t="n">
+        <v>0</v>
+      </c>
+      <c r="W448" t="n">
+        <v>15.717</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -34559,6 +37325,12 @@
       <c r="U449" t="n">
         <v>7.303</v>
       </c>
+      <c r="V449" t="n">
+        <v>0</v>
+      </c>
+      <c r="W449" t="n">
+        <v>16.925</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -34630,6 +37402,12 @@
       <c r="U450" t="n">
         <v>7.224</v>
       </c>
+      <c r="V450" t="n">
+        <v>0</v>
+      </c>
+      <c r="W450" t="n">
+        <v>16.793</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -34701,6 +37479,12 @@
       <c r="U451" t="n">
         <v>7.27</v>
       </c>
+      <c r="V451" t="n">
+        <v>0</v>
+      </c>
+      <c r="W451" t="n">
+        <v>16.871</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -34772,6 +37556,12 @@
       <c r="U452" t="n">
         <v>6.83</v>
       </c>
+      <c r="V452" t="n">
+        <v>0</v>
+      </c>
+      <c r="W452" t="n">
+        <v>16.136</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -34843,6 +37633,12 @@
       <c r="U453" t="n">
         <v>7.304</v>
       </c>
+      <c r="V453" t="n">
+        <v>0</v>
+      </c>
+      <c r="W453" t="n">
+        <v>16.927</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -34914,6 +37710,12 @@
       <c r="U454" t="n">
         <v>7.317</v>
       </c>
+      <c r="V454" t="n">
+        <v>0</v>
+      </c>
+      <c r="W454" t="n">
+        <v>16.947</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -34985,6 +37787,12 @@
       <c r="U455" t="n">
         <v>6.613</v>
       </c>
+      <c r="V455" t="n">
+        <v>0</v>
+      </c>
+      <c r="W455" t="n">
+        <v>15.759</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -35056,6 +37864,12 @@
       <c r="U456" t="n">
         <v>7.145</v>
       </c>
+      <c r="V456" t="n">
+        <v>0</v>
+      </c>
+      <c r="W456" t="n">
+        <v>16.662</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -35127,6 +37941,12 @@
       <c r="U457" t="n">
         <v>7.441</v>
       </c>
+      <c r="V457" t="n">
+        <v>0</v>
+      </c>
+      <c r="W457" t="n">
+        <v>17.153</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -35198,6 +38018,12 @@
       <c r="U458" t="n">
         <v>7.039</v>
       </c>
+      <c r="V458" t="n">
+        <v>0</v>
+      </c>
+      <c r="W458" t="n">
+        <v>16.487</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -35269,6 +38095,12 @@
       <c r="U459" t="n">
         <v>7.089</v>
       </c>
+      <c r="V459" t="n">
+        <v>0</v>
+      </c>
+      <c r="W459" t="n">
+        <v>16.56</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -35340,6 +38172,12 @@
       <c r="U460" t="n">
         <v>7.086</v>
       </c>
+      <c r="V460" t="n">
+        <v>0</v>
+      </c>
+      <c r="W460" t="n">
+        <v>16.562</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -35411,6 +38249,12 @@
       <c r="U461" t="n">
         <v>7.529</v>
       </c>
+      <c r="V461" t="n">
+        <v>0</v>
+      </c>
+      <c r="W461" t="n">
+        <v>17.286</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -35482,6 +38326,12 @@
       <c r="U462" t="n">
         <v>8.199999999999999</v>
       </c>
+      <c r="V462" t="n">
+        <v>0</v>
+      </c>
+      <c r="W462" t="n">
+        <v>18.37</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -35553,6 +38403,12 @@
       <c r="U463" t="n">
         <v>8.553000000000001</v>
       </c>
+      <c r="V463" t="n">
+        <v>0</v>
+      </c>
+      <c r="W463" t="n">
+        <v>18.927</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -35624,6 +38480,12 @@
       <c r="U464" t="n">
         <v>8.106</v>
       </c>
+      <c r="V464" t="n">
+        <v>0</v>
+      </c>
+      <c r="W464" t="n">
+        <v>18.221</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -35695,6 +38557,12 @@
       <c r="U465" t="n">
         <v>8.234</v>
       </c>
+      <c r="V465" t="n">
+        <v>0</v>
+      </c>
+      <c r="W465" t="n">
+        <v>18.424</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -35766,6 +38634,12 @@
       <c r="U466" t="n">
         <v>8.311</v>
       </c>
+      <c r="V466" t="n">
+        <v>0</v>
+      </c>
+      <c r="W466" t="n">
+        <v>18.542</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -35837,6 +38711,12 @@
       <c r="U467" t="n">
         <v>8.253</v>
       </c>
+      <c r="V467" t="n">
+        <v>0</v>
+      </c>
+      <c r="W467" t="n">
+        <v>18.459</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -35908,6 +38788,12 @@
       <c r="U468" t="n">
         <v>8.16</v>
       </c>
+      <c r="V468" t="n">
+        <v>0</v>
+      </c>
+      <c r="W468" t="n">
+        <v>18.303</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -35979,6 +38865,12 @@
       <c r="U469" t="n">
         <v>8.237</v>
       </c>
+      <c r="V469" t="n">
+        <v>0</v>
+      </c>
+      <c r="W469" t="n">
+        <v>18.421</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -36050,6 +38942,12 @@
       <c r="U470" t="n">
         <v>7.851</v>
       </c>
+      <c r="V470" t="n">
+        <v>0</v>
+      </c>
+      <c r="W470" t="n">
+        <v>17.808</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -36121,6 +39019,12 @@
       <c r="U471" t="n">
         <v>8.271000000000001</v>
       </c>
+      <c r="V471" t="n">
+        <v>0</v>
+      </c>
+      <c r="W471" t="n">
+        <v>18.481</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -36192,6 +39096,12 @@
       <c r="U472" t="n">
         <v>7.764</v>
       </c>
+      <c r="V472" t="n">
+        <v>0</v>
+      </c>
+      <c r="W472" t="n">
+        <v>17.668</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -36263,6 +39173,12 @@
       <c r="U473" t="n">
         <v>8.103</v>
       </c>
+      <c r="V473" t="n">
+        <v>0</v>
+      </c>
+      <c r="W473" t="n">
+        <v>18.214</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -36334,6 +39250,12 @@
       <c r="U474" t="n">
         <v>8.292999999999999</v>
       </c>
+      <c r="V474" t="n">
+        <v>0</v>
+      </c>
+      <c r="W474" t="n">
+        <v>18.511</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -36405,6 +39327,12 @@
       <c r="U475" t="n">
         <v>8.199</v>
       </c>
+      <c r="V475" t="n">
+        <v>0</v>
+      </c>
+      <c r="W475" t="n">
+        <v>18.371</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -36476,6 +39404,12 @@
       <c r="U476" t="n">
         <v>7.851</v>
       </c>
+      <c r="V476" t="n">
+        <v>0</v>
+      </c>
+      <c r="W476" t="n">
+        <v>17.809</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -36547,6 +39481,12 @@
       <c r="U477" t="n">
         <v>8.426</v>
       </c>
+      <c r="V477" t="n">
+        <v>0</v>
+      </c>
+      <c r="W477" t="n">
+        <v>18.726</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -36618,6 +39558,12 @@
       <c r="U478" t="n">
         <v>7.469</v>
       </c>
+      <c r="V478" t="n">
+        <v>0</v>
+      </c>
+      <c r="W478" t="n">
+        <v>17.182</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -36689,6 +39635,12 @@
       <c r="U479" t="n">
         <v>8.602</v>
       </c>
+      <c r="V479" t="n">
+        <v>0</v>
+      </c>
+      <c r="W479" t="n">
+        <v>18.997</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -36760,6 +39712,12 @@
       <c r="U480" t="n">
         <v>8.172000000000001</v>
       </c>
+      <c r="V480" t="n">
+        <v>0</v>
+      </c>
+      <c r="W480" t="n">
+        <v>18.327</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -36831,6 +39789,12 @@
       <c r="U481" t="n">
         <v>8.358000000000001</v>
       </c>
+      <c r="V481" t="n">
+        <v>0</v>
+      </c>
+      <c r="W481" t="n">
+        <v>18.61</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -36902,6 +39866,12 @@
       <c r="U482" t="n">
         <v>8.210000000000001</v>
       </c>
+      <c r="V482" t="n">
+        <v>0</v>
+      </c>
+      <c r="W482" t="n">
+        <v>18.378</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -36973,6 +39943,12 @@
       <c r="U483" t="n">
         <v>8.055999999999999</v>
       </c>
+      <c r="V483" t="n">
+        <v>0</v>
+      </c>
+      <c r="W483" t="n">
+        <v>18.145</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -37044,6 +40020,12 @@
       <c r="U484" t="n">
         <v>8.358000000000001</v>
       </c>
+      <c r="V484" t="n">
+        <v>0</v>
+      </c>
+      <c r="W484" t="n">
+        <v>18.621</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -37115,6 +40097,12 @@
       <c r="U485" t="n">
         <v>7.468</v>
       </c>
+      <c r="V485" t="n">
+        <v>0</v>
+      </c>
+      <c r="W485" t="n">
+        <v>17.188</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -37186,6 +40174,12 @@
       <c r="U486" t="n">
         <v>8.779</v>
       </c>
+      <c r="V486" t="n">
+        <v>0</v>
+      </c>
+      <c r="W486" t="n">
+        <v>19.262</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -37257,6 +40251,12 @@
       <c r="U487" t="n">
         <v>8.276</v>
       </c>
+      <c r="V487" t="n">
+        <v>0</v>
+      </c>
+      <c r="W487" t="n">
+        <v>18.489</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -37328,6 +40328,12 @@
       <c r="U488" t="n">
         <v>8.348000000000001</v>
       </c>
+      <c r="V488" t="n">
+        <v>0</v>
+      </c>
+      <c r="W488" t="n">
+        <v>18.593</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -37399,6 +40405,12 @@
       <c r="U489" t="n">
         <v>8.066000000000001</v>
       </c>
+      <c r="V489" t="n">
+        <v>0</v>
+      </c>
+      <c r="W489" t="n">
+        <v>18.139</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -37470,6 +40482,12 @@
       <c r="U490" t="n">
         <v>8.316000000000001</v>
       </c>
+      <c r="V490" t="n">
+        <v>0</v>
+      </c>
+      <c r="W490" t="n">
+        <v>18.547</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -37541,6 +40559,12 @@
       <c r="U491" t="n">
         <v>8.208</v>
       </c>
+      <c r="V491" t="n">
+        <v>0</v>
+      </c>
+      <c r="W491" t="n">
+        <v>18.374</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -37612,6 +40636,12 @@
       <c r="U492" t="n">
         <v>7.615</v>
       </c>
+      <c r="V492" t="n">
+        <v>0</v>
+      </c>
+      <c r="W492" t="n">
+        <v>17.422</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -37683,6 +40713,12 @@
       <c r="U493" t="n">
         <v>8.093</v>
       </c>
+      <c r="V493" t="n">
+        <v>0</v>
+      </c>
+      <c r="W493" t="n">
+        <v>18.197</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -37754,6 +40790,12 @@
       <c r="U494" t="n">
         <v>8.673999999999999</v>
       </c>
+      <c r="V494" t="n">
+        <v>0</v>
+      </c>
+      <c r="W494" t="n">
+        <v>19.102</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -37825,6 +40867,12 @@
       <c r="U495" t="n">
         <v>8.114000000000001</v>
       </c>
+      <c r="V495" t="n">
+        <v>0</v>
+      </c>
+      <c r="W495" t="n">
+        <v>18.322</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -37896,6 +40944,12 @@
       <c r="U496" t="n">
         <v>8.151</v>
       </c>
+      <c r="V496" t="n">
+        <v>0</v>
+      </c>
+      <c r="W496" t="n">
+        <v>18.377</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -37967,6 +41021,12 @@
       <c r="U497" t="n">
         <v>8.56</v>
       </c>
+      <c r="V497" t="n">
+        <v>0</v>
+      </c>
+      <c r="W497" t="n">
+        <v>19.019</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -38038,6 +41098,12 @@
       <c r="U498" t="n">
         <v>8.358000000000001</v>
       </c>
+      <c r="V498" t="n">
+        <v>0</v>
+      </c>
+      <c r="W498" t="n">
+        <v>18.711</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -38109,6 +41175,12 @@
       <c r="U499" t="n">
         <v>8.301</v>
       </c>
+      <c r="V499" t="n">
+        <v>0</v>
+      </c>
+      <c r="W499" t="n">
+        <v>18.621</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -38180,6 +41252,12 @@
       <c r="U500" t="n">
         <v>7.822</v>
       </c>
+      <c r="V500" t="n">
+        <v>0</v>
+      </c>
+      <c r="W500" t="n">
+        <v>17.837</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -38251,6 +41329,12 @@
       <c r="U501" t="n">
         <v>8.378</v>
       </c>
+      <c r="V501" t="n">
+        <v>0</v>
+      </c>
+      <c r="W501" t="n">
+        <v>18.739</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -38322,6 +41406,12 @@
       <c r="U502" t="n">
         <v>8.048</v>
       </c>
+      <c r="V502" t="n">
+        <v>0</v>
+      </c>
+      <c r="W502" t="n">
+        <v>18.212</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -38393,6 +41483,12 @@
       <c r="U503" t="n">
         <v>8.141</v>
       </c>
+      <c r="V503" t="n">
+        <v>0</v>
+      </c>
+      <c r="W503" t="n">
+        <v>18.362</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -38464,6 +41560,12 @@
       <c r="U504" t="n">
         <v>7.988</v>
       </c>
+      <c r="V504" t="n">
+        <v>0</v>
+      </c>
+      <c r="W504" t="n">
+        <v>18.122</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -38535,6 +41637,12 @@
       <c r="U505" t="n">
         <v>8.164</v>
       </c>
+      <c r="V505" t="n">
+        <v>0</v>
+      </c>
+      <c r="W505" t="n">
+        <v>18.404</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -38606,6 +41714,12 @@
       <c r="U506" t="n">
         <v>7.58</v>
       </c>
+      <c r="V506" t="n">
+        <v>0</v>
+      </c>
+      <c r="W506" t="n">
+        <v>17.455</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -38677,6 +41791,12 @@
       <c r="U507" t="n">
         <v>8.619</v>
       </c>
+      <c r="V507" t="n">
+        <v>0</v>
+      </c>
+      <c r="W507" t="n">
+        <v>19.114</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -38748,6 +41868,12 @@
       <c r="U508" t="n">
         <v>7.964</v>
       </c>
+      <c r="V508" t="n">
+        <v>0</v>
+      </c>
+      <c r="W508" t="n">
+        <v>18.082</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -38819,6 +41945,12 @@
       <c r="U509" t="n">
         <v>8.345000000000001</v>
       </c>
+      <c r="V509" t="n">
+        <v>0</v>
+      </c>
+      <c r="W509" t="n">
+        <v>18.668</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -38890,6 +42022,12 @@
       <c r="U510" t="n">
         <v>8.1</v>
       </c>
+      <c r="V510" t="n">
+        <v>0</v>
+      </c>
+      <c r="W510" t="n">
+        <v>18.301</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -38961,6 +42099,12 @@
       <c r="U511" t="n">
         <v>8.504</v>
       </c>
+      <c r="V511" t="n">
+        <v>0</v>
+      </c>
+      <c r="W511" t="n">
+        <v>18.937</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -39032,6 +42176,12 @@
       <c r="U512" t="n">
         <v>7.784</v>
       </c>
+      <c r="V512" t="n">
+        <v>0</v>
+      </c>
+      <c r="W512" t="n">
+        <v>17.791</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -39103,6 +42253,12 @@
       <c r="U513" t="n">
         <v>8.170999999999999</v>
       </c>
+      <c r="V513" t="n">
+        <v>0</v>
+      </c>
+      <c r="W513" t="n">
+        <v>18.415</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -39174,6 +42330,12 @@
       <c r="U514" t="n">
         <v>8.445</v>
       </c>
+      <c r="V514" t="n">
+        <v>0</v>
+      </c>
+      <c r="W514" t="n">
+        <v>18.849</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -39245,6 +42407,12 @@
       <c r="U515" t="n">
         <v>8.195</v>
       </c>
+      <c r="V515" t="n">
+        <v>0</v>
+      </c>
+      <c r="W515" t="n">
+        <v>18.459</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -39316,6 +42484,12 @@
       <c r="U516" t="n">
         <v>7.514</v>
       </c>
+      <c r="V516" t="n">
+        <v>0</v>
+      </c>
+      <c r="W516" t="n">
+        <v>17.349</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -39387,6 +42561,12 @@
       <c r="U517" t="n">
         <v>7.979</v>
       </c>
+      <c r="V517" t="n">
+        <v>0</v>
+      </c>
+      <c r="W517" t="n">
+        <v>18.107</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -39458,6 +42638,12 @@
       <c r="U518" t="n">
         <v>8.257</v>
       </c>
+      <c r="V518" t="n">
+        <v>0</v>
+      </c>
+      <c r="W518" t="n">
+        <v>18.557</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -39529,6 +42715,12 @@
       <c r="U519" t="n">
         <v>8.237</v>
       </c>
+      <c r="V519" t="n">
+        <v>0</v>
+      </c>
+      <c r="W519" t="n">
+        <v>18.519</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -39600,6 +42792,12 @@
       <c r="U520" t="n">
         <v>8.175000000000001</v>
       </c>
+      <c r="V520" t="n">
+        <v>0</v>
+      </c>
+      <c r="W520" t="n">
+        <v>18.426</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -39671,6 +42869,12 @@
       <c r="U521" t="n">
         <v>8.491</v>
       </c>
+      <c r="V521" t="n">
+        <v>0</v>
+      </c>
+      <c r="W521" t="n">
+        <v>18.923</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -39742,6 +42946,12 @@
       <c r="U522" t="n">
         <v>8.009</v>
       </c>
+      <c r="V522" t="n">
+        <v>0</v>
+      </c>
+      <c r="W522" t="n">
+        <v>18.155</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -39813,6 +43023,12 @@
       <c r="U523" t="n">
         <v>8.442</v>
       </c>
+      <c r="V523" t="n">
+        <v>0</v>
+      </c>
+      <c r="W523" t="n">
+        <v>18.838</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -39884,6 +43100,12 @@
       <c r="U524" t="n">
         <v>8.395</v>
       </c>
+      <c r="V524" t="n">
+        <v>0</v>
+      </c>
+      <c r="W524" t="n">
+        <v>18.774</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -39955,6 +43177,12 @@
       <c r="U525" t="n">
         <v>8.220000000000001</v>
       </c>
+      <c r="V525" t="n">
+        <v>0</v>
+      </c>
+      <c r="W525" t="n">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -40026,6 +43254,12 @@
       <c r="U526" t="n">
         <v>8.460000000000001</v>
       </c>
+      <c r="V526" t="n">
+        <v>0</v>
+      </c>
+      <c r="W526" t="n">
+        <v>18.867</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -40097,6 +43331,12 @@
       <c r="U527" t="n">
         <v>8.146000000000001</v>
       </c>
+      <c r="V527" t="n">
+        <v>0</v>
+      </c>
+      <c r="W527" t="n">
+        <v>18.371</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -40168,6 +43408,12 @@
       <c r="U528" t="n">
         <v>7.995</v>
       </c>
+      <c r="V528" t="n">
+        <v>0</v>
+      </c>
+      <c r="W528" t="n">
+        <v>18.133</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -40239,6 +43485,12 @@
       <c r="U529" t="n">
         <v>8.003</v>
       </c>
+      <c r="V529" t="n">
+        <v>0</v>
+      </c>
+      <c r="W529" t="n">
+        <v>18.212</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -40310,6 +43562,12 @@
       <c r="U530" t="n">
         <v>7.727</v>
       </c>
+      <c r="V530" t="n">
+        <v>0</v>
+      </c>
+      <c r="W530" t="n">
+        <v>17.765</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -40381,6 +43639,12 @@
       <c r="U531" t="n">
         <v>7.84</v>
       </c>
+      <c r="V531" t="n">
+        <v>0</v>
+      </c>
+      <c r="W531" t="n">
+        <v>17.952</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -40452,6 +43716,12 @@
       <c r="U532" t="n">
         <v>7.965</v>
       </c>
+      <c r="V532" t="n">
+        <v>0</v>
+      </c>
+      <c r="W532" t="n">
+        <v>18.152</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -40523,6 +43793,12 @@
       <c r="U533" t="n">
         <v>7.526</v>
       </c>
+      <c r="V533" t="n">
+        <v>0</v>
+      </c>
+      <c r="W533" t="n">
+        <v>17.432</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -40594,6 +43870,12 @@
       <c r="U534" t="n">
         <v>8.026999999999999</v>
       </c>
+      <c r="V534" t="n">
+        <v>0</v>
+      </c>
+      <c r="W534" t="n">
+        <v>18.251</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -40665,6 +43947,12 @@
       <c r="U535" t="n">
         <v>7.881</v>
       </c>
+      <c r="V535" t="n">
+        <v>0</v>
+      </c>
+      <c r="W535" t="n">
+        <v>18.018</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -40736,6 +44024,12 @@
       <c r="U536" t="n">
         <v>7.884</v>
       </c>
+      <c r="V536" t="n">
+        <v>0</v>
+      </c>
+      <c r="W536" t="n">
+        <v>18.021</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -40807,6 +44101,12 @@
       <c r="U537" t="n">
         <v>7.736</v>
       </c>
+      <c r="V537" t="n">
+        <v>0</v>
+      </c>
+      <c r="W537" t="n">
+        <v>17.779</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -40878,6 +44178,12 @@
       <c r="U538" t="n">
         <v>7.966</v>
       </c>
+      <c r="V538" t="n">
+        <v>0</v>
+      </c>
+      <c r="W538" t="n">
+        <v>18.157</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -40949,6 +44255,12 @@
       <c r="U539" t="n">
         <v>7.967</v>
       </c>
+      <c r="V539" t="n">
+        <v>0</v>
+      </c>
+      <c r="W539" t="n">
+        <v>18.158</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -41020,6 +44332,12 @@
       <c r="U540" t="n">
         <v>8.236000000000001</v>
       </c>
+      <c r="V540" t="n">
+        <v>0</v>
+      </c>
+      <c r="W540" t="n">
+        <v>18.59</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -41091,6 +44409,12 @@
       <c r="U541" t="n">
         <v>7.555</v>
       </c>
+      <c r="V541" t="n">
+        <v>0</v>
+      </c>
+      <c r="W541" t="n">
+        <v>17.48</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -41162,6 +44486,12 @@
       <c r="U542" t="n">
         <v>8.09</v>
       </c>
+      <c r="V542" t="n">
+        <v>0</v>
+      </c>
+      <c r="W542" t="n">
+        <v>18.355</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -41233,6 +44563,12 @@
       <c r="U543" t="n">
         <v>8.007</v>
       </c>
+      <c r="V543" t="n">
+        <v>0</v>
+      </c>
+      <c r="W543" t="n">
+        <v>18.221</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -41304,6 +44640,12 @@
       <c r="U544" t="n">
         <v>7.948</v>
       </c>
+      <c r="V544" t="n">
+        <v>0</v>
+      </c>
+      <c r="W544" t="n">
+        <v>18.128</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -41374,6 +44716,12 @@
       </c>
       <c r="U545" t="n">
         <v>7.878</v>
+      </c>
+      <c r="V545" t="n">
+        <v>0</v>
+      </c>
+      <c r="W545" t="n">
+        <v>18.011</v>
       </c>
     </row>
   </sheetData>

--- a/projections/kicker_2026_combined.xlsx
+++ b/projections/kicker_2026_combined.xlsx
@@ -583,10 +583,10 @@
         <v>0.7955</v>
       </c>
       <c r="Q2" t="n">
-        <v>105.7</v>
+        <v>121.42</v>
       </c>
       <c r="R2" t="n">
-        <v>196.56</v>
+        <v>180.83</v>
       </c>
       <c r="S2" t="n">
         <v>171.57</v>
@@ -651,10 +651,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q3" t="n">
-        <v>102.4</v>
+        <v>118.08</v>
       </c>
       <c r="R3" t="n">
-        <v>193.02</v>
+        <v>177.33</v>
       </c>
       <c r="S3" t="n">
         <v>161.71</v>
@@ -719,10 +719,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q4" t="n">
-        <v>101.25</v>
+        <v>116.12</v>
       </c>
       <c r="R4" t="n">
-        <v>187.23</v>
+        <v>172.34</v>
       </c>
       <c r="S4" t="n">
         <v>155.33</v>
@@ -787,10 +787,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q5" t="n">
-        <v>100.8</v>
+        <v>115.69</v>
       </c>
       <c r="R5" t="n">
-        <v>186.88</v>
+        <v>171.98</v>
       </c>
       <c r="S5" t="n">
         <v>159.53</v>
@@ -855,10 +855,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q6" t="n">
-        <v>100.33</v>
+        <v>115.18</v>
       </c>
       <c r="R6" t="n">
-        <v>186.15</v>
+        <v>171.29</v>
       </c>
       <c r="S6" t="n">
         <v>145.85</v>
@@ -923,10 +923,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q7" t="n">
-        <v>99.55</v>
+        <v>114.33</v>
       </c>
       <c r="R7" t="n">
-        <v>185.03</v>
+        <v>170.23</v>
       </c>
       <c r="S7" t="n">
         <v>129.02</v>
@@ -991,10 +991,10 @@
         <v>0.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>98.3</v>
+        <v>113.05</v>
       </c>
       <c r="R8" t="n">
-        <v>183.46</v>
+        <v>168.73</v>
       </c>
       <c r="S8" t="n">
         <v>158.4</v>
@@ -1059,10 +1059,10 @@
         <v>0.5962</v>
       </c>
       <c r="Q9" t="n">
-        <v>97.93000000000001</v>
+        <v>112.48</v>
       </c>
       <c r="R9" t="n">
-        <v>182</v>
+        <v>167.45</v>
       </c>
       <c r="S9" t="n">
         <v>135.76</v>
@@ -1127,10 +1127,10 @@
         <v>0.7391</v>
       </c>
       <c r="Q10" t="n">
-        <v>96.53</v>
+        <v>111.38</v>
       </c>
       <c r="R10" t="n">
-        <v>182.33</v>
+        <v>167.48</v>
       </c>
       <c r="S10" t="n">
         <v>157.69</v>
@@ -1195,10 +1195,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q11" t="n">
-        <v>96.92</v>
+        <v>111.53</v>
       </c>
       <c r="R11" t="n">
-        <v>181.36</v>
+        <v>166.75</v>
       </c>
       <c r="S11" t="n">
         <v>145.83</v>
@@ -1263,10 +1263,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q12" t="n">
-        <v>96.64</v>
+        <v>111.33</v>
       </c>
       <c r="R12" t="n">
-        <v>181.5</v>
+        <v>166.81</v>
       </c>
       <c r="S12" t="n">
         <v>146.71</v>
@@ -1331,10 +1331,10 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>97.23999999999999</v>
+        <v>111.72</v>
       </c>
       <c r="R13" t="n">
-        <v>180.92</v>
+        <v>166.43</v>
       </c>
       <c r="S13" t="n">
         <v>136.7</v>
@@ -1399,10 +1399,10 @@
         <v>0.617</v>
       </c>
       <c r="Q14" t="n">
-        <v>96.67</v>
+        <v>111.29</v>
       </c>
       <c r="R14" t="n">
-        <v>181.19</v>
+        <v>166.56</v>
       </c>
       <c r="S14" t="n">
         <v>135.59</v>
@@ -1467,10 +1467,10 @@
         <v>0.5667</v>
       </c>
       <c r="Q15" t="n">
-        <v>96.56</v>
+        <v>111.02</v>
       </c>
       <c r="R15" t="n">
-        <v>180.06</v>
+        <v>165.62</v>
       </c>
       <c r="S15" t="n">
         <v>144.1</v>
@@ -1535,10 +1535,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q16" t="n">
-        <v>96.13</v>
+        <v>110.73</v>
       </c>
       <c r="R16" t="n">
-        <v>180.43</v>
+        <v>165.85</v>
       </c>
       <c r="S16" t="n">
         <v>137.55</v>
@@ -1603,10 +1603,10 @@
         <v>0.8254</v>
       </c>
       <c r="Q17" t="n">
-        <v>94.90000000000001</v>
+        <v>109.7</v>
       </c>
       <c r="R17" t="n">
-        <v>180.42</v>
+        <v>165.62</v>
       </c>
       <c r="S17" t="n">
         <v>142.56</v>
@@ -1671,10 +1671,10 @@
         <v>0.6744</v>
       </c>
       <c r="Q18" t="n">
-        <v>95.16</v>
+        <v>109.78</v>
       </c>
       <c r="R18" t="n">
-        <v>179.6</v>
+        <v>165</v>
       </c>
       <c r="S18" t="n">
         <v>142.04</v>
@@ -1739,10 +1739,10 @@
         <v>0.6604</v>
       </c>
       <c r="Q19" t="n">
-        <v>94.83</v>
+        <v>109.54</v>
       </c>
       <c r="R19" t="n">
-        <v>179.83</v>
+        <v>165.12</v>
       </c>
       <c r="S19" t="n">
         <v>148.39</v>
@@ -1807,10 +1807,10 @@
         <v>0.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>93.94</v>
+        <v>108.29</v>
       </c>
       <c r="R20" t="n">
-        <v>176.87</v>
+        <v>162.52</v>
       </c>
       <c r="S20" t="n">
         <v>144.41</v>
@@ -1875,10 +1875,10 @@
         <v>0.8431</v>
       </c>
       <c r="Q21" t="n">
-        <v>93.77</v>
+        <v>108.15</v>
       </c>
       <c r="R21" t="n">
-        <v>176.85</v>
+        <v>162.47</v>
       </c>
       <c r="S21" t="n">
         <v>142.2</v>
@@ -1943,10 +1943,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q22" t="n">
-        <v>93.25</v>
+        <v>107.52</v>
       </c>
       <c r="R22" t="n">
-        <v>175.73</v>
+        <v>161.45</v>
       </c>
       <c r="S22" t="n">
         <v>132.79</v>
@@ -2011,10 +2011,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q23" t="n">
-        <v>92.43000000000001</v>
+        <v>106.9</v>
       </c>
       <c r="R23" t="n">
-        <v>176.07</v>
+        <v>161.59</v>
       </c>
       <c r="S23" t="n">
         <v>142.14</v>
@@ -2079,10 +2079,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q24" t="n">
-        <v>90.29000000000001</v>
+        <v>104.75</v>
       </c>
       <c r="R24" t="n">
-        <v>173.81</v>
+        <v>159.36</v>
       </c>
       <c r="S24" t="n">
         <v>127.36</v>
@@ -2147,10 +2147,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q25" t="n">
-        <v>89.76000000000001</v>
+        <v>103.75</v>
       </c>
       <c r="R25" t="n">
-        <v>170.54</v>
+        <v>156.57</v>
       </c>
       <c r="S25" t="n">
         <v>141.17</v>
@@ -2215,10 +2215,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q26" t="n">
-        <v>89.17</v>
+        <v>103.17</v>
       </c>
       <c r="R26" t="n">
-        <v>170.07</v>
+        <v>156.07</v>
       </c>
       <c r="S26" t="n">
         <v>128.46</v>
@@ -2283,10 +2283,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q27" t="n">
-        <v>88.79000000000001</v>
+        <v>102.91</v>
       </c>
       <c r="R27" t="n">
-        <v>170.39</v>
+        <v>156.26</v>
       </c>
       <c r="S27" t="n">
         <v>139.26</v>
@@ -2351,10 +2351,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q28" t="n">
-        <v>82.88</v>
+        <v>96.61</v>
       </c>
       <c r="R28" t="n">
-        <v>162.24</v>
+        <v>148.51</v>
       </c>
       <c r="S28" t="n">
         <v>121.38</v>
@@ -2419,10 +2419,10 @@
         <v>0.7255</v>
       </c>
       <c r="Q29" t="n">
-        <v>82.34</v>
+        <v>96.11</v>
       </c>
       <c r="R29" t="n">
-        <v>161.94</v>
+        <v>148.16</v>
       </c>
       <c r="S29" t="n">
         <v>125.18</v>
@@ -2487,10 +2487,10 @@
         <v>0.6923</v>
       </c>
       <c r="Q30" t="n">
-        <v>81.94</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="R30" t="n">
-        <v>160.48</v>
+        <v>146.89</v>
       </c>
       <c r="S30" t="n">
         <v>122.33</v>
@@ -2555,10 +2555,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q31" t="n">
-        <v>83.13</v>
+        <v>96.25</v>
       </c>
       <c r="R31" t="n">
-        <v>158.97</v>
+        <v>145.84</v>
       </c>
       <c r="S31" t="n">
         <v>121.74</v>
@@ -2623,10 +2623,10 @@
         <v>0.6364</v>
       </c>
       <c r="Q32" t="n">
-        <v>82.45</v>
+        <v>95.8</v>
       </c>
       <c r="R32" t="n">
-        <v>159.59</v>
+        <v>146.24</v>
       </c>
       <c r="S32" t="n">
         <v>123.07</v>
@@ -2691,10 +2691,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q33" t="n">
-        <v>81.37</v>
+        <v>94.91</v>
       </c>
       <c r="R33" t="n">
-        <v>159.57</v>
+        <v>146.04</v>
       </c>
       <c r="S33" t="n">
         <v>124.16</v>
@@ -2907,10 +2907,10 @@
         <v>6.744</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.334</v>
       </c>
       <c r="W2" t="n">
-        <v>16.055</v>
+        <v>12.832</v>
       </c>
     </row>
     <row r="3">
@@ -2984,10 +2984,10 @@
         <v>7.284</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.521</v>
       </c>
       <c r="W3" t="n">
-        <v>16.958</v>
+        <v>13.609</v>
       </c>
     </row>
     <row r="4">
@@ -3061,10 +3061,10 @@
         <v>7.371</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.551</v>
       </c>
       <c r="W4" t="n">
-        <v>17.107</v>
+        <v>13.737</v>
       </c>
     </row>
     <row r="5">
@@ -3138,10 +3138,10 @@
         <v>7.176</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.484</v>
       </c>
       <c r="W5" t="n">
-        <v>16.78</v>
+        <v>13.456</v>
       </c>
     </row>
     <row r="6">
@@ -3215,10 +3215,10 @@
         <v>7.546</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.612</v>
       </c>
       <c r="W6" t="n">
-        <v>17.392</v>
+        <v>13.984</v>
       </c>
     </row>
     <row r="7">
@@ -3292,10 +3292,10 @@
         <v>7.264</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.514</v>
       </c>
       <c r="W7" t="n">
-        <v>16.922</v>
+        <v>13.579</v>
       </c>
     </row>
     <row r="8">
@@ -3369,10 +3369,10 @@
         <v>7.281</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="W8" t="n">
-        <v>16.953</v>
+        <v>13.605</v>
       </c>
     </row>
     <row r="9">
@@ -3446,10 +3446,10 @@
         <v>7.061</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.444</v>
       </c>
       <c r="W9" t="n">
-        <v>16.589</v>
+        <v>13.291</v>
       </c>
     </row>
     <row r="10">
@@ -3523,10 +3523,10 @@
         <v>6.706</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2.321</v>
       </c>
       <c r="W10" t="n">
-        <v>15.99</v>
+        <v>12.776</v>
       </c>
     </row>
     <row r="11">
@@ -3600,10 +3600,10 @@
         <v>6.964</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="W11" t="n">
-        <v>16.414</v>
+        <v>13.143</v>
       </c>
     </row>
     <row r="12">
@@ -3677,10 +3677,10 @@
         <v>7.262</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2.514</v>
       </c>
       <c r="W12" t="n">
-        <v>16.926</v>
+        <v>13.581</v>
       </c>
     </row>
     <row r="13">
@@ -3754,10 +3754,10 @@
         <v>7.52</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2.603</v>
       </c>
       <c r="W13" t="n">
-        <v>17.355</v>
+        <v>13.951</v>
       </c>
     </row>
     <row r="14">
@@ -3831,10 +3831,10 @@
         <v>7.266</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.515</v>
       </c>
       <c r="W14" t="n">
-        <v>16.932</v>
+        <v>13.586</v>
       </c>
     </row>
     <row r="15">
@@ -3908,10 +3908,10 @@
         <v>7.117</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.463</v>
       </c>
       <c r="W15" t="n">
-        <v>16.677</v>
+        <v>13.368</v>
       </c>
     </row>
     <row r="16">
@@ -3985,10 +3985,10 @@
         <v>7.12</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.464</v>
       </c>
       <c r="W16" t="n">
-        <v>16.682</v>
+        <v>13.372</v>
       </c>
     </row>
     <row r="17">
@@ -4062,10 +4062,10 @@
         <v>7.39</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.558</v>
       </c>
       <c r="W17" t="n">
-        <v>17.138</v>
+        <v>13.764</v>
       </c>
     </row>
     <row r="18">
@@ -4139,10 +4139,10 @@
         <v>7.484</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="W18" t="n">
-        <v>17.289</v>
+        <v>13.895</v>
       </c>
     </row>
     <row r="19">
@@ -4216,10 +4216,10 @@
         <v>7.938</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.748</v>
       </c>
       <c r="W19" t="n">
-        <v>18.049</v>
+        <v>14.549</v>
       </c>
     </row>
     <row r="20">
@@ -4293,10 +4293,10 @@
         <v>8.201000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2.839</v>
       </c>
       <c r="W20" t="n">
-        <v>18.483</v>
+        <v>14.924</v>
       </c>
     </row>
     <row r="21">
@@ -4370,10 +4370,10 @@
         <v>7.789</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.696</v>
       </c>
       <c r="W21" t="n">
-        <v>17.809</v>
+        <v>14.341</v>
       </c>
     </row>
     <row r="22">
@@ -4447,10 +4447,10 @@
         <v>8.228999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.848</v>
       </c>
       <c r="W22" t="n">
-        <v>18.528</v>
+        <v>14.963</v>
       </c>
     </row>
     <row r="23">
@@ -4524,10 +4524,10 @@
         <v>8.654999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2.996</v>
       </c>
       <c r="W23" t="n">
-        <v>19.195</v>
+        <v>15.547</v>
       </c>
     </row>
     <row r="24">
@@ -4601,10 +4601,10 @@
         <v>9.042999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="W24" t="n">
-        <v>19.776</v>
+        <v>16.061</v>
       </c>
     </row>
     <row r="25">
@@ -4678,10 +4678,10 @@
         <v>8.455</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2.927</v>
       </c>
       <c r="W25" t="n">
-        <v>18.885</v>
+        <v>15.275</v>
       </c>
     </row>
     <row r="26">
@@ -4755,10 +4755,10 @@
         <v>8.523</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="W26" t="n">
-        <v>18.991</v>
+        <v>15.368</v>
       </c>
     </row>
     <row r="27">
@@ -4832,10 +4832,10 @@
         <v>8.685</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3.006</v>
       </c>
       <c r="W27" t="n">
-        <v>19.241</v>
+        <v>15.587</v>
       </c>
     </row>
     <row r="28">
@@ -4909,10 +4909,10 @@
         <v>8.603999999999999</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2.978</v>
       </c>
       <c r="W28" t="n">
-        <v>19.124</v>
+        <v>15.483</v>
       </c>
     </row>
     <row r="29">
@@ -4986,10 +4986,10 @@
         <v>7.774</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>2.691</v>
       </c>
       <c r="W29" t="n">
-        <v>17.784</v>
+        <v>14.319</v>
       </c>
     </row>
     <row r="30">
@@ -5063,10 +5063,10 @@
         <v>8.384</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>2.902</v>
       </c>
       <c r="W30" t="n">
-        <v>18.774</v>
+        <v>15.178</v>
       </c>
     </row>
     <row r="31">
@@ -5140,10 +5140,10 @@
         <v>8.086</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>2.799</v>
       </c>
       <c r="W31" t="n">
-        <v>18.29</v>
+        <v>14.758</v>
       </c>
     </row>
     <row r="32">
@@ -5217,10 +5217,10 @@
         <v>8.074999999999999</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2.795</v>
       </c>
       <c r="W32" t="n">
-        <v>18.281</v>
+        <v>14.748</v>
       </c>
     </row>
     <row r="33">
@@ -5294,10 +5294,10 @@
         <v>9.105</v>
       </c>
       <c r="V33" t="n">
-        <v>0.01</v>
+        <v>3.158</v>
       </c>
       <c r="W33" t="n">
-        <v>19.866</v>
+        <v>16.141</v>
       </c>
     </row>
     <row r="34">
@@ -5371,10 +5371,10 @@
         <v>7.977</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>2.761</v>
       </c>
       <c r="W34" t="n">
-        <v>18.115</v>
+        <v>14.606</v>
       </c>
     </row>
     <row r="35">
@@ -5448,10 +5448,10 @@
         <v>8.733000000000001</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3.023</v>
       </c>
       <c r="W35" t="n">
-        <v>19.317</v>
+        <v>15.654</v>
       </c>
     </row>
     <row r="36">
@@ -5525,10 +5525,10 @@
         <v>8.007</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2.772</v>
       </c>
       <c r="W36" t="n">
-        <v>18.149</v>
+        <v>14.638</v>
       </c>
     </row>
     <row r="37">
@@ -5602,10 +5602,10 @@
         <v>7.566</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2.619</v>
       </c>
       <c r="W37" t="n">
-        <v>17.426</v>
+        <v>14.013</v>
       </c>
     </row>
     <row r="38">
@@ -5679,10 +5679,10 @@
         <v>7.997</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2.768</v>
       </c>
       <c r="W38" t="n">
-        <v>18.135</v>
+        <v>14.626</v>
       </c>
     </row>
     <row r="39">
@@ -5756,10 +5756,10 @@
         <v>7.789</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2.696</v>
       </c>
       <c r="W39" t="n">
-        <v>17.798</v>
+        <v>14.334</v>
       </c>
     </row>
     <row r="40">
@@ -5833,10 +5833,10 @@
         <v>7.708</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2.668</v>
       </c>
       <c r="W40" t="n">
-        <v>17.663</v>
+        <v>14.217</v>
       </c>
     </row>
     <row r="41">
@@ -5910,10 +5910,10 @@
         <v>7.532</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2.607</v>
       </c>
       <c r="W41" t="n">
-        <v>17.375</v>
+        <v>13.968</v>
       </c>
     </row>
     <row r="42">
@@ -5987,10 +5987,10 @@
         <v>6.87</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2.378</v>
       </c>
       <c r="W42" t="n">
-        <v>16.271</v>
+        <v>13.017</v>
       </c>
     </row>
     <row r="43">
@@ -6064,10 +6064,10 @@
         <v>6.847</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="W43" t="n">
-        <v>16.232</v>
+        <v>12.984</v>
       </c>
     </row>
     <row r="44">
@@ -6141,10 +6141,10 @@
         <v>7.833</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2.711</v>
       </c>
       <c r="W44" t="n">
-        <v>17.869</v>
+        <v>14.395</v>
       </c>
     </row>
     <row r="45">
@@ -6218,10 +6218,10 @@
         <v>7.792</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2.697</v>
       </c>
       <c r="W45" t="n">
-        <v>17.798</v>
+        <v>14.335</v>
       </c>
     </row>
     <row r="46">
@@ -6295,10 +6295,10 @@
         <v>7.646</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>2.647</v>
       </c>
       <c r="W46" t="n">
-        <v>17.558</v>
+        <v>14.127</v>
       </c>
     </row>
     <row r="47">
@@ -6372,10 +6372,10 @@
         <v>8.096</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>2.802</v>
       </c>
       <c r="W47" t="n">
-        <v>18.285</v>
+        <v>14.758</v>
       </c>
     </row>
     <row r="48">
@@ -6449,10 +6449,10 @@
         <v>6.837</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>2.367</v>
       </c>
       <c r="W48" t="n">
-        <v>16.215</v>
+        <v>12.969</v>
       </c>
     </row>
     <row r="49">
@@ -6526,10 +6526,10 @@
         <v>7.808</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>2.703</v>
       </c>
       <c r="W49" t="n">
-        <v>17.814</v>
+        <v>14.351</v>
       </c>
     </row>
     <row r="50">
@@ -6603,10 +6603,10 @@
         <v>7.718</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>2.671</v>
       </c>
       <c r="W50" t="n">
-        <v>17.673</v>
+        <v>14.227</v>
       </c>
     </row>
     <row r="51">
@@ -6680,10 +6680,10 @@
         <v>8.029</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>2.779</v>
       </c>
       <c r="W51" t="n">
-        <v>18.176</v>
+        <v>14.664</v>
       </c>
     </row>
     <row r="52">
@@ -6757,10 +6757,10 @@
         <v>7.494</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>2.594</v>
       </c>
       <c r="W52" t="n">
-        <v>17.314</v>
+        <v>13.915</v>
       </c>
     </row>
     <row r="53">
@@ -6834,10 +6834,10 @@
         <v>7.788</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>2.696</v>
       </c>
       <c r="W53" t="n">
-        <v>17.703</v>
+        <v>14.271</v>
       </c>
     </row>
     <row r="54">
@@ -6911,10 +6911,10 @@
         <v>7.705</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="W54" t="n">
-        <v>17.572</v>
+        <v>14.157</v>
       </c>
     </row>
     <row r="55">
@@ -6988,10 +6988,10 @@
         <v>7.582</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>2.624</v>
       </c>
       <c r="W55" t="n">
-        <v>17.362</v>
+        <v>13.977</v>
       </c>
     </row>
     <row r="56">
@@ -7065,10 +7065,10 @@
         <v>8.093</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>2.801</v>
       </c>
       <c r="W56" t="n">
-        <v>18.204</v>
+        <v>14.704</v>
       </c>
     </row>
     <row r="57">
@@ -7142,10 +7142,10 @@
         <v>7.957</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>2.754</v>
       </c>
       <c r="W57" t="n">
-        <v>17.982</v>
+        <v>14.512</v>
       </c>
     </row>
     <row r="58">
@@ -7219,10 +7219,10 @@
         <v>8.196</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>2.837</v>
       </c>
       <c r="W58" t="n">
-        <v>18.372</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="59">
@@ -7296,10 +7296,10 @@
         <v>7.765</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>2.688</v>
       </c>
       <c r="W59" t="n">
-        <v>17.67</v>
+        <v>14.242</v>
       </c>
     </row>
     <row r="60">
@@ -7373,10 +7373,10 @@
         <v>7.65</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>2.648</v>
       </c>
       <c r="W60" t="n">
-        <v>17.481</v>
+        <v>14.078</v>
       </c>
     </row>
     <row r="61">
@@ -7450,10 +7450,10 @@
         <v>8.26</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>2.859</v>
       </c>
       <c r="W61" t="n">
-        <v>18.473</v>
+        <v>14.938</v>
       </c>
     </row>
     <row r="62">
@@ -7527,10 +7527,10 @@
         <v>8.188000000000001</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>2.834</v>
       </c>
       <c r="W62" t="n">
-        <v>18.358</v>
+        <v>14.838</v>
       </c>
     </row>
     <row r="63">
@@ -7604,10 +7604,10 @@
         <v>7.413</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>2.566</v>
       </c>
       <c r="W63" t="n">
-        <v>17.092</v>
+        <v>13.742</v>
       </c>
     </row>
     <row r="64">
@@ -7681,10 +7681,10 @@
         <v>8.255000000000001</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>2.857</v>
       </c>
       <c r="W64" t="n">
-        <v>18.466</v>
+        <v>14.932</v>
       </c>
     </row>
     <row r="65">
@@ -7758,10 +7758,10 @@
         <v>7.56</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>2.617</v>
       </c>
       <c r="W65" t="n">
-        <v>17.334</v>
+        <v>13.951</v>
       </c>
     </row>
     <row r="66">
@@ -7835,10 +7835,10 @@
         <v>8.109999999999999</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>2.807</v>
       </c>
       <c r="W66" t="n">
-        <v>18.233</v>
+        <v>14.729</v>
       </c>
     </row>
     <row r="67">
@@ -7912,10 +7912,10 @@
         <v>8.19</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>2.835</v>
       </c>
       <c r="W67" t="n">
-        <v>18.361</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="68">
@@ -7989,10 +7989,10 @@
         <v>7.821</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>2.707</v>
       </c>
       <c r="W68" t="n">
-        <v>17.757</v>
+        <v>14.318</v>
       </c>
     </row>
     <row r="69">
@@ -8066,10 +8066,10 @@
         <v>7.946</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="W69" t="n">
-        <v>17.966</v>
+        <v>14.498</v>
       </c>
     </row>
     <row r="70">
@@ -8143,10 +8143,10 @@
         <v>8.978999999999999</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>3.108</v>
       </c>
       <c r="W70" t="n">
-        <v>20.057</v>
+        <v>16.223</v>
       </c>
     </row>
     <row r="71">
@@ -8220,10 +8220,10 @@
         <v>8.978999999999999</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>3.108</v>
       </c>
       <c r="W71" t="n">
-        <v>20.046</v>
+        <v>16.215</v>
       </c>
     </row>
     <row r="72">
@@ -8297,10 +8297,10 @@
         <v>8.833</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>3.057</v>
       </c>
       <c r="W72" t="n">
-        <v>19.815</v>
+        <v>16.014</v>
       </c>
     </row>
     <row r="73">
@@ -8374,10 +8374,10 @@
         <v>8.692</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>3.009</v>
       </c>
       <c r="W73" t="n">
-        <v>19.577</v>
+        <v>15.809</v>
       </c>
     </row>
     <row r="74">
@@ -8451,10 +8451,10 @@
         <v>9.353</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>3.237</v>
       </c>
       <c r="W74" t="n">
-        <v>20.644</v>
+        <v>16.736</v>
       </c>
     </row>
     <row r="75">
@@ -8528,10 +8528,10 @@
         <v>8.742000000000001</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>3.026</v>
       </c>
       <c r="W75" t="n">
-        <v>19.672</v>
+        <v>15.889</v>
       </c>
     </row>
     <row r="76">
@@ -8605,10 +8605,10 @@
         <v>8.592000000000001</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>2.974</v>
       </c>
       <c r="W76" t="n">
-        <v>19.424</v>
+        <v>15.675</v>
       </c>
     </row>
     <row r="77">
@@ -8682,10 +8682,10 @@
         <v>8.856</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>3.065</v>
       </c>
       <c r="W77" t="n">
-        <v>19.846</v>
+        <v>16.042</v>
       </c>
     </row>
     <row r="78">
@@ -8759,10 +8759,10 @@
         <v>8.759</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>3.032</v>
       </c>
       <c r="W78" t="n">
-        <v>19.699</v>
+        <v>15.912</v>
       </c>
     </row>
     <row r="79">
@@ -8836,10 +8836,10 @@
         <v>9.098000000000001</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>3.149</v>
       </c>
       <c r="W79" t="n">
-        <v>20.24</v>
+        <v>16.383</v>
       </c>
     </row>
     <row r="80">
@@ -8913,10 +8913,10 @@
         <v>8.993</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>3.113</v>
       </c>
       <c r="W80" t="n">
-        <v>20.073</v>
+        <v>16.238</v>
       </c>
     </row>
     <row r="81">
@@ -8990,10 +8990,10 @@
         <v>8.975</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>3.107</v>
       </c>
       <c r="W81" t="n">
-        <v>20.03</v>
+        <v>16.203</v>
       </c>
     </row>
     <row r="82">
@@ -9067,10 +9067,10 @@
         <v>8.542999999999999</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>2.957</v>
       </c>
       <c r="W82" t="n">
-        <v>19.337</v>
+        <v>15.601</v>
       </c>
     </row>
     <row r="83">
@@ -9144,10 +9144,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>3.074</v>
       </c>
       <c r="W83" t="n">
-        <v>19.888</v>
+        <v>16.078</v>
       </c>
     </row>
     <row r="84">
@@ -9221,10 +9221,10 @@
         <v>8.779</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>3.039</v>
       </c>
       <c r="W84" t="n">
-        <v>19.714</v>
+        <v>15.929</v>
       </c>
     </row>
     <row r="85">
@@ -9298,10 +9298,10 @@
         <v>9.227</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>3.194</v>
       </c>
       <c r="W85" t="n">
-        <v>20.442</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="86">
@@ -9375,10 +9375,10 @@
         <v>8.826000000000001</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>3.055</v>
       </c>
       <c r="W86" t="n">
-        <v>19.806</v>
+        <v>16.005</v>
       </c>
     </row>
     <row r="87">
@@ -9452,10 +9452,10 @@
         <v>7.986</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>2.764</v>
       </c>
       <c r="W87" t="n">
-        <v>18.053</v>
+        <v>14.568</v>
       </c>
     </row>
     <row r="88">
@@ -9529,10 +9529,10 @@
         <v>7.832</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>2.711</v>
       </c>
       <c r="W88" t="n">
-        <v>17.798</v>
+        <v>14.348</v>
       </c>
     </row>
     <row r="89">
@@ -9606,10 +9606,10 @@
         <v>7.808</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>2.703</v>
       </c>
       <c r="W89" t="n">
-        <v>17.761</v>
+        <v>14.316</v>
       </c>
     </row>
     <row r="90">
@@ -9683,10 +9683,10 @@
         <v>8.275</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>2.864</v>
       </c>
       <c r="W90" t="n">
-        <v>18.504</v>
+        <v>14.963</v>
       </c>
     </row>
     <row r="91">
@@ -9760,10 +9760,10 @@
         <v>7.945</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="W91" t="n">
-        <v>17.984</v>
+        <v>14.509</v>
       </c>
     </row>
     <row r="92">
@@ -9837,10 +9837,10 @@
         <v>8.045</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>2.785</v>
       </c>
       <c r="W92" t="n">
-        <v>18.149</v>
+        <v>14.652</v>
       </c>
     </row>
     <row r="93">
@@ -9914,10 +9914,10 @@
         <v>8.096</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>2.802</v>
       </c>
       <c r="W93" t="n">
-        <v>18.221</v>
+        <v>14.716</v>
       </c>
     </row>
     <row r="94">
@@ -9991,10 +9991,10 @@
         <v>7.406</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>2.563</v>
       </c>
       <c r="W94" t="n">
-        <v>17.108</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="95">
@@ -10068,10 +10068,10 @@
         <v>8.292</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="W95" t="n">
-        <v>18.532</v>
+        <v>14.988</v>
       </c>
     </row>
     <row r="96">
@@ -10145,10 +10145,10 @@
         <v>7.987</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>2.765</v>
       </c>
       <c r="W96" t="n">
-        <v>18.05</v>
+        <v>14.567</v>
       </c>
     </row>
     <row r="97">
@@ -10222,10 +10222,10 @@
         <v>8.06</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="W97" t="n">
-        <v>18.171</v>
+        <v>14.671</v>
       </c>
     </row>
     <row r="98">
@@ -10299,10 +10299,10 @@
         <v>7.82</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>2.707</v>
       </c>
       <c r="W98" t="n">
-        <v>17.779</v>
+        <v>14.332</v>
       </c>
     </row>
     <row r="99">
@@ -10376,10 +10376,10 @@
         <v>7.902</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>2.735</v>
       </c>
       <c r="W99" t="n">
-        <v>17.915</v>
+        <v>14.449</v>
       </c>
     </row>
     <row r="100">
@@ -10453,10 +10453,10 @@
         <v>7.849</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>2.717</v>
       </c>
       <c r="W100" t="n">
-        <v>17.827</v>
+        <v>14.373</v>
       </c>
     </row>
     <row r="101">
@@ -10530,10 +10530,10 @@
         <v>8.294</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>2.871</v>
       </c>
       <c r="W101" t="n">
-        <v>18.536</v>
+        <v>14.991</v>
       </c>
     </row>
     <row r="102">
@@ -10607,10 +10607,10 @@
         <v>8.382</v>
       </c>
       <c r="V102" t="n">
-        <v>0</v>
+        <v>2.901</v>
       </c>
       <c r="W102" t="n">
-        <v>18.678</v>
+        <v>15.114</v>
       </c>
     </row>
     <row r="103">
@@ -10684,10 +10684,10 @@
         <v>7.432</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>2.572</v>
       </c>
       <c r="W103" t="n">
-        <v>17.15</v>
+        <v>13.786</v>
       </c>
     </row>
     <row r="104">
@@ -10761,10 +10761,10 @@
         <v>8.224</v>
       </c>
       <c r="V104" t="n">
-        <v>0</v>
+        <v>2.847</v>
       </c>
       <c r="W104" t="n">
-        <v>18.542</v>
+        <v>14.971</v>
       </c>
     </row>
     <row r="105">
@@ -10838,10 +10838,10 @@
         <v>7.673</v>
       </c>
       <c r="V105" t="n">
-        <v>0</v>
+        <v>2.656</v>
       </c>
       <c r="W105" t="n">
-        <v>17.65</v>
+        <v>14.197</v>
       </c>
     </row>
     <row r="106">
@@ -10915,10 +10915,10 @@
         <v>8.423999999999999</v>
       </c>
       <c r="V106" t="n">
-        <v>0</v>
+        <v>2.916</v>
       </c>
       <c r="W106" t="n">
-        <v>18.868</v>
+        <v>15.253</v>
       </c>
     </row>
     <row r="107">
@@ -10992,10 +10992,10 @@
         <v>8.185</v>
       </c>
       <c r="V107" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="W107" t="n">
-        <v>18.487</v>
+        <v>14.921</v>
       </c>
     </row>
     <row r="108">
@@ -11069,10 +11069,10 @@
         <v>8.18</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>2.831</v>
       </c>
       <c r="W108" t="n">
-        <v>18.479</v>
+        <v>14.914</v>
       </c>
     </row>
     <row r="109">
@@ -11146,10 +11146,10 @@
         <v>8.007999999999999</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>2.772</v>
       </c>
       <c r="W109" t="n">
-        <v>18.206</v>
+        <v>14.676</v>
       </c>
     </row>
     <row r="110">
@@ -11223,10 +11223,10 @@
         <v>8.552</v>
       </c>
       <c r="V110" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="W110" t="n">
-        <v>19.066</v>
+        <v>15.427</v>
       </c>
     </row>
     <row r="111">
@@ -11300,10 +11300,10 @@
         <v>7.838</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>2.713</v>
       </c>
       <c r="W111" t="n">
-        <v>17.928</v>
+        <v>14.435</v>
       </c>
     </row>
     <row r="112">
@@ -11377,10 +11377,10 @@
         <v>8.108000000000001</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>2.806</v>
       </c>
       <c r="W112" t="n">
-        <v>18.363</v>
+        <v>14.813</v>
       </c>
     </row>
     <row r="113">
@@ -11454,10 +11454,10 @@
         <v>8.096</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>2.802</v>
       </c>
       <c r="W113" t="n">
-        <v>18.342</v>
+        <v>14.795</v>
       </c>
     </row>
     <row r="114">
@@ -11531,10 +11531,10 @@
         <v>8.369</v>
       </c>
       <c r="V114" t="n">
-        <v>0</v>
+        <v>2.897</v>
       </c>
       <c r="W114" t="n">
-        <v>18.781</v>
+        <v>15.177</v>
       </c>
     </row>
     <row r="115">
@@ -11608,10 +11608,10 @@
         <v>8.146000000000001</v>
       </c>
       <c r="V115" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="W115" t="n">
-        <v>18.427</v>
+        <v>14.868</v>
       </c>
     </row>
     <row r="116">
@@ -11685,10 +11685,10 @@
         <v>8.356</v>
       </c>
       <c r="V116" t="n">
-        <v>0</v>
+        <v>2.892</v>
       </c>
       <c r="W116" t="n">
-        <v>18.76</v>
+        <v>15.159</v>
       </c>
     </row>
     <row r="117">
@@ -11762,10 +11762,10 @@
         <v>7.52</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>2.603</v>
       </c>
       <c r="W117" t="n">
-        <v>17.404</v>
+        <v>13.983</v>
       </c>
     </row>
     <row r="118">
@@ -11839,10 +11839,10 @@
         <v>8.847</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>3.062</v>
       </c>
       <c r="W118" t="n">
-        <v>19.516</v>
+        <v>15.823</v>
       </c>
     </row>
     <row r="119">
@@ -11916,10 +11916,10 @@
         <v>8.467000000000001</v>
       </c>
       <c r="V119" t="n">
-        <v>0</v>
+        <v>2.931</v>
       </c>
       <c r="W119" t="n">
-        <v>18.933</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="120">
@@ -11993,10 +11993,10 @@
         <v>8.077</v>
       </c>
       <c r="V120" t="n">
-        <v>0</v>
+        <v>2.796</v>
       </c>
       <c r="W120" t="n">
-        <v>18.313</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="121">
@@ -12070,10 +12070,10 @@
         <v>8.907999999999999</v>
       </c>
       <c r="V121" t="n">
-        <v>0</v>
+        <v>3.083</v>
       </c>
       <c r="W121" t="n">
-        <v>20.028</v>
+        <v>16.179</v>
       </c>
     </row>
     <row r="122">
@@ -12147,10 +12147,10 @@
         <v>9.031000000000001</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>3.126</v>
       </c>
       <c r="W122" t="n">
-        <v>20.229</v>
+        <v>16.353</v>
       </c>
     </row>
     <row r="123">
@@ -12224,10 +12224,10 @@
         <v>8.762</v>
       </c>
       <c r="V123" t="n">
-        <v>0</v>
+        <v>3.033</v>
       </c>
       <c r="W123" t="n">
-        <v>19.792</v>
+        <v>15.974</v>
       </c>
     </row>
     <row r="124">
@@ -12301,10 +12301,10 @@
         <v>7.855</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>2.719</v>
       </c>
       <c r="W124" t="n">
-        <v>18.299</v>
+        <v>14.684</v>
       </c>
     </row>
     <row r="125">
@@ -12378,10 +12378,10 @@
         <v>8.499000000000001</v>
       </c>
       <c r="V125" t="n">
-        <v>0</v>
+        <v>2.942</v>
       </c>
       <c r="W125" t="n">
-        <v>19.361</v>
+        <v>15.601</v>
       </c>
     </row>
     <row r="126">
@@ -12455,10 +12455,10 @@
         <v>8.432</v>
       </c>
       <c r="V126" t="n">
-        <v>0</v>
+        <v>2.919</v>
       </c>
       <c r="W126" t="n">
-        <v>19.251</v>
+        <v>15.506</v>
       </c>
     </row>
     <row r="127">
@@ -12532,10 +12532,10 @@
         <v>8.737</v>
       </c>
       <c r="V127" t="n">
-        <v>0</v>
+        <v>3.024</v>
       </c>
       <c r="W127" t="n">
-        <v>19.751</v>
+        <v>15.939</v>
       </c>
     </row>
     <row r="128">
@@ -12609,10 +12609,10 @@
         <v>8.289</v>
       </c>
       <c r="V128" t="n">
-        <v>0</v>
+        <v>2.869</v>
       </c>
       <c r="W128" t="n">
-        <v>19.018</v>
+        <v>15.304</v>
       </c>
     </row>
     <row r="129">
@@ -12686,10 +12686,10 @@
         <v>8.319000000000001</v>
       </c>
       <c r="V129" t="n">
-        <v>0</v>
+        <v>2.879</v>
       </c>
       <c r="W129" t="n">
-        <v>19.066</v>
+        <v>15.346</v>
       </c>
     </row>
     <row r="130">
@@ -12763,10 +12763,10 @@
         <v>8.962999999999999</v>
       </c>
       <c r="V130" t="n">
-        <v>0</v>
+        <v>3.102</v>
       </c>
       <c r="W130" t="n">
-        <v>20.12</v>
+        <v>16.258</v>
       </c>
     </row>
     <row r="131">
@@ -12840,10 +12840,10 @@
         <v>8.762</v>
       </c>
       <c r="V131" t="n">
-        <v>0</v>
+        <v>3.033</v>
       </c>
       <c r="W131" t="n">
-        <v>19.792</v>
+        <v>15.974</v>
       </c>
     </row>
     <row r="132">
@@ -12917,10 +12917,10 @@
         <v>9.085000000000001</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>3.145</v>
       </c>
       <c r="W132" t="n">
-        <v>20.315</v>
+        <v>16.428</v>
       </c>
     </row>
     <row r="133">
@@ -12994,10 +12994,10 @@
         <v>9.002000000000001</v>
       </c>
       <c r="V133" t="n">
-        <v>0</v>
+        <v>3.116</v>
       </c>
       <c r="W133" t="n">
-        <v>20.181</v>
+        <v>16.312</v>
       </c>
     </row>
     <row r="134">
@@ -13071,10 +13071,10 @@
         <v>9.191000000000001</v>
       </c>
       <c r="V134" t="n">
-        <v>0</v>
+        <v>3.181</v>
       </c>
       <c r="W134" t="n">
-        <v>20.487</v>
+        <v>16.577</v>
       </c>
     </row>
     <row r="135">
@@ -13148,10 +13148,10 @@
         <v>8.987</v>
       </c>
       <c r="V135" t="n">
-        <v>0</v>
+        <v>3.111</v>
       </c>
       <c r="W135" t="n">
-        <v>20.156</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="136">
@@ -13225,10 +13225,10 @@
         <v>8.605</v>
       </c>
       <c r="V136" t="n">
-        <v>0</v>
+        <v>2.978</v>
       </c>
       <c r="W136" t="n">
-        <v>19.536</v>
+        <v>15.752</v>
       </c>
     </row>
     <row r="137">
@@ -13302,10 +13302,10 @@
         <v>8.263</v>
       </c>
       <c r="V137" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="W137" t="n">
-        <v>18.975</v>
+        <v>15.267</v>
       </c>
     </row>
     <row r="138">
@@ -13379,10 +13379,10 @@
         <v>6.572</v>
       </c>
       <c r="V138" t="n">
-        <v>0</v>
+        <v>2.275</v>
       </c>
       <c r="W138" t="n">
-        <v>15.397</v>
+        <v>12.342</v>
       </c>
     </row>
     <row r="139">
@@ -13456,10 +13456,10 @@
         <v>6.839</v>
       </c>
       <c r="V139" t="n">
-        <v>0</v>
+        <v>2.367</v>
       </c>
       <c r="W139" t="n">
-        <v>15.843</v>
+        <v>12.726</v>
       </c>
     </row>
     <row r="140">
@@ -13533,10 +13533,10 @@
         <v>7.521</v>
       </c>
       <c r="V140" t="n">
-        <v>0</v>
+        <v>2.603</v>
       </c>
       <c r="W140" t="n">
-        <v>16.971</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="141">
@@ -13610,10 +13610,10 @@
         <v>7.361</v>
       </c>
       <c r="V141" t="n">
-        <v>0</v>
+        <v>2.548</v>
       </c>
       <c r="W141" t="n">
-        <v>16.71</v>
+        <v>13.474</v>
       </c>
     </row>
     <row r="142">
@@ -13687,10 +13687,10 @@
         <v>7.416</v>
       </c>
       <c r="V142" t="n">
-        <v>0</v>
+        <v>2.567</v>
       </c>
       <c r="W142" t="n">
-        <v>16.799</v>
+        <v>13.551</v>
       </c>
     </row>
     <row r="143">
@@ -13764,10 +13764,10 @@
         <v>7.146</v>
       </c>
       <c r="V143" t="n">
-        <v>0</v>
+        <v>2.473</v>
       </c>
       <c r="W143" t="n">
-        <v>16.355</v>
+        <v>13.167</v>
       </c>
     </row>
     <row r="144">
@@ -13841,10 +13841,10 @@
         <v>6.827</v>
       </c>
       <c r="V144" t="n">
-        <v>0</v>
+        <v>2.363</v>
       </c>
       <c r="W144" t="n">
-        <v>15.824</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="145">
@@ -13918,10 +13918,10 @@
         <v>7.546</v>
       </c>
       <c r="V145" t="n">
-        <v>0</v>
+        <v>2.612</v>
       </c>
       <c r="W145" t="n">
-        <v>17.012</v>
+        <v>13.735</v>
       </c>
     </row>
     <row r="146">
@@ -13995,10 +13995,10 @@
         <v>6.609</v>
       </c>
       <c r="V146" t="n">
-        <v>0</v>
+        <v>2.288</v>
       </c>
       <c r="W146" t="n">
-        <v>15.463</v>
+        <v>12.398</v>
       </c>
     </row>
     <row r="147">
@@ -14072,10 +14072,10 @@
         <v>7.198</v>
       </c>
       <c r="V147" t="n">
-        <v>0</v>
+        <v>2.491</v>
       </c>
       <c r="W147" t="n">
-        <v>16.441</v>
+        <v>13.242</v>
       </c>
     </row>
     <row r="148">
@@ -14149,10 +14149,10 @@
         <v>6.958</v>
       </c>
       <c r="V148" t="n">
-        <v>0</v>
+        <v>2.408</v>
       </c>
       <c r="W148" t="n">
-        <v>16.041</v>
+        <v>12.897</v>
       </c>
     </row>
     <row r="149">
@@ -14226,10 +14226,10 @@
         <v>7.271</v>
       </c>
       <c r="V149" t="n">
-        <v>0</v>
+        <v>2.517</v>
       </c>
       <c r="W149" t="n">
-        <v>16.561</v>
+        <v>13.345</v>
       </c>
     </row>
     <row r="150">
@@ -14303,10 +14303,10 @@
         <v>6.861</v>
       </c>
       <c r="V150" t="n">
-        <v>0</v>
+        <v>2.375</v>
       </c>
       <c r="W150" t="n">
-        <v>15.878</v>
+        <v>12.757</v>
       </c>
     </row>
     <row r="151">
@@ -14380,10 +14380,10 @@
         <v>7.294</v>
       </c>
       <c r="V151" t="n">
-        <v>0</v>
+        <v>2.525</v>
       </c>
       <c r="W151" t="n">
-        <v>16.598</v>
+        <v>13.378</v>
       </c>
     </row>
     <row r="152">
@@ -14457,10 +14457,10 @@
         <v>6.693</v>
       </c>
       <c r="V152" t="n">
-        <v>0</v>
+        <v>2.317</v>
       </c>
       <c r="W152" t="n">
-        <v>15.6</v>
+        <v>12.517</v>
       </c>
     </row>
     <row r="153">
@@ -14534,10 +14534,10 @@
         <v>7.437</v>
       </c>
       <c r="V153" t="n">
-        <v>0</v>
+        <v>2.574</v>
       </c>
       <c r="W153" t="n">
-        <v>16.834</v>
+        <v>13.581</v>
       </c>
     </row>
     <row r="154">
@@ -14611,10 +14611,10 @@
         <v>7.489</v>
       </c>
       <c r="V154" t="n">
-        <v>0</v>
+        <v>2.592</v>
       </c>
       <c r="W154" t="n">
-        <v>16.921</v>
+        <v>13.656</v>
       </c>
     </row>
     <row r="155">
@@ -14688,10 +14688,10 @@
         <v>8.177</v>
       </c>
       <c r="V155" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="W155" t="n">
-        <v>18.431</v>
+        <v>14.882</v>
       </c>
     </row>
     <row r="156">
@@ -14765,10 +14765,10 @@
         <v>7.708</v>
       </c>
       <c r="V156" t="n">
-        <v>0</v>
+        <v>2.668</v>
       </c>
       <c r="W156" t="n">
-        <v>17.661</v>
+        <v>14.216</v>
       </c>
     </row>
     <row r="157">
@@ -14842,10 +14842,10 @@
         <v>8.372999999999999</v>
       </c>
       <c r="V157" t="n">
-        <v>0</v>
+        <v>2.898</v>
       </c>
       <c r="W157" t="n">
-        <v>18.752</v>
+        <v>15.159</v>
       </c>
     </row>
     <row r="158">
@@ -14919,10 +14919,10 @@
         <v>8.173999999999999</v>
       </c>
       <c r="V158" t="n">
-        <v>0</v>
+        <v>2.829</v>
       </c>
       <c r="W158" t="n">
-        <v>18.426</v>
+        <v>14.877</v>
       </c>
     </row>
     <row r="159">
@@ -14996,10 +14996,10 @@
         <v>8.012</v>
       </c>
       <c r="V159" t="n">
-        <v>0</v>
+        <v>2.773</v>
       </c>
       <c r="W159" t="n">
-        <v>18.162</v>
+        <v>14.649</v>
       </c>
     </row>
     <row r="160">
@@ -15073,10 +15073,10 @@
         <v>8.153</v>
       </c>
       <c r="V160" t="n">
-        <v>0</v>
+        <v>2.822</v>
       </c>
       <c r="W160" t="n">
-        <v>18.393</v>
+        <v>14.849</v>
       </c>
     </row>
     <row r="161">
@@ -15150,10 +15150,10 @@
         <v>8.130000000000001</v>
       </c>
       <c r="V161" t="n">
-        <v>0</v>
+        <v>2.814</v>
       </c>
       <c r="W161" t="n">
-        <v>18.356</v>
+        <v>14.816</v>
       </c>
     </row>
     <row r="162">
@@ -15227,10 +15227,10 @@
         <v>7.894</v>
       </c>
       <c r="V162" t="n">
-        <v>0</v>
+        <v>2.732</v>
       </c>
       <c r="W162" t="n">
-        <v>17.969</v>
+        <v>14.482</v>
       </c>
     </row>
     <row r="163">
@@ -15304,10 +15304,10 @@
         <v>8.323</v>
       </c>
       <c r="V163" t="n">
-        <v>0</v>
+        <v>2.881</v>
       </c>
       <c r="W163" t="n">
-        <v>18.67</v>
+        <v>15.089</v>
       </c>
     </row>
     <row r="164">
@@ -15381,10 +15381,10 @@
         <v>8.058999999999999</v>
       </c>
       <c r="V164" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="W164" t="n">
-        <v>18.238</v>
+        <v>14.715</v>
       </c>
     </row>
     <row r="165">
@@ -15458,10 +15458,10 @@
         <v>8.222</v>
       </c>
       <c r="V165" t="n">
-        <v>0</v>
+        <v>2.846</v>
       </c>
       <c r="W165" t="n">
-        <v>18.503</v>
+        <v>14.944</v>
       </c>
     </row>
     <row r="166">
@@ -15535,10 +15535,10 @@
         <v>8.262</v>
       </c>
       <c r="V166" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="W166" t="n">
-        <v>18.57</v>
+        <v>15.002</v>
       </c>
     </row>
     <row r="167">
@@ -15612,10 +15612,10 @@
         <v>8.212999999999999</v>
       </c>
       <c r="V167" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="W167" t="n">
-        <v>18.489</v>
+        <v>14.932</v>
       </c>
     </row>
     <row r="168">
@@ -15689,10 +15689,10 @@
         <v>8.179</v>
       </c>
       <c r="V168" t="n">
-        <v>0</v>
+        <v>2.831</v>
       </c>
       <c r="W168" t="n">
-        <v>18.434</v>
+        <v>14.884</v>
       </c>
     </row>
     <row r="169">
@@ -15766,10 +15766,10 @@
         <v>8.148</v>
       </c>
       <c r="V169" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="W169" t="n">
-        <v>18.386</v>
+        <v>14.842</v>
       </c>
     </row>
     <row r="170">
@@ -15843,10 +15843,10 @@
         <v>7.971</v>
       </c>
       <c r="V170" t="n">
-        <v>0</v>
+        <v>2.759</v>
       </c>
       <c r="W170" t="n">
-        <v>18.094</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="171">
@@ -15920,10 +15920,10 @@
         <v>8.301</v>
       </c>
       <c r="V171" t="n">
-        <v>0</v>
+        <v>2.873</v>
       </c>
       <c r="W171" t="n">
-        <v>18.636</v>
+        <v>15.059</v>
       </c>
     </row>
     <row r="172">
@@ -15997,10 +15997,10 @@
         <v>7.984</v>
       </c>
       <c r="V172" t="n">
-        <v>0</v>
+        <v>2.764</v>
       </c>
       <c r="W172" t="n">
-        <v>18.087</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="173">
@@ -16074,10 +16074,10 @@
         <v>8.025</v>
       </c>
       <c r="V173" t="n">
-        <v>0</v>
+        <v>2.778</v>
       </c>
       <c r="W173" t="n">
-        <v>18.144</v>
+        <v>14.641</v>
       </c>
     </row>
     <row r="174">
@@ -16151,10 +16151,10 @@
         <v>7.877</v>
       </c>
       <c r="V174" t="n">
-        <v>0</v>
+        <v>2.727</v>
       </c>
       <c r="W174" t="n">
-        <v>17.909</v>
+        <v>14.437</v>
       </c>
     </row>
     <row r="175">
@@ -16228,10 +16228,10 @@
         <v>8.212999999999999</v>
       </c>
       <c r="V175" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="W175" t="n">
-        <v>18.456</v>
+        <v>14.911</v>
       </c>
     </row>
     <row r="176">
@@ -16305,10 +16305,10 @@
         <v>8.099</v>
       </c>
       <c r="V176" t="n">
-        <v>0</v>
+        <v>2.803</v>
       </c>
       <c r="W176" t="n">
-        <v>18.273</v>
+        <v>14.751</v>
       </c>
     </row>
     <row r="177">
@@ -16382,10 +16382,10 @@
         <v>8.125999999999999</v>
       </c>
       <c r="V177" t="n">
-        <v>0</v>
+        <v>2.813</v>
       </c>
       <c r="W177" t="n">
-        <v>18.314</v>
+        <v>14.788</v>
       </c>
     </row>
     <row r="178">
@@ -16459,10 +16459,10 @@
         <v>8.050000000000001</v>
       </c>
       <c r="V178" t="n">
-        <v>0</v>
+        <v>2.786</v>
       </c>
       <c r="W178" t="n">
-        <v>18.192</v>
+        <v>14.681</v>
       </c>
     </row>
     <row r="179">
@@ -16536,10 +16536,10 @@
         <v>8.128</v>
       </c>
       <c r="V179" t="n">
-        <v>0</v>
+        <v>2.813</v>
       </c>
       <c r="W179" t="n">
-        <v>18.319</v>
+        <v>14.792</v>
       </c>
     </row>
     <row r="180">
@@ -16613,10 +16613,10 @@
         <v>7.971</v>
       </c>
       <c r="V180" t="n">
-        <v>0</v>
+        <v>2.759</v>
       </c>
       <c r="W180" t="n">
-        <v>18.062</v>
+        <v>14.569</v>
       </c>
     </row>
     <row r="181">
@@ -16690,10 +16690,10 @@
         <v>7.985</v>
       </c>
       <c r="V181" t="n">
-        <v>0</v>
+        <v>2.764</v>
       </c>
       <c r="W181" t="n">
-        <v>18.085</v>
+        <v>14.589</v>
       </c>
     </row>
     <row r="182">
@@ -16767,10 +16767,10 @@
         <v>8.227</v>
       </c>
       <c r="V182" t="n">
-        <v>0</v>
+        <v>2.848</v>
       </c>
       <c r="W182" t="n">
-        <v>18.478</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="183">
@@ -16844,10 +16844,10 @@
         <v>7.748</v>
       </c>
       <c r="V183" t="n">
-        <v>0</v>
+        <v>2.682</v>
       </c>
       <c r="W183" t="n">
-        <v>17.7</v>
+        <v>14.255</v>
       </c>
     </row>
     <row r="184">
@@ -16921,10 +16921,10 @@
         <v>7.566</v>
       </c>
       <c r="V184" t="n">
-        <v>0</v>
+        <v>2.619</v>
       </c>
       <c r="W184" t="n">
-        <v>17.399</v>
+        <v>13.995</v>
       </c>
     </row>
     <row r="185">
@@ -16998,10 +16998,10 @@
         <v>7.806</v>
       </c>
       <c r="V185" t="n">
-        <v>0</v>
+        <v>2.702</v>
       </c>
       <c r="W185" t="n">
-        <v>17.794</v>
+        <v>14.337</v>
       </c>
     </row>
     <row r="186">
@@ -17075,10 +17075,10 @@
         <v>7.977</v>
       </c>
       <c r="V186" t="n">
-        <v>0</v>
+        <v>2.761</v>
       </c>
       <c r="W186" t="n">
-        <v>18.074</v>
+        <v>14.579</v>
       </c>
     </row>
     <row r="187">
@@ -17152,10 +17152,10 @@
         <v>8.159000000000001</v>
       </c>
       <c r="V187" t="n">
-        <v>0</v>
+        <v>2.824</v>
       </c>
       <c r="W187" t="n">
-        <v>18.367</v>
+        <v>14.834</v>
       </c>
     </row>
     <row r="188">
@@ -17229,10 +17229,10 @@
         <v>7.373</v>
       </c>
       <c r="V188" t="n">
-        <v>0</v>
+        <v>2.552</v>
       </c>
       <c r="W188" t="n">
-        <v>17.082</v>
+        <v>13.721</v>
       </c>
     </row>
     <row r="189">
@@ -17306,10 +17306,10 @@
         <v>8.327</v>
       </c>
       <c r="V189" t="n">
-        <v>0</v>
+        <v>2.882</v>
       </c>
       <c r="W189" t="n">
-        <v>18.839</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="190">
@@ -17383,10 +17383,10 @@
         <v>8.269</v>
       </c>
       <c r="V190" t="n">
-        <v>0</v>
+        <v>2.862</v>
       </c>
       <c r="W190" t="n">
-        <v>18.735</v>
+        <v>15.112</v>
       </c>
     </row>
     <row r="191">
@@ -17460,10 +17460,10 @@
         <v>8.356</v>
       </c>
       <c r="V191" t="n">
-        <v>0</v>
+        <v>2.892</v>
       </c>
       <c r="W191" t="n">
-        <v>18.884</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="192">
@@ -17537,10 +17537,10 @@
         <v>8.000999999999999</v>
       </c>
       <c r="V192" t="n">
-        <v>0</v>
+        <v>2.769</v>
       </c>
       <c r="W192" t="n">
-        <v>18.29</v>
+        <v>14.729</v>
       </c>
     </row>
     <row r="193">
@@ -17614,10 +17614,10 @@
         <v>8.49</v>
       </c>
       <c r="V193" t="n">
-        <v>0</v>
+        <v>2.939</v>
       </c>
       <c r="W193" t="n">
-        <v>19.096</v>
+        <v>15.425</v>
       </c>
     </row>
     <row r="194">
@@ -17691,10 +17691,10 @@
         <v>8.183</v>
       </c>
       <c r="V194" t="n">
-        <v>0</v>
+        <v>2.832</v>
       </c>
       <c r="W194" t="n">
-        <v>18.606</v>
+        <v>14.998</v>
       </c>
     </row>
     <row r="195">
@@ -17768,10 +17768,10 @@
         <v>7.762</v>
       </c>
       <c r="V195" t="n">
-        <v>0</v>
+        <v>2.687</v>
       </c>
       <c r="W195" t="n">
-        <v>17.911</v>
+        <v>14.398</v>
       </c>
     </row>
     <row r="196">
@@ -17845,10 +17845,10 @@
         <v>8.202999999999999</v>
       </c>
       <c r="V196" t="n">
-        <v>0</v>
+        <v>2.839</v>
       </c>
       <c r="W196" t="n">
-        <v>18.626</v>
+        <v>15.018</v>
       </c>
     </row>
     <row r="197">
@@ -17922,10 +17922,10 @@
         <v>8.17</v>
       </c>
       <c r="V197" t="n">
-        <v>0</v>
+        <v>2.828</v>
       </c>
       <c r="W197" t="n">
-        <v>18.584</v>
+        <v>14.979</v>
       </c>
     </row>
     <row r="198">
@@ -17999,10 +17999,10 @@
         <v>7.638</v>
       </c>
       <c r="V198" t="n">
-        <v>0</v>
+        <v>2.644</v>
       </c>
       <c r="W198" t="n">
-        <v>17.709</v>
+        <v>14.223</v>
       </c>
     </row>
     <row r="199">
@@ -18076,10 +18076,10 @@
         <v>7.822</v>
       </c>
       <c r="V199" t="n">
-        <v>0</v>
+        <v>2.707</v>
       </c>
       <c r="W199" t="n">
-        <v>18.014</v>
+        <v>14.486</v>
       </c>
     </row>
     <row r="200">
@@ -18153,10 +18153,10 @@
         <v>7.996</v>
       </c>
       <c r="V200" t="n">
-        <v>0</v>
+        <v>2.768</v>
       </c>
       <c r="W200" t="n">
-        <v>18.301</v>
+        <v>14.734</v>
       </c>
     </row>
     <row r="201">
@@ -18230,10 +18230,10 @@
         <v>7.706</v>
       </c>
       <c r="V201" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="W201" t="n">
-        <v>17.818</v>
+        <v>14.318</v>
       </c>
     </row>
     <row r="202">
@@ -18307,10 +18307,10 @@
         <v>8.108000000000001</v>
       </c>
       <c r="V202" t="n">
-        <v>0</v>
+        <v>2.806</v>
       </c>
       <c r="W202" t="n">
-        <v>18.483</v>
+        <v>14.892</v>
       </c>
     </row>
     <row r="203">
@@ -18384,10 +18384,10 @@
         <v>8.458</v>
       </c>
       <c r="V203" t="n">
-        <v>0</v>
+        <v>2.928</v>
       </c>
       <c r="W203" t="n">
-        <v>19.045</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="204">
@@ -18461,10 +18461,10 @@
         <v>8.183</v>
       </c>
       <c r="V204" t="n">
-        <v>0</v>
+        <v>2.832</v>
       </c>
       <c r="W204" t="n">
-        <v>18.604</v>
+        <v>14.997</v>
       </c>
     </row>
     <row r="205">
@@ -18538,10 +18538,10 @@
         <v>7.977</v>
       </c>
       <c r="V205" t="n">
-        <v>0</v>
+        <v>2.761</v>
       </c>
       <c r="W205" t="n">
-        <v>18.269</v>
+        <v>14.707</v>
       </c>
     </row>
     <row r="206">
@@ -18615,10 +18615,10 @@
         <v>8.515000000000001</v>
       </c>
       <c r="V206" t="n">
-        <v>0</v>
+        <v>2.947</v>
       </c>
       <c r="W206" t="n">
-        <v>18.979</v>
+        <v>15.357</v>
       </c>
     </row>
     <row r="207">
@@ -18692,10 +18692,10 @@
         <v>8.497999999999999</v>
       </c>
       <c r="V207" t="n">
-        <v>0</v>
+        <v>2.941</v>
       </c>
       <c r="W207" t="n">
-        <v>18.929</v>
+        <v>15.318</v>
       </c>
     </row>
     <row r="208">
@@ -18769,10 +18769,10 @@
         <v>8.446</v>
       </c>
       <c r="V208" t="n">
-        <v>0</v>
+        <v>2.923</v>
       </c>
       <c r="W208" t="n">
-        <v>18.835</v>
+        <v>15.239</v>
       </c>
     </row>
     <row r="209">
@@ -18846,10 +18846,10 @@
         <v>8.302</v>
       </c>
       <c r="V209" t="n">
-        <v>0</v>
+        <v>2.874</v>
       </c>
       <c r="W209" t="n">
-        <v>18.631</v>
+        <v>15.056</v>
       </c>
     </row>
     <row r="210">
@@ -18923,10 +18923,10 @@
         <v>8.595000000000001</v>
       </c>
       <c r="V210" t="n">
-        <v>0</v>
+        <v>2.975</v>
       </c>
       <c r="W210" t="n">
-        <v>19.069</v>
+        <v>15.444</v>
       </c>
     </row>
     <row r="211">
@@ -19000,10 +19000,10 @@
         <v>8.566000000000001</v>
       </c>
       <c r="V211" t="n">
-        <v>0</v>
+        <v>2.965</v>
       </c>
       <c r="W211" t="n">
-        <v>19.015</v>
+        <v>15.398</v>
       </c>
     </row>
     <row r="212">
@@ -19077,10 +19077,10 @@
         <v>8.616</v>
       </c>
       <c r="V212" t="n">
-        <v>0</v>
+        <v>2.982</v>
       </c>
       <c r="W212" t="n">
-        <v>19.144</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="213">
@@ -19154,10 +19154,10 @@
         <v>8.446999999999999</v>
       </c>
       <c r="V213" t="n">
-        <v>0</v>
+        <v>2.924</v>
       </c>
       <c r="W213" t="n">
-        <v>18.856</v>
+        <v>15.253</v>
       </c>
     </row>
     <row r="214">
@@ -19231,10 +19231,10 @@
         <v>8.353999999999999</v>
       </c>
       <c r="V214" t="n">
-        <v>0</v>
+        <v>2.892</v>
       </c>
       <c r="W214" t="n">
-        <v>18.69</v>
+        <v>15.112</v>
       </c>
     </row>
     <row r="215">
@@ -19308,10 +19308,10 @@
         <v>8.608000000000001</v>
       </c>
       <c r="V215" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="W215" t="n">
-        <v>19.12</v>
+        <v>15.481</v>
       </c>
     </row>
     <row r="216">
@@ -19385,10 +19385,10 @@
         <v>8.677</v>
       </c>
       <c r="V216" t="n">
-        <v>0</v>
+        <v>3.003</v>
       </c>
       <c r="W216" t="n">
-        <v>19.207</v>
+        <v>15.562</v>
       </c>
     </row>
     <row r="217">
@@ -19462,10 +19462,10 @@
         <v>8.148</v>
       </c>
       <c r="V217" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="W217" t="n">
-        <v>18.382</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="218">
@@ -19539,10 +19539,10 @@
         <v>8.837999999999999</v>
       </c>
       <c r="V218" t="n">
-        <v>0</v>
+        <v>3.059</v>
       </c>
       <c r="W218" t="n">
-        <v>19.472</v>
+        <v>15.791</v>
       </c>
     </row>
     <row r="219">
@@ -19616,10 +19616,10 @@
         <v>8.43</v>
       </c>
       <c r="V219" t="n">
-        <v>0</v>
+        <v>2.918</v>
       </c>
       <c r="W219" t="n">
-        <v>18.834</v>
+        <v>15.233</v>
       </c>
     </row>
     <row r="220">
@@ -19693,10 +19693,10 @@
         <v>8.333</v>
       </c>
       <c r="V220" t="n">
-        <v>0</v>
+        <v>2.884</v>
       </c>
       <c r="W220" t="n">
-        <v>18.684</v>
+        <v>15.101</v>
       </c>
     </row>
     <row r="221">
@@ -19770,10 +19770,10 @@
         <v>8.554</v>
       </c>
       <c r="V221" t="n">
-        <v>0</v>
+        <v>2.961</v>
       </c>
       <c r="W221" t="n">
-        <v>19.024</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="222">
@@ -19847,10 +19847,10 @@
         <v>8.295</v>
       </c>
       <c r="V222" t="n">
-        <v>0</v>
+        <v>2.871</v>
       </c>
       <c r="W222" t="n">
-        <v>18.609</v>
+        <v>15.039</v>
       </c>
     </row>
     <row r="223">
@@ -19924,10 +19924,10 @@
         <v>8.202999999999999</v>
       </c>
       <c r="V223" t="n">
-        <v>0</v>
+        <v>2.839</v>
       </c>
       <c r="W223" t="n">
-        <v>18.514</v>
+        <v>14.945</v>
       </c>
     </row>
     <row r="224">
@@ -20001,10 +20001,10 @@
         <v>7.675</v>
       </c>
       <c r="V224" t="n">
-        <v>0</v>
+        <v>2.657</v>
       </c>
       <c r="W224" t="n">
-        <v>17.671</v>
+        <v>14.211</v>
       </c>
     </row>
     <row r="225">
@@ -20078,10 +20078,10 @@
         <v>7.984</v>
       </c>
       <c r="V225" t="n">
-        <v>0</v>
+        <v>2.764</v>
       </c>
       <c r="W225" t="n">
-        <v>18.167</v>
+        <v>14.642</v>
       </c>
     </row>
     <row r="226">
@@ -20155,10 +20155,10 @@
         <v>8.179</v>
       </c>
       <c r="V226" t="n">
-        <v>0</v>
+        <v>2.831</v>
       </c>
       <c r="W226" t="n">
-        <v>18.495</v>
+        <v>14.924</v>
       </c>
     </row>
     <row r="227">
@@ -20232,10 +20232,10 @@
         <v>7.985</v>
       </c>
       <c r="V227" t="n">
-        <v>0</v>
+        <v>2.764</v>
       </c>
       <c r="W227" t="n">
-        <v>18.165</v>
+        <v>14.641</v>
       </c>
     </row>
     <row r="228">
@@ -20309,10 +20309,10 @@
         <v>7.907</v>
       </c>
       <c r="V228" t="n">
-        <v>0</v>
+        <v>2.737</v>
       </c>
       <c r="W228" t="n">
-        <v>18.054</v>
+        <v>14.542</v>
       </c>
     </row>
     <row r="229">
@@ -20386,10 +20386,10 @@
         <v>7.887</v>
       </c>
       <c r="V229" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="W229" t="n">
-        <v>18.015</v>
+        <v>14.509</v>
       </c>
     </row>
     <row r="230">
@@ -20463,10 +20463,10 @@
         <v>8.137</v>
       </c>
       <c r="V230" t="n">
-        <v>0</v>
+        <v>2.817</v>
       </c>
       <c r="W230" t="n">
-        <v>18.42</v>
+        <v>14.861</v>
       </c>
     </row>
     <row r="231">
@@ -20540,10 +20540,10 @@
         <v>8.292999999999999</v>
       </c>
       <c r="V231" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="W231" t="n">
-        <v>18.655</v>
+        <v>15.068</v>
       </c>
     </row>
     <row r="232">
@@ -20617,10 +20617,10 @@
         <v>8.284000000000001</v>
       </c>
       <c r="V232" t="n">
-        <v>0</v>
+        <v>2.867</v>
       </c>
       <c r="W232" t="n">
-        <v>18.637</v>
+        <v>15.053</v>
       </c>
     </row>
     <row r="233">
@@ -20694,10 +20694,10 @@
         <v>8.401</v>
       </c>
       <c r="V233" t="n">
-        <v>0</v>
+        <v>2.908</v>
       </c>
       <c r="W233" t="n">
-        <v>18.845</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="234">
@@ -20771,10 +20771,10 @@
         <v>7.82</v>
       </c>
       <c r="V234" t="n">
-        <v>0</v>
+        <v>2.707</v>
       </c>
       <c r="W234" t="n">
-        <v>17.897</v>
+        <v>14.409</v>
       </c>
     </row>
     <row r="235">
@@ -20848,10 +20848,10 @@
         <v>8.269</v>
       </c>
       <c r="V235" t="n">
-        <v>0</v>
+        <v>2.862</v>
       </c>
       <c r="W235" t="n">
-        <v>18.618</v>
+        <v>15.036</v>
       </c>
     </row>
     <row r="236">
@@ -20925,10 +20925,10 @@
         <v>7.864</v>
       </c>
       <c r="V236" t="n">
-        <v>0</v>
+        <v>2.722</v>
       </c>
       <c r="W236" t="n">
-        <v>17.98</v>
+        <v>14.478</v>
       </c>
     </row>
     <row r="237">
@@ -21002,10 +21002,10 @@
         <v>8.029999999999999</v>
       </c>
       <c r="V237" t="n">
-        <v>0</v>
+        <v>2.779</v>
       </c>
       <c r="W237" t="n">
-        <v>18.241</v>
+        <v>14.707</v>
       </c>
     </row>
     <row r="238">
@@ -21079,10 +21079,10 @@
         <v>8.333</v>
       </c>
       <c r="V238" t="n">
-        <v>0</v>
+        <v>2.884</v>
       </c>
       <c r="W238" t="n">
-        <v>18.732</v>
+        <v>15.133</v>
       </c>
     </row>
     <row r="239">
@@ -21156,10 +21156,10 @@
         <v>8.154999999999999</v>
       </c>
       <c r="V239" t="n">
-        <v>0</v>
+        <v>2.823</v>
       </c>
       <c r="W239" t="n">
-        <v>18.438</v>
+        <v>14.879</v>
       </c>
     </row>
     <row r="240">
@@ -21233,10 +21233,10 @@
         <v>7.878</v>
       </c>
       <c r="V240" t="n">
-        <v>0</v>
+        <v>2.727</v>
       </c>
       <c r="W240" t="n">
-        <v>18.055</v>
+        <v>14.532</v>
       </c>
     </row>
     <row r="241">
@@ -21310,10 +21310,10 @@
         <v>8.316000000000001</v>
       </c>
       <c r="V241" t="n">
-        <v>0</v>
+        <v>2.878</v>
       </c>
       <c r="W241" t="n">
-        <v>18.771</v>
+        <v>15.152</v>
       </c>
     </row>
     <row r="242">
@@ -21387,10 +21387,10 @@
         <v>8.118</v>
       </c>
       <c r="V242" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="W242" t="n">
-        <v>18.448</v>
+        <v>14.872</v>
       </c>
     </row>
     <row r="243">
@@ -21464,10 +21464,10 @@
         <v>8.417999999999999</v>
       </c>
       <c r="V243" t="n">
-        <v>0</v>
+        <v>2.914</v>
       </c>
       <c r="W243" t="n">
-        <v>18.939</v>
+        <v>15.297</v>
       </c>
     </row>
     <row r="244">
@@ -21541,10 +21541,10 @@
         <v>7.912</v>
       </c>
       <c r="V244" t="n">
-        <v>0</v>
+        <v>2.739</v>
       </c>
       <c r="W244" t="n">
-        <v>18.107</v>
+        <v>14.578</v>
       </c>
     </row>
     <row r="245">
@@ -21618,10 +21618,10 @@
         <v>7.485</v>
       </c>
       <c r="V245" t="n">
-        <v>0</v>
+        <v>2.591</v>
       </c>
       <c r="W245" t="n">
-        <v>17.402</v>
+        <v>13.969</v>
       </c>
     </row>
     <row r="246">
@@ -21695,10 +21695,10 @@
         <v>7.563</v>
       </c>
       <c r="V246" t="n">
-        <v>0</v>
+        <v>2.618</v>
       </c>
       <c r="W246" t="n">
-        <v>17.534</v>
+        <v>14.083</v>
       </c>
     </row>
     <row r="247">
@@ -21772,10 +21772,10 @@
         <v>8.114000000000001</v>
       </c>
       <c r="V247" t="n">
-        <v>0</v>
+        <v>2.809</v>
       </c>
       <c r="W247" t="n">
-        <v>18.443</v>
+        <v>14.868</v>
       </c>
     </row>
     <row r="248">
@@ -21849,10 +21849,10 @@
         <v>8.109</v>
       </c>
       <c r="V248" t="n">
-        <v>0</v>
+        <v>2.807</v>
       </c>
       <c r="W248" t="n">
-        <v>18.433</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="249">
@@ -21926,10 +21926,10 @@
         <v>8.193</v>
       </c>
       <c r="V249" t="n">
-        <v>0</v>
+        <v>2.836</v>
       </c>
       <c r="W249" t="n">
-        <v>18.573</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="250">
@@ -22003,10 +22003,10 @@
         <v>8.058</v>
       </c>
       <c r="V250" t="n">
-        <v>0</v>
+        <v>2.789</v>
       </c>
       <c r="W250" t="n">
-        <v>18.35</v>
+        <v>14.788</v>
       </c>
     </row>
     <row r="251">
@@ -22080,10 +22080,10 @@
         <v>8.07</v>
       </c>
       <c r="V251" t="n">
-        <v>0</v>
+        <v>2.793</v>
       </c>
       <c r="W251" t="n">
-        <v>18.371</v>
+        <v>14.805</v>
       </c>
     </row>
     <row r="252">
@@ -22157,10 +22157,10 @@
         <v>8.265000000000001</v>
       </c>
       <c r="V252" t="n">
-        <v>0</v>
+        <v>2.861</v>
       </c>
       <c r="W252" t="n">
-        <v>18.687</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="253">
@@ -22234,10 +22234,10 @@
         <v>8.103999999999999</v>
       </c>
       <c r="V253" t="n">
-        <v>0</v>
+        <v>2.805</v>
       </c>
       <c r="W253" t="n">
-        <v>18.426</v>
+        <v>14.853</v>
       </c>
     </row>
     <row r="254">
@@ -22311,10 +22311,10 @@
         <v>8.628</v>
       </c>
       <c r="V254" t="n">
-        <v>0</v>
+        <v>2.986</v>
       </c>
       <c r="W254" t="n">
-        <v>19.277</v>
+        <v>15.591</v>
       </c>
     </row>
     <row r="255">
@@ -22388,10 +22388,10 @@
         <v>7.566</v>
       </c>
       <c r="V255" t="n">
-        <v>0</v>
+        <v>2.619</v>
       </c>
       <c r="W255" t="n">
-        <v>17.533</v>
+        <v>14.083</v>
       </c>
     </row>
     <row r="256">
@@ -22465,10 +22465,10 @@
         <v>8.526</v>
       </c>
       <c r="V256" t="n">
-        <v>0</v>
+        <v>2.951</v>
       </c>
       <c r="W256" t="n">
-        <v>19.113</v>
+        <v>15.448</v>
       </c>
     </row>
     <row r="257">
@@ -22542,10 +22542,10 @@
         <v>8.747999999999999</v>
       </c>
       <c r="V257" t="n">
-        <v>0</v>
+        <v>3.028</v>
       </c>
       <c r="W257" t="n">
-        <v>19.343</v>
+        <v>15.676</v>
       </c>
     </row>
     <row r="258">
@@ -22619,10 +22619,10 @@
         <v>8.691000000000001</v>
       </c>
       <c r="V258" t="n">
-        <v>0</v>
+        <v>3.008</v>
       </c>
       <c r="W258" t="n">
-        <v>19.263</v>
+        <v>15.604</v>
       </c>
     </row>
     <row r="259">
@@ -22696,10 +22696,10 @@
         <v>7.76</v>
       </c>
       <c r="V259" t="n">
-        <v>0</v>
+        <v>2.686</v>
       </c>
       <c r="W259" t="n">
-        <v>17.792</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="260">
@@ -22773,10 +22773,10 @@
         <v>7.488</v>
       </c>
       <c r="V260" t="n">
-        <v>0</v>
+        <v>2.592</v>
       </c>
       <c r="W260" t="n">
-        <v>17.356</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="261">
@@ -22850,10 +22850,10 @@
         <v>8.301</v>
       </c>
       <c r="V261" t="n">
-        <v>0</v>
+        <v>2.873</v>
       </c>
       <c r="W261" t="n">
-        <v>18.662</v>
+        <v>15.076</v>
       </c>
     </row>
     <row r="262">
@@ -22927,10 +22927,10 @@
         <v>9.243</v>
       </c>
       <c r="V262" t="n">
-        <v>0.187</v>
+        <v>3.322</v>
       </c>
       <c r="W262" t="n">
-        <v>20.079</v>
+        <v>16.328</v>
       </c>
     </row>
     <row r="263">
@@ -23004,10 +23004,10 @@
         <v>8.412000000000001</v>
       </c>
       <c r="V263" t="n">
-        <v>0</v>
+        <v>2.912</v>
       </c>
       <c r="W263" t="n">
-        <v>18.83</v>
+        <v>15.224</v>
       </c>
     </row>
     <row r="264">
@@ -23081,10 +23081,10 @@
         <v>8.179</v>
       </c>
       <c r="V264" t="n">
-        <v>0</v>
+        <v>2.831</v>
       </c>
       <c r="W264" t="n">
-        <v>18.477</v>
+        <v>14.913</v>
       </c>
     </row>
     <row r="265">
@@ -23158,10 +23158,10 @@
         <v>8.843999999999999</v>
       </c>
       <c r="V265" t="n">
-        <v>0.032</v>
+        <v>3.082</v>
       </c>
       <c r="W265" t="n">
-        <v>19.469</v>
+        <v>15.791</v>
       </c>
     </row>
     <row r="266">
@@ -23235,10 +23235,10 @@
         <v>8.951000000000001</v>
       </c>
       <c r="V266" t="n">
-        <v>0.059</v>
+        <v>3.137</v>
       </c>
       <c r="W266" t="n">
-        <v>19.637</v>
+        <v>15.938</v>
       </c>
     </row>
     <row r="267">
@@ -23312,10 +23312,10 @@
         <v>8.718999999999999</v>
       </c>
       <c r="V267" t="n">
-        <v>0</v>
+        <v>3.018</v>
       </c>
       <c r="W267" t="n">
-        <v>19.299</v>
+        <v>15.637</v>
       </c>
     </row>
     <row r="268">
@@ -23389,10 +23389,10 @@
         <v>8.616</v>
       </c>
       <c r="V268" t="n">
-        <v>0</v>
+        <v>2.982</v>
       </c>
       <c r="W268" t="n">
-        <v>19.143</v>
+        <v>15.499</v>
       </c>
     </row>
     <row r="269">
@@ -23466,10 +23466,10 @@
         <v>8.353999999999999</v>
       </c>
       <c r="V269" t="n">
-        <v>0</v>
+        <v>2.892</v>
       </c>
       <c r="W269" t="n">
-        <v>18.738</v>
+        <v>15.144</v>
       </c>
     </row>
     <row r="270">
@@ -23543,10 +23543,10 @@
         <v>8.816000000000001</v>
       </c>
       <c r="V270" t="n">
-        <v>0</v>
+        <v>3.052</v>
       </c>
       <c r="W270" t="n">
-        <v>19.448</v>
+        <v>15.768</v>
       </c>
     </row>
     <row r="271">
@@ -23620,10 +23620,10 @@
         <v>7.693</v>
       </c>
       <c r="V271" t="n">
-        <v>0</v>
+        <v>2.663</v>
       </c>
       <c r="W271" t="n">
-        <v>17.685</v>
+        <v>14.226</v>
       </c>
     </row>
     <row r="272">
@@ -23697,10 +23697,10 @@
         <v>8.609</v>
       </c>
       <c r="V272" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="W272" t="n">
-        <v>19.133</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="273">
@@ -23774,10 +23774,10 @@
         <v>8.394</v>
       </c>
       <c r="V273" t="n">
-        <v>0</v>
+        <v>2.905</v>
       </c>
       <c r="W273" t="n">
-        <v>18.807</v>
+        <v>15.203</v>
       </c>
     </row>
     <row r="274">
@@ -23851,10 +23851,10 @@
         <v>8.166</v>
       </c>
       <c r="V274" t="n">
-        <v>0</v>
+        <v>2.827</v>
       </c>
       <c r="W274" t="n">
-        <v>18.416</v>
+        <v>14.868</v>
       </c>
     </row>
     <row r="275">
@@ -23928,10 +23928,10 @@
         <v>8.141</v>
       </c>
       <c r="V275" t="n">
-        <v>0</v>
+        <v>2.818</v>
       </c>
       <c r="W275" t="n">
-        <v>18.376</v>
+        <v>14.833</v>
       </c>
     </row>
     <row r="276">
@@ -24005,10 +24005,10 @@
         <v>8.929</v>
       </c>
       <c r="V276" t="n">
-        <v>0</v>
+        <v>3.091</v>
       </c>
       <c r="W276" t="n">
-        <v>19.62</v>
+        <v>15.919</v>
       </c>
     </row>
     <row r="277">
@@ -24082,10 +24082,10 @@
         <v>8.436</v>
       </c>
       <c r="V277" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="W277" t="n">
-        <v>18.848</v>
+        <v>15.244</v>
       </c>
     </row>
     <row r="278">
@@ -24159,10 +24159,10 @@
         <v>8.795</v>
       </c>
       <c r="V278" t="n">
-        <v>0</v>
+        <v>3.044</v>
       </c>
       <c r="W278" t="n">
-        <v>19.41</v>
+        <v>15.736</v>
       </c>
     </row>
     <row r="279">
@@ -24236,10 +24236,10 @@
         <v>8.807</v>
       </c>
       <c r="V279" t="n">
-        <v>0</v>
+        <v>3.048</v>
       </c>
       <c r="W279" t="n">
-        <v>19.427</v>
+        <v>15.751</v>
       </c>
     </row>
     <row r="280">
@@ -24313,10 +24313,10 @@
         <v>7.937</v>
       </c>
       <c r="V280" t="n">
-        <v>0</v>
+        <v>2.747</v>
       </c>
       <c r="W280" t="n">
-        <v>18.051</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="281">
@@ -24390,10 +24390,10 @@
         <v>8.311999999999999</v>
       </c>
       <c r="V281" t="n">
-        <v>0</v>
+        <v>2.877</v>
       </c>
       <c r="W281" t="n">
-        <v>18.65</v>
+        <v>15.072</v>
       </c>
     </row>
     <row r="282">
@@ -24467,10 +24467,10 @@
         <v>8.318</v>
       </c>
       <c r="V282" t="n">
-        <v>0</v>
+        <v>2.879</v>
       </c>
       <c r="W282" t="n">
-        <v>18.66</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="283">
@@ -24544,10 +24544,10 @@
         <v>8.853999999999999</v>
       </c>
       <c r="V283" t="n">
-        <v>0</v>
+        <v>3.065</v>
       </c>
       <c r="W283" t="n">
-        <v>19.5</v>
+        <v>15.815</v>
       </c>
     </row>
     <row r="284">
@@ -24621,10 +24621,10 @@
         <v>8.615</v>
       </c>
       <c r="V284" t="n">
-        <v>0</v>
+        <v>2.982</v>
       </c>
       <c r="W284" t="n">
-        <v>19.128</v>
+        <v>15.489</v>
       </c>
     </row>
     <row r="285">
@@ -24698,10 +24698,10 @@
         <v>8.531000000000001</v>
       </c>
       <c r="V285" t="n">
-        <v>0</v>
+        <v>2.953</v>
       </c>
       <c r="W285" t="n">
-        <v>18.992</v>
+        <v>15.371</v>
       </c>
     </row>
     <row r="286">
@@ -24775,10 +24775,10 @@
         <v>8.422000000000001</v>
       </c>
       <c r="V286" t="n">
-        <v>0</v>
+        <v>2.915</v>
       </c>
       <c r="W286" t="n">
-        <v>18.83</v>
+        <v>15.227</v>
       </c>
     </row>
     <row r="287">
@@ -24852,10 +24852,10 @@
         <v>7.548</v>
       </c>
       <c r="V287" t="n">
-        <v>0</v>
+        <v>2.613</v>
       </c>
       <c r="W287" t="n">
-        <v>17.408</v>
+        <v>13.995</v>
       </c>
     </row>
     <row r="288">
@@ -24929,10 +24929,10 @@
         <v>8.414</v>
       </c>
       <c r="V288" t="n">
-        <v>0</v>
+        <v>2.912</v>
       </c>
       <c r="W288" t="n">
-        <v>18.817</v>
+        <v>15.216</v>
       </c>
     </row>
     <row r="289">
@@ -25006,10 +25006,10 @@
         <v>8.507</v>
       </c>
       <c r="V289" t="n">
-        <v>0</v>
+        <v>2.945</v>
       </c>
       <c r="W289" t="n">
-        <v>18.956</v>
+        <v>15.339</v>
       </c>
     </row>
     <row r="290">
@@ -25083,10 +25083,10 @@
         <v>8.494</v>
       </c>
       <c r="V290" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="W290" t="n">
-        <v>18.936</v>
+        <v>15.322</v>
       </c>
     </row>
     <row r="291">
@@ -25160,10 +25160,10 @@
         <v>8.173</v>
       </c>
       <c r="V291" t="n">
-        <v>0</v>
+        <v>2.829</v>
       </c>
       <c r="W291" t="n">
-        <v>18.339</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="292">
@@ -25237,10 +25237,10 @@
         <v>8.228999999999999</v>
       </c>
       <c r="V292" t="n">
-        <v>0</v>
+        <v>2.848</v>
       </c>
       <c r="W292" t="n">
-        <v>18.428</v>
+        <v>14.898</v>
       </c>
     </row>
     <row r="293">
@@ -25314,10 +25314,10 @@
         <v>8.25</v>
       </c>
       <c r="V293" t="n">
-        <v>0</v>
+        <v>2.856</v>
       </c>
       <c r="W293" t="n">
-        <v>18.461</v>
+        <v>14.927</v>
       </c>
     </row>
     <row r="294">
@@ -25391,10 +25391,10 @@
         <v>8.284000000000001</v>
       </c>
       <c r="V294" t="n">
-        <v>0</v>
+        <v>2.867</v>
       </c>
       <c r="W294" t="n">
-        <v>18.513</v>
+        <v>14.972</v>
       </c>
     </row>
     <row r="295">
@@ -25468,10 +25468,10 @@
         <v>7.632</v>
       </c>
       <c r="V295" t="n">
-        <v>0</v>
+        <v>2.642</v>
       </c>
       <c r="W295" t="n">
-        <v>17.455</v>
+        <v>14.055</v>
       </c>
     </row>
     <row r="296">
@@ -25545,10 +25545,10 @@
         <v>8.577</v>
       </c>
       <c r="V296" t="n">
-        <v>0</v>
+        <v>2.969</v>
       </c>
       <c r="W296" t="n">
-        <v>18.976</v>
+        <v>15.377</v>
       </c>
     </row>
     <row r="297">
@@ -25622,10 +25622,10 @@
         <v>8.182</v>
       </c>
       <c r="V297" t="n">
-        <v>0</v>
+        <v>2.832</v>
       </c>
       <c r="W297" t="n">
-        <v>18.356</v>
+        <v>14.834</v>
       </c>
     </row>
     <row r="298">
@@ -25699,10 +25699,10 @@
         <v>7.962</v>
       </c>
       <c r="V298" t="n">
-        <v>0</v>
+        <v>2.756</v>
       </c>
       <c r="W298" t="n">
-        <v>18</v>
+        <v>14.525</v>
       </c>
     </row>
     <row r="299">
@@ -25776,10 +25776,10 @@
         <v>8.555</v>
       </c>
       <c r="V299" t="n">
-        <v>0</v>
+        <v>2.961</v>
       </c>
       <c r="W299" t="n">
-        <v>18.945</v>
+        <v>15.349</v>
       </c>
     </row>
     <row r="300">
@@ -25853,10 +25853,10 @@
         <v>8.625</v>
       </c>
       <c r="V300" t="n">
-        <v>0</v>
+        <v>2.985</v>
       </c>
       <c r="W300" t="n">
-        <v>19.045</v>
+        <v>15.438</v>
       </c>
     </row>
     <row r="301">
@@ -25930,10 +25930,10 @@
         <v>8.148</v>
       </c>
       <c r="V301" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="W301" t="n">
-        <v>18.3</v>
+        <v>14.786</v>
       </c>
     </row>
     <row r="302">
@@ -26007,10 +26007,10 @@
         <v>8.119</v>
       </c>
       <c r="V302" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="W302" t="n">
-        <v>18.253</v>
+        <v>14.745</v>
       </c>
     </row>
     <row r="303">
@@ -26084,10 +26084,10 @@
         <v>8.512</v>
       </c>
       <c r="V303" t="n">
-        <v>0</v>
+        <v>2.946</v>
       </c>
       <c r="W303" t="n">
-        <v>18.873</v>
+        <v>15.287</v>
       </c>
     </row>
     <row r="304">
@@ -26161,10 +26161,10 @@
         <v>8.173999999999999</v>
       </c>
       <c r="V304" t="n">
-        <v>0</v>
+        <v>2.829</v>
       </c>
       <c r="W304" t="n">
-        <v>18.331</v>
+        <v>14.815</v>
       </c>
     </row>
     <row r="305">
@@ -26238,10 +26238,10 @@
         <v>7.92</v>
       </c>
       <c r="V305" t="n">
-        <v>0</v>
+        <v>2.741</v>
       </c>
       <c r="W305" t="n">
-        <v>17.926</v>
+        <v>14.463</v>
       </c>
     </row>
     <row r="306">
@@ -26315,10 +26315,10 @@
         <v>8.371</v>
       </c>
       <c r="V306" t="n">
-        <v>0</v>
+        <v>2.897</v>
       </c>
       <c r="W306" t="n">
-        <v>18.657</v>
+        <v>15.097</v>
       </c>
     </row>
     <row r="307">
@@ -26392,10 +26392,10 @@
         <v>8.247999999999999</v>
       </c>
       <c r="V307" t="n">
-        <v>0</v>
+        <v>2.855</v>
       </c>
       <c r="W307" t="n">
-        <v>18.46</v>
+        <v>14.925</v>
       </c>
     </row>
     <row r="308">
@@ -26469,10 +26469,10 @@
         <v>7.194</v>
       </c>
       <c r="V308" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="W308" t="n">
-        <v>16.728</v>
+        <v>13.428</v>
       </c>
     </row>
     <row r="309">
@@ -26546,10 +26546,10 @@
         <v>7.885</v>
       </c>
       <c r="V309" t="n">
-        <v>0</v>
+        <v>2.729</v>
       </c>
       <c r="W309" t="n">
-        <v>17.863</v>
+        <v>14.409</v>
       </c>
     </row>
     <row r="310">
@@ -26623,10 +26623,10 @@
         <v>7.589</v>
       </c>
       <c r="V310" t="n">
-        <v>0</v>
+        <v>2.627</v>
       </c>
       <c r="W310" t="n">
-        <v>17.381</v>
+        <v>13.992</v>
       </c>
     </row>
     <row r="311">
@@ -26700,10 +26700,10 @@
         <v>7.702</v>
       </c>
       <c r="V311" t="n">
-        <v>0</v>
+        <v>2.666</v>
       </c>
       <c r="W311" t="n">
-        <v>17.556</v>
+        <v>14.145</v>
       </c>
     </row>
     <row r="312">
@@ -26777,10 +26777,10 @@
         <v>7.748</v>
       </c>
       <c r="V312" t="n">
-        <v>0</v>
+        <v>2.682</v>
       </c>
       <c r="W312" t="n">
-        <v>17.635</v>
+        <v>14.213</v>
       </c>
     </row>
     <row r="313">
@@ -26854,10 +26854,10 @@
         <v>7.841</v>
       </c>
       <c r="V313" t="n">
-        <v>0</v>
+        <v>2.714</v>
       </c>
       <c r="W313" t="n">
-        <v>17.788</v>
+        <v>14.345</v>
       </c>
     </row>
     <row r="314">
@@ -26931,10 +26931,10 @@
         <v>7.6</v>
       </c>
       <c r="V314" t="n">
-        <v>0</v>
+        <v>2.631</v>
       </c>
       <c r="W314" t="n">
-        <v>17.399</v>
+        <v>14.007</v>
       </c>
     </row>
     <row r="315">
@@ -27008,10 +27008,10 @@
         <v>7.739</v>
       </c>
       <c r="V315" t="n">
-        <v>0</v>
+        <v>2.679</v>
       </c>
       <c r="W315" t="n">
-        <v>17.624</v>
+        <v>14.202</v>
       </c>
     </row>
     <row r="316">
@@ -27085,10 +27085,10 @@
         <v>7.636</v>
       </c>
       <c r="V316" t="n">
-        <v>0</v>
+        <v>2.643</v>
       </c>
       <c r="W316" t="n">
-        <v>17.457</v>
+        <v>14.058</v>
       </c>
     </row>
     <row r="317">
@@ -27162,10 +27162,10 @@
         <v>7.854</v>
       </c>
       <c r="V317" t="n">
-        <v>0</v>
+        <v>2.719</v>
       </c>
       <c r="W317" t="n">
-        <v>17.809</v>
+        <v>14.363</v>
       </c>
     </row>
     <row r="318">
@@ -27239,10 +27239,10 @@
         <v>7.766</v>
       </c>
       <c r="V318" t="n">
-        <v>0</v>
+        <v>2.688</v>
       </c>
       <c r="W318" t="n">
-        <v>17.669</v>
+        <v>14.241</v>
       </c>
     </row>
     <row r="319">
@@ -27316,10 +27316,10 @@
         <v>7.765</v>
       </c>
       <c r="V319" t="n">
-        <v>0</v>
+        <v>2.688</v>
       </c>
       <c r="W319" t="n">
-        <v>17.667</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="320">
@@ -27393,10 +27393,10 @@
         <v>7.513</v>
       </c>
       <c r="V320" t="n">
-        <v>0</v>
+        <v>2.601</v>
       </c>
       <c r="W320" t="n">
-        <v>17.253</v>
+        <v>13.882</v>
       </c>
     </row>
     <row r="321">
@@ -27470,10 +27470,10 @@
         <v>7.736</v>
       </c>
       <c r="V321" t="n">
-        <v>0</v>
+        <v>2.678</v>
       </c>
       <c r="W321" t="n">
-        <v>17.617</v>
+        <v>14.197</v>
       </c>
     </row>
     <row r="322">
@@ -27547,10 +27547,10 @@
         <v>7.08</v>
       </c>
       <c r="V322" t="n">
-        <v>0</v>
+        <v>2.451</v>
       </c>
       <c r="W322" t="n">
-        <v>16.537</v>
+        <v>13.264</v>
       </c>
     </row>
     <row r="323">
@@ -27624,10 +27624,10 @@
         <v>7.12</v>
       </c>
       <c r="V323" t="n">
-        <v>0</v>
+        <v>2.464</v>
       </c>
       <c r="W323" t="n">
-        <v>16.607</v>
+        <v>13.323</v>
       </c>
     </row>
     <row r="324">
@@ -27701,10 +27701,10 @@
         <v>7.839</v>
       </c>
       <c r="V324" t="n">
-        <v>0</v>
+        <v>2.713</v>
       </c>
       <c r="W324" t="n">
-        <v>17.785</v>
+        <v>14.342</v>
       </c>
     </row>
     <row r="325">
@@ -27778,10 +27778,10 @@
         <v>8.364000000000001</v>
       </c>
       <c r="V325" t="n">
-        <v>0</v>
+        <v>2.895</v>
       </c>
       <c r="W325" t="n">
-        <v>18.742</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="326">
@@ -27855,10 +27855,10 @@
         <v>8.488</v>
       </c>
       <c r="V326" t="n">
-        <v>0</v>
+        <v>2.938</v>
       </c>
       <c r="W326" t="n">
-        <v>18.927</v>
+        <v>15.314</v>
       </c>
     </row>
     <row r="327">
@@ -27932,10 +27932,10 @@
         <v>8.500999999999999</v>
       </c>
       <c r="V327" t="n">
-        <v>0</v>
+        <v>2.942</v>
       </c>
       <c r="W327" t="n">
-        <v>18.955</v>
+        <v>15.337</v>
       </c>
     </row>
     <row r="328">
@@ -28009,10 +28009,10 @@
         <v>8.032</v>
       </c>
       <c r="V328" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="W328" t="n">
-        <v>18.2</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="329">
@@ -28086,10 +28086,10 @@
         <v>8.550000000000001</v>
       </c>
       <c r="V329" t="n">
-        <v>0</v>
+        <v>2.959</v>
       </c>
       <c r="W329" t="n">
-        <v>19.042</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="330">
@@ -28163,10 +28163,10 @@
         <v>7.63</v>
       </c>
       <c r="V330" t="n">
-        <v>0</v>
+        <v>2.641</v>
       </c>
       <c r="W330" t="n">
-        <v>17.549</v>
+        <v>14.116</v>
       </c>
     </row>
     <row r="331">
@@ -28240,10 +28240,10 @@
         <v>8.173</v>
       </c>
       <c r="V331" t="n">
-        <v>0</v>
+        <v>2.829</v>
       </c>
       <c r="W331" t="n">
-        <v>18.435</v>
+        <v>14.883</v>
       </c>
     </row>
     <row r="332">
@@ -28317,10 +28317,10 @@
         <v>8.602</v>
       </c>
       <c r="V332" t="n">
-        <v>0</v>
+        <v>2.977</v>
       </c>
       <c r="W332" t="n">
-        <v>19.126</v>
+        <v>15.483</v>
       </c>
     </row>
     <row r="333">
@@ -28394,10 +28394,10 @@
         <v>8.523</v>
       </c>
       <c r="V333" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="W333" t="n">
-        <v>18.983</v>
+        <v>15.362</v>
       </c>
     </row>
     <row r="334">
@@ -28471,10 +28471,10 @@
         <v>8.209</v>
       </c>
       <c r="V334" t="n">
-        <v>0</v>
+        <v>2.841</v>
       </c>
       <c r="W334" t="n">
-        <v>18.492</v>
+        <v>14.933</v>
       </c>
     </row>
     <row r="335">
@@ -28548,10 +28548,10 @@
         <v>8.27</v>
       </c>
       <c r="V335" t="n">
-        <v>0</v>
+        <v>2.863</v>
       </c>
       <c r="W335" t="n">
-        <v>18.594</v>
+        <v>15.021</v>
       </c>
     </row>
     <row r="336">
@@ -28625,10 +28625,10 @@
         <v>8.696999999999999</v>
       </c>
       <c r="V336" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="W336" t="n">
-        <v>19.265</v>
+        <v>15.607</v>
       </c>
     </row>
     <row r="337">
@@ -28702,10 +28702,10 @@
         <v>8.476000000000001</v>
       </c>
       <c r="V337" t="n">
-        <v>0</v>
+        <v>2.934</v>
       </c>
       <c r="W337" t="n">
-        <v>18.927</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="338">
@@ -28779,10 +28779,10 @@
         <v>7.631</v>
       </c>
       <c r="V338" t="n">
-        <v>0</v>
+        <v>2.641</v>
       </c>
       <c r="W338" t="n">
-        <v>17.551</v>
+        <v>14.117</v>
       </c>
     </row>
     <row r="339">
@@ -28856,10 +28856,10 @@
         <v>8.414999999999999</v>
       </c>
       <c r="V339" t="n">
-        <v>0</v>
+        <v>2.913</v>
       </c>
       <c r="W339" t="n">
-        <v>18.819</v>
+        <v>15.218</v>
       </c>
     </row>
     <row r="340">
@@ -28933,10 +28933,10 @@
         <v>8.225</v>
       </c>
       <c r="V340" t="n">
-        <v>0</v>
+        <v>2.847</v>
       </c>
       <c r="W340" t="n">
-        <v>18.523</v>
+        <v>14.959</v>
       </c>
     </row>
     <row r="341">
@@ -29010,10 +29010,10 @@
         <v>8.122999999999999</v>
       </c>
       <c r="V341" t="n">
-        <v>0</v>
+        <v>2.812</v>
       </c>
       <c r="W341" t="n">
-        <v>18.353</v>
+        <v>14.812</v>
       </c>
     </row>
     <row r="342">
@@ -29087,10 +29087,10 @@
         <v>7.323</v>
       </c>
       <c r="V342" t="n">
-        <v>0</v>
+        <v>2.535</v>
       </c>
       <c r="W342" t="n">
-        <v>16.968</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="343">
@@ -29164,10 +29164,10 @@
         <v>7.094</v>
       </c>
       <c r="V343" t="n">
-        <v>0</v>
+        <v>2.455</v>
       </c>
       <c r="W343" t="n">
-        <v>16.592</v>
+        <v>13.304</v>
       </c>
     </row>
     <row r="344">
@@ -29241,10 +29241,10 @@
         <v>7.202</v>
       </c>
       <c r="V344" t="n">
-        <v>0</v>
+        <v>2.493</v>
       </c>
       <c r="W344" t="n">
-        <v>16.769</v>
+        <v>13.458</v>
       </c>
     </row>
     <row r="345">
@@ -29318,10 +29318,10 @@
         <v>7.201</v>
       </c>
       <c r="V345" t="n">
-        <v>0</v>
+        <v>2.493</v>
       </c>
       <c r="W345" t="n">
-        <v>16.766</v>
+        <v>13.455</v>
       </c>
     </row>
     <row r="346">
@@ -29395,10 +29395,10 @@
         <v>7.193</v>
       </c>
       <c r="V346" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="W346" t="n">
-        <v>16.76</v>
+        <v>13.449</v>
       </c>
     </row>
     <row r="347">
@@ -29472,10 +29472,10 @@
         <v>6.948</v>
       </c>
       <c r="V347" t="n">
-        <v>0</v>
+        <v>2.405</v>
       </c>
       <c r="W347" t="n">
-        <v>16.343</v>
+        <v>13.091</v>
       </c>
     </row>
     <row r="348">
@@ -29549,10 +29549,10 @@
         <v>7.244</v>
       </c>
       <c r="V348" t="n">
-        <v>0</v>
+        <v>2.507</v>
       </c>
       <c r="W348" t="n">
-        <v>16.845</v>
+        <v>13.522</v>
       </c>
     </row>
     <row r="349">
@@ -29626,10 +29626,10 @@
         <v>7.246</v>
       </c>
       <c r="V349" t="n">
-        <v>0</v>
+        <v>2.508</v>
       </c>
       <c r="W349" t="n">
-        <v>16.848</v>
+        <v>13.524</v>
       </c>
     </row>
     <row r="350">
@@ -29703,10 +29703,10 @@
         <v>6.989</v>
       </c>
       <c r="V350" t="n">
-        <v>0</v>
+        <v>2.419</v>
       </c>
       <c r="W350" t="n">
-        <v>16.409</v>
+        <v>13.148</v>
       </c>
     </row>
     <row r="351">
@@ -29780,10 +29780,10 @@
         <v>7.295</v>
       </c>
       <c r="V351" t="n">
-        <v>0</v>
+        <v>2.525</v>
       </c>
       <c r="W351" t="n">
-        <v>16.931</v>
+        <v>13.596</v>
       </c>
     </row>
     <row r="352">
@@ -29857,10 +29857,10 @@
         <v>6.595</v>
       </c>
       <c r="V352" t="n">
-        <v>0</v>
+        <v>2.283</v>
       </c>
       <c r="W352" t="n">
-        <v>15.739</v>
+        <v>12.574</v>
       </c>
     </row>
     <row r="353">
@@ -29934,10 +29934,10 @@
         <v>7.088</v>
       </c>
       <c r="V353" t="n">
-        <v>0</v>
+        <v>2.453</v>
       </c>
       <c r="W353" t="n">
-        <v>16.579</v>
+        <v>13.294</v>
       </c>
     </row>
     <row r="354">
@@ -30011,10 +30011,10 @@
         <v>7.095</v>
       </c>
       <c r="V354" t="n">
-        <v>0</v>
+        <v>2.456</v>
       </c>
       <c r="W354" t="n">
-        <v>16.588</v>
+        <v>13.302</v>
       </c>
     </row>
     <row r="355">
@@ -30088,10 +30088,10 @@
         <v>7.374</v>
       </c>
       <c r="V355" t="n">
-        <v>0</v>
+        <v>2.552</v>
       </c>
       <c r="W355" t="n">
-        <v>17.052</v>
+        <v>13.702</v>
       </c>
     </row>
     <row r="356">
@@ -30165,10 +30165,10 @@
         <v>7.182</v>
       </c>
       <c r="V356" t="n">
-        <v>0</v>
+        <v>2.486</v>
       </c>
       <c r="W356" t="n">
-        <v>16.741</v>
+        <v>13.432</v>
       </c>
     </row>
     <row r="357">
@@ -30242,10 +30242,10 @@
         <v>7.07</v>
       </c>
       <c r="V357" t="n">
-        <v>0</v>
+        <v>2.447</v>
       </c>
       <c r="W357" t="n">
-        <v>16.547</v>
+        <v>13.267</v>
       </c>
     </row>
     <row r="358">
@@ -30319,10 +30319,10 @@
         <v>7.08</v>
       </c>
       <c r="V358" t="n">
-        <v>0</v>
+        <v>2.451</v>
       </c>
       <c r="W358" t="n">
-        <v>16.568</v>
+        <v>13.284</v>
       </c>
     </row>
     <row r="359">
@@ -30396,10 +30396,10 @@
         <v>7.427</v>
       </c>
       <c r="V359" t="n">
-        <v>0</v>
+        <v>2.571</v>
       </c>
       <c r="W359" t="n">
-        <v>16.985</v>
+        <v>13.677</v>
       </c>
     </row>
     <row r="360">
@@ -30473,10 +30473,10 @@
         <v>6.898</v>
       </c>
       <c r="V360" t="n">
-        <v>0</v>
+        <v>2.388</v>
       </c>
       <c r="W360" t="n">
-        <v>16.107</v>
+        <v>12.919</v>
       </c>
     </row>
     <row r="361">
@@ -30550,10 +30550,10 @@
         <v>7.059</v>
       </c>
       <c r="V361" t="n">
-        <v>0</v>
+        <v>2.443</v>
       </c>
       <c r="W361" t="n">
-        <v>16.378</v>
+        <v>13.152</v>
       </c>
     </row>
     <row r="362">
@@ -30627,10 +30627,10 @@
         <v>7.031</v>
       </c>
       <c r="V362" t="n">
-        <v>0</v>
+        <v>2.434</v>
       </c>
       <c r="W362" t="n">
-        <v>16.33</v>
+        <v>13.111</v>
       </c>
     </row>
     <row r="363">
@@ -30704,10 +30704,10 @@
         <v>7.016</v>
       </c>
       <c r="V363" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="W363" t="n">
-        <v>16.3</v>
+        <v>13.086</v>
       </c>
     </row>
     <row r="364">
@@ -30781,10 +30781,10 @@
         <v>7.038</v>
       </c>
       <c r="V364" t="n">
-        <v>0</v>
+        <v>2.436</v>
       </c>
       <c r="W364" t="n">
-        <v>16.343</v>
+        <v>13.122</v>
       </c>
     </row>
     <row r="365">
@@ -30858,10 +30858,10 @@
         <v>7.177</v>
       </c>
       <c r="V365" t="n">
-        <v>0</v>
+        <v>2.484</v>
       </c>
       <c r="W365" t="n">
-        <v>16.573</v>
+        <v>13.321</v>
       </c>
     </row>
     <row r="366">
@@ -30935,10 +30935,10 @@
         <v>7.338</v>
       </c>
       <c r="V366" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="W366" t="n">
-        <v>16.84</v>
+        <v>13.551</v>
       </c>
     </row>
     <row r="367">
@@ -31012,10 +31012,10 @@
         <v>6.914</v>
       </c>
       <c r="V367" t="n">
-        <v>0</v>
+        <v>2.393</v>
       </c>
       <c r="W367" t="n">
-        <v>16.136</v>
+        <v>12.944</v>
       </c>
     </row>
     <row r="368">
@@ -31089,10 +31089,10 @@
         <v>7.463</v>
       </c>
       <c r="V368" t="n">
-        <v>0</v>
+        <v>2.583</v>
       </c>
       <c r="W368" t="n">
-        <v>17.046</v>
+        <v>13.729</v>
       </c>
     </row>
     <row r="369">
@@ -31166,10 +31166,10 @@
         <v>6.657</v>
       </c>
       <c r="V369" t="n">
-        <v>0</v>
+        <v>2.304</v>
       </c>
       <c r="W369" t="n">
-        <v>15.703</v>
+        <v>12.572</v>
       </c>
     </row>
     <row r="370">
@@ -31243,10 +31243,10 @@
         <v>7.443</v>
       </c>
       <c r="V370" t="n">
-        <v>0</v>
+        <v>2.576</v>
       </c>
       <c r="W370" t="n">
-        <v>17.009</v>
+        <v>13.698</v>
       </c>
     </row>
     <row r="371">
@@ -31320,10 +31320,10 @@
         <v>7.126</v>
       </c>
       <c r="V371" t="n">
-        <v>0</v>
+        <v>2.467</v>
       </c>
       <c r="W371" t="n">
-        <v>16.489</v>
+        <v>13.248</v>
       </c>
     </row>
     <row r="372">
@@ -31397,10 +31397,10 @@
         <v>7.273</v>
       </c>
       <c r="V372" t="n">
-        <v>0</v>
+        <v>2.517</v>
       </c>
       <c r="W372" t="n">
-        <v>16.732</v>
+        <v>13.458</v>
       </c>
     </row>
     <row r="373">
@@ -31474,10 +31474,10 @@
         <v>7.196</v>
       </c>
       <c r="V373" t="n">
-        <v>0</v>
+        <v>2.491</v>
       </c>
       <c r="W373" t="n">
-        <v>16.606</v>
+        <v>13.349</v>
       </c>
     </row>
     <row r="374">
@@ -31551,10 +31551,10 @@
         <v>7.325</v>
       </c>
       <c r="V374" t="n">
-        <v>0</v>
+        <v>2.535</v>
       </c>
       <c r="W374" t="n">
-        <v>16.817</v>
+        <v>13.531</v>
       </c>
     </row>
     <row r="375">
@@ -31628,10 +31628,10 @@
         <v>6.628</v>
       </c>
       <c r="V375" t="n">
-        <v>0</v>
+        <v>2.294</v>
       </c>
       <c r="W375" t="n">
-        <v>15.647</v>
+        <v>12.525</v>
       </c>
     </row>
     <row r="376">
@@ -31705,10 +31705,10 @@
         <v>8.537000000000001</v>
       </c>
       <c r="V376" t="n">
-        <v>0</v>
+        <v>2.955</v>
       </c>
       <c r="W376" t="n">
-        <v>19.145</v>
+        <v>15.473</v>
       </c>
     </row>
     <row r="377">
@@ -31782,10 +31782,10 @@
         <v>8.420999999999999</v>
       </c>
       <c r="V377" t="n">
-        <v>0</v>
+        <v>2.915</v>
       </c>
       <c r="W377" t="n">
-        <v>18.956</v>
+        <v>15.309</v>
       </c>
     </row>
     <row r="378">
@@ -31859,10 +31859,10 @@
         <v>8.337999999999999</v>
       </c>
       <c r="V378" t="n">
-        <v>0</v>
+        <v>2.886</v>
       </c>
       <c r="W378" t="n">
-        <v>18.822</v>
+        <v>15.193</v>
       </c>
     </row>
     <row r="379">
@@ -31936,10 +31936,10 @@
         <v>8.398</v>
       </c>
       <c r="V379" t="n">
-        <v>0</v>
+        <v>2.907</v>
       </c>
       <c r="W379" t="n">
-        <v>18.911</v>
+        <v>15.272</v>
       </c>
     </row>
     <row r="380">
@@ -32013,10 +32013,10 @@
         <v>8.313000000000001</v>
       </c>
       <c r="V380" t="n">
-        <v>0</v>
+        <v>2.877</v>
       </c>
       <c r="W380" t="n">
-        <v>18.781</v>
+        <v>15.158</v>
       </c>
     </row>
     <row r="381">
@@ -32090,10 +32090,10 @@
         <v>7.841</v>
       </c>
       <c r="V381" t="n">
-        <v>0</v>
+        <v>2.714</v>
       </c>
       <c r="W381" t="n">
-        <v>18.006</v>
+        <v>14.488</v>
       </c>
     </row>
     <row r="382">
@@ -32167,10 +32167,10 @@
         <v>8.513999999999999</v>
       </c>
       <c r="V382" t="n">
-        <v>0</v>
+        <v>2.947</v>
       </c>
       <c r="W382" t="n">
-        <v>19.105</v>
+        <v>15.439</v>
       </c>
     </row>
     <row r="383">
@@ -32244,10 +32244,10 @@
         <v>7.654</v>
       </c>
       <c r="V383" t="n">
-        <v>0</v>
+        <v>2.649</v>
       </c>
       <c r="W383" t="n">
-        <v>17.7</v>
+        <v>14.223</v>
       </c>
     </row>
     <row r="384">
@@ -32321,10 +32321,10 @@
         <v>7.885</v>
       </c>
       <c r="V384" t="n">
-        <v>0</v>
+        <v>2.729</v>
       </c>
       <c r="W384" t="n">
-        <v>18.08</v>
+        <v>14.551</v>
       </c>
     </row>
     <row r="385">
@@ -32398,10 +32398,10 @@
         <v>8.567</v>
       </c>
       <c r="V385" t="n">
-        <v>0</v>
+        <v>2.965</v>
       </c>
       <c r="W385" t="n">
-        <v>19.19</v>
+        <v>15.513</v>
       </c>
     </row>
     <row r="386">
@@ -32475,10 +32475,10 @@
         <v>8.162000000000001</v>
       </c>
       <c r="V386" t="n">
-        <v>0</v>
+        <v>2.825</v>
       </c>
       <c r="W386" t="n">
-        <v>18.534</v>
+        <v>14.944</v>
       </c>
     </row>
     <row r="387">
@@ -32552,10 +32552,10 @@
         <v>8.257</v>
       </c>
       <c r="V387" t="n">
-        <v>0</v>
+        <v>2.858</v>
       </c>
       <c r="W387" t="n">
-        <v>18.69</v>
+        <v>15.079</v>
       </c>
     </row>
     <row r="388">
@@ -32629,10 +32629,10 @@
         <v>8.071</v>
       </c>
       <c r="V388" t="n">
-        <v>0</v>
+        <v>2.794</v>
       </c>
       <c r="W388" t="n">
-        <v>18.386</v>
+        <v>14.816</v>
       </c>
     </row>
     <row r="389">
@@ -32706,10 +32706,10 @@
         <v>8.132</v>
       </c>
       <c r="V389" t="n">
-        <v>0</v>
+        <v>2.815</v>
       </c>
       <c r="W389" t="n">
-        <v>18.482</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="390">
@@ -32783,10 +32783,10 @@
         <v>7.636</v>
       </c>
       <c r="V390" t="n">
-        <v>0</v>
+        <v>2.643</v>
       </c>
       <c r="W390" t="n">
-        <v>17.671</v>
+        <v>14.198</v>
       </c>
     </row>
     <row r="391">
@@ -32860,10 +32860,10 @@
         <v>8.269</v>
       </c>
       <c r="V391" t="n">
-        <v>0</v>
+        <v>2.862</v>
       </c>
       <c r="W391" t="n">
-        <v>18.71</v>
+        <v>15.096</v>
       </c>
     </row>
     <row r="392">
@@ -32937,10 +32937,10 @@
         <v>8.446</v>
       </c>
       <c r="V392" t="n">
-        <v>0</v>
+        <v>2.923</v>
       </c>
       <c r="W392" t="n">
-        <v>18.996</v>
+        <v>15.344</v>
       </c>
     </row>
     <row r="393">
@@ -33014,10 +33014,10 @@
         <v>7.309</v>
       </c>
       <c r="V393" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="W393" t="n">
-        <v>17.053</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="394">
@@ -33091,10 +33091,10 @@
         <v>6.706</v>
       </c>
       <c r="V394" t="n">
-        <v>0</v>
+        <v>2.321</v>
       </c>
       <c r="W394" t="n">
-        <v>16.022</v>
+        <v>12.797</v>
       </c>
     </row>
     <row r="395">
@@ -33168,10 +33168,10 @@
         <v>6.791</v>
       </c>
       <c r="V395" t="n">
-        <v>0</v>
+        <v>2.351</v>
       </c>
       <c r="W395" t="n">
-        <v>16.171</v>
+        <v>12.924</v>
       </c>
     </row>
     <row r="396">
@@ -33245,10 +33245,10 @@
         <v>7.12</v>
       </c>
       <c r="V396" t="n">
-        <v>0</v>
+        <v>2.464</v>
       </c>
       <c r="W396" t="n">
-        <v>16.729</v>
+        <v>13.403</v>
       </c>
     </row>
     <row r="397">
@@ -33322,10 +33322,10 @@
         <v>7.126</v>
       </c>
       <c r="V397" t="n">
-        <v>0</v>
+        <v>2.467</v>
       </c>
       <c r="W397" t="n">
-        <v>16.743</v>
+        <v>13.414</v>
       </c>
     </row>
     <row r="398">
@@ -33399,10 +33399,10 @@
         <v>7.269</v>
       </c>
       <c r="V398" t="n">
-        <v>0</v>
+        <v>2.516</v>
       </c>
       <c r="W398" t="n">
-        <v>16.988</v>
+        <v>13.624</v>
       </c>
     </row>
     <row r="399">
@@ -33476,10 +33476,10 @@
         <v>7.4</v>
       </c>
       <c r="V399" t="n">
-        <v>0</v>
+        <v>2.561</v>
       </c>
       <c r="W399" t="n">
-        <v>17.202</v>
+        <v>13.809</v>
       </c>
     </row>
     <row r="400">
@@ -33553,10 +33553,10 @@
         <v>7.859</v>
       </c>
       <c r="V400" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="W400" t="n">
-        <v>17.958</v>
+        <v>14.462</v>
       </c>
     </row>
     <row r="401">
@@ -33630,10 +33630,10 @@
         <v>7.615</v>
       </c>
       <c r="V401" t="n">
-        <v>0</v>
+        <v>2.636</v>
       </c>
       <c r="W401" t="n">
-        <v>17.561</v>
+        <v>14.118</v>
       </c>
     </row>
     <row r="402">
@@ -33707,10 +33707,10 @@
         <v>7.041</v>
       </c>
       <c r="V402" t="n">
-        <v>0</v>
+        <v>2.437</v>
       </c>
       <c r="W402" t="n">
-        <v>16.6</v>
+        <v>13.291</v>
       </c>
     </row>
     <row r="403">
@@ -33784,10 +33784,10 @@
         <v>6.759</v>
       </c>
       <c r="V403" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="W403" t="n">
-        <v>16.11</v>
+        <v>12.873</v>
       </c>
     </row>
     <row r="404">
@@ -33861,10 +33861,10 @@
         <v>6.949</v>
       </c>
       <c r="V404" t="n">
-        <v>0</v>
+        <v>2.405</v>
       </c>
       <c r="W404" t="n">
-        <v>16.452</v>
+        <v>13.163</v>
       </c>
     </row>
     <row r="405">
@@ -33938,10 +33938,10 @@
         <v>6.877</v>
       </c>
       <c r="V405" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="W405" t="n">
-        <v>16.307</v>
+        <v>13.043</v>
       </c>
     </row>
     <row r="406">
@@ -34015,10 +34015,10 @@
         <v>6.911</v>
       </c>
       <c r="V406" t="n">
-        <v>0</v>
+        <v>2.392</v>
       </c>
       <c r="W406" t="n">
-        <v>16.364</v>
+        <v>13.092</v>
       </c>
     </row>
     <row r="407">
@@ -34092,10 +34092,10 @@
         <v>7.537</v>
       </c>
       <c r="V407" t="n">
-        <v>0</v>
+        <v>2.609</v>
       </c>
       <c r="W407" t="n">
-        <v>17.433</v>
+        <v>14.008</v>
       </c>
     </row>
     <row r="408">
@@ -34169,10 +34169,10 @@
         <v>7.862</v>
       </c>
       <c r="V408" t="n">
-        <v>0</v>
+        <v>2.721</v>
       </c>
       <c r="W408" t="n">
-        <v>17.964</v>
+        <v>14.467</v>
       </c>
     </row>
     <row r="409">
@@ -34246,10 +34246,10 @@
         <v>6.988</v>
       </c>
       <c r="V409" t="n">
-        <v>0</v>
+        <v>2.419</v>
       </c>
       <c r="W409" t="n">
-        <v>16.503</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="410">
@@ -34323,10 +34323,10 @@
         <v>7.539</v>
       </c>
       <c r="V410" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="W410" t="n">
-        <v>17.259</v>
+        <v>13.895</v>
       </c>
     </row>
     <row r="411">
@@ -34400,10 +34400,10 @@
         <v>7.982</v>
       </c>
       <c r="V411" t="n">
-        <v>0</v>
+        <v>2.763</v>
       </c>
       <c r="W411" t="n">
-        <v>17.972</v>
+        <v>14.514</v>
       </c>
     </row>
     <row r="412">
@@ -34477,10 +34477,10 @@
         <v>7.644</v>
       </c>
       <c r="V412" t="n">
-        <v>0</v>
+        <v>2.646</v>
       </c>
       <c r="W412" t="n">
-        <v>17.423</v>
+        <v>14.038</v>
       </c>
     </row>
     <row r="413">
@@ -34554,10 +34554,10 @@
         <v>7.215</v>
       </c>
       <c r="V413" t="n">
-        <v>0</v>
+        <v>2.497</v>
       </c>
       <c r="W413" t="n">
-        <v>16.724</v>
+        <v>13.433</v>
       </c>
     </row>
     <row r="414">
@@ -34631,10 +34631,10 @@
         <v>7.484</v>
       </c>
       <c r="V414" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="W414" t="n">
-        <v>17.168</v>
+        <v>13.816</v>
       </c>
     </row>
     <row r="415">
@@ -34708,10 +34708,10 @@
         <v>7.792</v>
       </c>
       <c r="V415" t="n">
-        <v>0</v>
+        <v>2.697</v>
       </c>
       <c r="W415" t="n">
-        <v>17.657</v>
+        <v>14.242</v>
       </c>
     </row>
     <row r="416">
@@ -34785,10 +34785,10 @@
         <v>7.932</v>
       </c>
       <c r="V416" t="n">
-        <v>0</v>
+        <v>2.746</v>
       </c>
       <c r="W416" t="n">
-        <v>17.887</v>
+        <v>14.441</v>
       </c>
     </row>
     <row r="417">
@@ -34862,10 +34862,10 @@
         <v>7.787</v>
       </c>
       <c r="V417" t="n">
-        <v>0</v>
+        <v>2.695</v>
       </c>
       <c r="W417" t="n">
-        <v>17.658</v>
+        <v>14.241</v>
       </c>
     </row>
     <row r="418">
@@ -34939,10 +34939,10 @@
         <v>7.893</v>
       </c>
       <c r="V418" t="n">
-        <v>0</v>
+        <v>2.732</v>
       </c>
       <c r="W418" t="n">
-        <v>17.831</v>
+        <v>14.391</v>
       </c>
     </row>
     <row r="419">
@@ -35016,10 +35016,10 @@
         <v>7.594</v>
       </c>
       <c r="V419" t="n">
-        <v>0</v>
+        <v>2.629</v>
       </c>
       <c r="W419" t="n">
-        <v>17.345</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="420">
@@ -35093,10 +35093,10 @@
         <v>7.12</v>
       </c>
       <c r="V420" t="n">
-        <v>0</v>
+        <v>2.464</v>
       </c>
       <c r="W420" t="n">
-        <v>16.565</v>
+        <v>13.296</v>
       </c>
     </row>
     <row r="421">
@@ -35170,10 +35170,10 @@
         <v>7.822</v>
       </c>
       <c r="V421" t="n">
-        <v>0</v>
+        <v>2.707</v>
       </c>
       <c r="W421" t="n">
-        <v>17.711</v>
+        <v>14.288</v>
       </c>
     </row>
     <row r="422">
@@ -35247,10 +35247,10 @@
         <v>7.367</v>
       </c>
       <c r="V422" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="W422" t="n">
-        <v>16.971</v>
+        <v>13.647</v>
       </c>
     </row>
     <row r="423">
@@ -35324,10 +35324,10 @@
         <v>7.704</v>
       </c>
       <c r="V423" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="W423" t="n">
-        <v>17.526</v>
+        <v>14.126</v>
       </c>
     </row>
     <row r="424">
@@ -35401,10 +35401,10 @@
         <v>7.886</v>
       </c>
       <c r="V424" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="W424" t="n">
-        <v>17.813</v>
+        <v>14.377</v>
       </c>
     </row>
     <row r="425">
@@ -35478,10 +35478,10 @@
         <v>7.531</v>
       </c>
       <c r="V425" t="n">
-        <v>0</v>
+        <v>2.607</v>
       </c>
       <c r="W425" t="n">
-        <v>17.246</v>
+        <v>13.883</v>
       </c>
     </row>
     <row r="426">
@@ -35555,10 +35555,10 @@
         <v>7.88</v>
       </c>
       <c r="V426" t="n">
-        <v>0</v>
+        <v>2.728</v>
       </c>
       <c r="W426" t="n">
-        <v>17.812</v>
+        <v>14.374</v>
       </c>
     </row>
     <row r="427">
@@ -35632,10 +35632,10 @@
         <v>7.875</v>
       </c>
       <c r="V427" t="n">
-        <v>0</v>
+        <v>2.726</v>
       </c>
       <c r="W427" t="n">
-        <v>18.072</v>
+        <v>14.542</v>
       </c>
     </row>
     <row r="428">
@@ -35709,10 +35709,10 @@
         <v>7.915</v>
       </c>
       <c r="V428" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="W428" t="n">
-        <v>18.139</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="429">
@@ -35786,10 +35786,10 @@
         <v>7.777</v>
       </c>
       <c r="V429" t="n">
-        <v>0</v>
+        <v>2.692</v>
       </c>
       <c r="W429" t="n">
-        <v>17.914</v>
+        <v>14.405</v>
       </c>
     </row>
     <row r="430">
@@ -35863,10 +35863,10 @@
         <v>7.197</v>
       </c>
       <c r="V430" t="n">
-        <v>0</v>
+        <v>2.491</v>
       </c>
       <c r="W430" t="n">
-        <v>16.955</v>
+        <v>13.577</v>
       </c>
     </row>
     <row r="431">
@@ -35940,10 +35940,10 @@
         <v>8.103999999999999</v>
       </c>
       <c r="V431" t="n">
-        <v>0</v>
+        <v>2.805</v>
       </c>
       <c r="W431" t="n">
-        <v>18.447</v>
+        <v>14.867</v>
       </c>
     </row>
     <row r="432">
@@ -36017,10 +36017,10 @@
         <v>8.096</v>
       </c>
       <c r="V432" t="n">
-        <v>0</v>
+        <v>2.802</v>
       </c>
       <c r="W432" t="n">
-        <v>18.439</v>
+        <v>14.859</v>
       </c>
     </row>
     <row r="433">
@@ -36094,10 +36094,10 @@
         <v>7.676</v>
       </c>
       <c r="V433" t="n">
-        <v>0</v>
+        <v>2.657</v>
       </c>
       <c r="W433" t="n">
-        <v>17.746</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="434">
@@ -36171,10 +36171,10 @@
         <v>8.045</v>
       </c>
       <c r="V434" t="n">
-        <v>0</v>
+        <v>2.785</v>
       </c>
       <c r="W434" t="n">
-        <v>18.343</v>
+        <v>14.779</v>
       </c>
     </row>
     <row r="435">
@@ -36248,10 +36248,10 @@
         <v>7.746</v>
       </c>
       <c r="V435" t="n">
-        <v>0</v>
+        <v>2.681</v>
       </c>
       <c r="W435" t="n">
-        <v>17.865</v>
+        <v>14.362</v>
       </c>
     </row>
     <row r="436">
@@ -36325,10 +36325,10 @@
         <v>7.61</v>
       </c>
       <c r="V436" t="n">
-        <v>0</v>
+        <v>2.634</v>
       </c>
       <c r="W436" t="n">
-        <v>17.643</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="437">
@@ -36402,10 +36402,10 @@
         <v>8.009</v>
       </c>
       <c r="V437" t="n">
-        <v>0</v>
+        <v>2.772</v>
       </c>
       <c r="W437" t="n">
-        <v>18.298</v>
+        <v>14.737</v>
       </c>
     </row>
     <row r="438">
@@ -36479,10 +36479,10 @@
         <v>7.455</v>
       </c>
       <c r="V438" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="W438" t="n">
-        <v>17.387</v>
+        <v>13.949</v>
       </c>
     </row>
     <row r="439">
@@ -36556,10 +36556,10 @@
         <v>7.923</v>
       </c>
       <c r="V439" t="n">
-        <v>0</v>
+        <v>2.742</v>
       </c>
       <c r="W439" t="n">
-        <v>18.141</v>
+        <v>14.604</v>
       </c>
     </row>
     <row r="440">
@@ -36633,10 +36633,10 @@
         <v>7.779</v>
       </c>
       <c r="V440" t="n">
-        <v>0</v>
+        <v>2.693</v>
       </c>
       <c r="W440" t="n">
-        <v>17.917</v>
+        <v>14.408</v>
       </c>
     </row>
     <row r="441">
@@ -36710,10 +36710,10 @@
         <v>7.513</v>
       </c>
       <c r="V441" t="n">
-        <v>0</v>
+        <v>2.601</v>
       </c>
       <c r="W441" t="n">
-        <v>17.483</v>
+        <v>14.032</v>
       </c>
     </row>
     <row r="442">
@@ -36787,10 +36787,10 @@
         <v>7.761</v>
       </c>
       <c r="V442" t="n">
-        <v>0</v>
+        <v>2.686</v>
       </c>
       <c r="W442" t="n">
-        <v>17.883</v>
+        <v>14.379</v>
       </c>
     </row>
     <row r="443">
@@ -36864,10 +36864,10 @@
         <v>7.582</v>
       </c>
       <c r="V443" t="n">
-        <v>0</v>
+        <v>2.624</v>
       </c>
       <c r="W443" t="n">
-        <v>17.596</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="444">
@@ -36941,10 +36941,10 @@
         <v>7.109</v>
       </c>
       <c r="V444" t="n">
-        <v>0</v>
+        <v>2.461</v>
       </c>
       <c r="W444" t="n">
-        <v>16.602</v>
+        <v>13.316</v>
       </c>
     </row>
     <row r="445">
@@ -37018,10 +37018,10 @@
         <v>7.078</v>
       </c>
       <c r="V445" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="W445" t="n">
-        <v>16.549</v>
+        <v>13.271</v>
       </c>
     </row>
     <row r="446">
@@ -37095,10 +37095,10 @@
         <v>6.81</v>
       </c>
       <c r="V446" t="n">
-        <v>0</v>
+        <v>2.357</v>
       </c>
       <c r="W446" t="n">
-        <v>16.103</v>
+        <v>12.886</v>
       </c>
     </row>
     <row r="447">
@@ -37172,10 +37172,10 @@
         <v>7.234</v>
       </c>
       <c r="V447" t="n">
-        <v>0</v>
+        <v>2.504</v>
       </c>
       <c r="W447" t="n">
-        <v>16.812</v>
+        <v>13.497</v>
       </c>
     </row>
     <row r="448">
@@ -37249,10 +37249,10 @@
         <v>6.59</v>
       </c>
       <c r="V448" t="n">
-        <v>0</v>
+        <v>2.281</v>
       </c>
       <c r="W448" t="n">
-        <v>15.717</v>
+        <v>12.558</v>
       </c>
     </row>
     <row r="449">
@@ -37326,10 +37326,10 @@
         <v>7.303</v>
       </c>
       <c r="V449" t="n">
-        <v>0</v>
+        <v>2.528</v>
       </c>
       <c r="W449" t="n">
-        <v>16.925</v>
+        <v>13.594</v>
       </c>
     </row>
     <row r="450">
@@ -37403,10 +37403,10 @@
         <v>7.224</v>
       </c>
       <c r="V450" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="W450" t="n">
-        <v>16.793</v>
+        <v>13.481</v>
       </c>
     </row>
     <row r="451">
@@ -37480,10 +37480,10 @@
         <v>7.27</v>
       </c>
       <c r="V451" t="n">
-        <v>0</v>
+        <v>2.516</v>
       </c>
       <c r="W451" t="n">
-        <v>16.871</v>
+        <v>13.548</v>
       </c>
     </row>
     <row r="452">
@@ -37557,10 +37557,10 @@
         <v>6.83</v>
       </c>
       <c r="V452" t="n">
-        <v>0</v>
+        <v>2.364</v>
       </c>
       <c r="W452" t="n">
-        <v>16.136</v>
+        <v>12.915</v>
       </c>
     </row>
     <row r="453">
@@ -37634,10 +37634,10 @@
         <v>7.304</v>
       </c>
       <c r="V453" t="n">
-        <v>0</v>
+        <v>2.528</v>
       </c>
       <c r="W453" t="n">
-        <v>16.927</v>
+        <v>13.596</v>
       </c>
     </row>
     <row r="454">
@@ -37711,10 +37711,10 @@
         <v>7.317</v>
       </c>
       <c r="V454" t="n">
-        <v>0</v>
+        <v>2.533</v>
       </c>
       <c r="W454" t="n">
-        <v>16.947</v>
+        <v>13.614</v>
       </c>
     </row>
     <row r="455">
@@ -37788,10 +37788,10 @@
         <v>6.613</v>
       </c>
       <c r="V455" t="n">
-        <v>0</v>
+        <v>2.289</v>
       </c>
       <c r="W455" t="n">
-        <v>15.759</v>
+        <v>12.593</v>
       </c>
     </row>
     <row r="456">
@@ -37865,10 +37865,10 @@
         <v>7.145</v>
       </c>
       <c r="V456" t="n">
-        <v>0</v>
+        <v>2.473</v>
       </c>
       <c r="W456" t="n">
-        <v>16.662</v>
+        <v>13.368</v>
       </c>
     </row>
     <row r="457">
@@ -37942,10 +37942,10 @@
         <v>7.441</v>
       </c>
       <c r="V457" t="n">
-        <v>0</v>
+        <v>2.576</v>
       </c>
       <c r="W457" t="n">
-        <v>17.153</v>
+        <v>13.791</v>
       </c>
     </row>
     <row r="458">
@@ -38019,10 +38019,10 @@
         <v>7.039</v>
       </c>
       <c r="V458" t="n">
-        <v>0</v>
+        <v>2.436</v>
       </c>
       <c r="W458" t="n">
-        <v>16.487</v>
+        <v>13.217</v>
       </c>
     </row>
     <row r="459">
@@ -38096,10 +38096,10 @@
         <v>7.089</v>
       </c>
       <c r="V459" t="n">
-        <v>0</v>
+        <v>2.454</v>
       </c>
       <c r="W459" t="n">
-        <v>16.56</v>
+        <v>13.282</v>
       </c>
     </row>
     <row r="460">
@@ -38173,10 +38173,10 @@
         <v>7.086</v>
       </c>
       <c r="V460" t="n">
-        <v>0</v>
+        <v>2.453</v>
       </c>
       <c r="W460" t="n">
-        <v>16.562</v>
+        <v>13.282</v>
       </c>
     </row>
     <row r="461">
@@ -38250,10 +38250,10 @@
         <v>7.529</v>
       </c>
       <c r="V461" t="n">
-        <v>0</v>
+        <v>2.606</v>
       </c>
       <c r="W461" t="n">
-        <v>17.286</v>
+        <v>13.909</v>
       </c>
     </row>
     <row r="462">
@@ -38327,10 +38327,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="V462" t="n">
-        <v>0</v>
+        <v>2.838</v>
       </c>
       <c r="W462" t="n">
-        <v>18.37</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="463">
@@ -38404,10 +38404,10 @@
         <v>8.553000000000001</v>
       </c>
       <c r="V463" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="W463" t="n">
-        <v>18.927</v>
+        <v>15.336</v>
       </c>
     </row>
     <row r="464">
@@ -38481,10 +38481,10 @@
         <v>8.106</v>
       </c>
       <c r="V464" t="n">
-        <v>0</v>
+        <v>2.806</v>
       </c>
       <c r="W464" t="n">
-        <v>18.221</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="465">
@@ -38558,10 +38558,10 @@
         <v>8.234</v>
       </c>
       <c r="V465" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="W465" t="n">
-        <v>18.424</v>
+        <v>14.897</v>
       </c>
     </row>
     <row r="466">
@@ -38635,10 +38635,10 @@
         <v>8.311</v>
       </c>
       <c r="V466" t="n">
-        <v>0</v>
+        <v>2.877</v>
       </c>
       <c r="W466" t="n">
-        <v>18.542</v>
+        <v>15.001</v>
       </c>
     </row>
     <row r="467">
@@ -38712,10 +38712,10 @@
         <v>8.253</v>
       </c>
       <c r="V467" t="n">
-        <v>0</v>
+        <v>2.857</v>
       </c>
       <c r="W467" t="n">
-        <v>18.459</v>
+        <v>14.926</v>
       </c>
     </row>
     <row r="468">
@@ -38789,10 +38789,10 @@
         <v>8.16</v>
       </c>
       <c r="V468" t="n">
-        <v>0</v>
+        <v>2.824</v>
       </c>
       <c r="W468" t="n">
-        <v>18.303</v>
+        <v>14.792</v>
       </c>
     </row>
     <row r="469">
@@ -38866,10 +38866,10 @@
         <v>8.237</v>
       </c>
       <c r="V469" t="n">
-        <v>0</v>
+        <v>2.851</v>
       </c>
       <c r="W469" t="n">
-        <v>18.421</v>
+        <v>14.896</v>
       </c>
     </row>
     <row r="470">
@@ -38943,10 +38943,10 @@
         <v>7.851</v>
       </c>
       <c r="V470" t="n">
-        <v>0</v>
+        <v>2.718</v>
       </c>
       <c r="W470" t="n">
-        <v>17.808</v>
+        <v>14.362</v>
       </c>
     </row>
     <row r="471">
@@ -39020,10 +39020,10 @@
         <v>8.271000000000001</v>
       </c>
       <c r="V471" t="n">
-        <v>0</v>
+        <v>2.863</v>
       </c>
       <c r="W471" t="n">
-        <v>18.481</v>
+        <v>14.947</v>
       </c>
     </row>
     <row r="472">
@@ -39097,10 +39097,10 @@
         <v>7.764</v>
       </c>
       <c r="V472" t="n">
-        <v>0</v>
+        <v>2.687</v>
       </c>
       <c r="W472" t="n">
-        <v>17.668</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="473">
@@ -39174,10 +39174,10 @@
         <v>8.103</v>
       </c>
       <c r="V473" t="n">
-        <v>0</v>
+        <v>2.805</v>
       </c>
       <c r="W473" t="n">
-        <v>18.214</v>
+        <v>14.714</v>
       </c>
     </row>
     <row r="474">
@@ -39251,10 +39251,10 @@
         <v>8.292999999999999</v>
       </c>
       <c r="V474" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="W474" t="n">
-        <v>18.511</v>
+        <v>14.974</v>
       </c>
     </row>
     <row r="475">
@@ -39328,10 +39328,10 @@
         <v>8.199</v>
       </c>
       <c r="V475" t="n">
-        <v>0</v>
+        <v>2.838</v>
       </c>
       <c r="W475" t="n">
-        <v>18.371</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="476">
@@ -39405,10 +39405,10 @@
         <v>7.851</v>
       </c>
       <c r="V476" t="n">
-        <v>0</v>
+        <v>2.718</v>
       </c>
       <c r="W476" t="n">
-        <v>17.809</v>
+        <v>14.362</v>
       </c>
     </row>
     <row r="477">
@@ -39482,10 +39482,10 @@
         <v>8.426</v>
       </c>
       <c r="V477" t="n">
-        <v>0</v>
+        <v>2.917</v>
       </c>
       <c r="W477" t="n">
-        <v>18.726</v>
+        <v>15.161</v>
       </c>
     </row>
     <row r="478">
@@ -39559,10 +39559,10 @@
         <v>7.469</v>
       </c>
       <c r="V478" t="n">
-        <v>0</v>
+        <v>2.585</v>
       </c>
       <c r="W478" t="n">
-        <v>17.182</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="479">
@@ -39636,10 +39636,10 @@
         <v>8.602</v>
       </c>
       <c r="V479" t="n">
-        <v>0</v>
+        <v>2.977</v>
       </c>
       <c r="W479" t="n">
-        <v>18.997</v>
+        <v>15.399</v>
       </c>
     </row>
     <row r="480">
@@ -39713,10 +39713,10 @@
         <v>8.172000000000001</v>
       </c>
       <c r="V480" t="n">
-        <v>0</v>
+        <v>2.829</v>
       </c>
       <c r="W480" t="n">
-        <v>18.327</v>
+        <v>14.812</v>
       </c>
     </row>
     <row r="481">
@@ -39790,10 +39790,10 @@
         <v>8.358000000000001</v>
       </c>
       <c r="V481" t="n">
-        <v>0</v>
+        <v>2.893</v>
       </c>
       <c r="W481" t="n">
-        <v>18.61</v>
+        <v>15.061</v>
       </c>
     </row>
     <row r="482">
@@ -39867,10 +39867,10 @@
         <v>8.210000000000001</v>
       </c>
       <c r="V482" t="n">
-        <v>0</v>
+        <v>2.842</v>
       </c>
       <c r="W482" t="n">
-        <v>18.378</v>
+        <v>14.858</v>
       </c>
     </row>
     <row r="483">
@@ -39944,10 +39944,10 @@
         <v>8.055999999999999</v>
       </c>
       <c r="V483" t="n">
-        <v>0</v>
+        <v>2.788</v>
       </c>
       <c r="W483" t="n">
-        <v>18.145</v>
+        <v>14.653</v>
       </c>
     </row>
     <row r="484">
@@ -40021,10 +40021,10 @@
         <v>8.358000000000001</v>
       </c>
       <c r="V484" t="n">
-        <v>0</v>
+        <v>2.893</v>
       </c>
       <c r="W484" t="n">
-        <v>18.621</v>
+        <v>15.069</v>
       </c>
     </row>
     <row r="485">
@@ -40098,10 +40098,10 @@
         <v>7.468</v>
       </c>
       <c r="V485" t="n">
-        <v>0</v>
+        <v>2.585</v>
       </c>
       <c r="W485" t="n">
-        <v>17.188</v>
+        <v>13.824</v>
       </c>
     </row>
     <row r="486">
@@ -40175,10 +40175,10 @@
         <v>8.779</v>
       </c>
       <c r="V486" t="n">
-        <v>0</v>
+        <v>3.039</v>
       </c>
       <c r="W486" t="n">
-        <v>19.262</v>
+        <v>15.633</v>
       </c>
     </row>
     <row r="487">
@@ -40252,10 +40252,10 @@
         <v>8.276</v>
       </c>
       <c r="V487" t="n">
-        <v>0</v>
+        <v>2.865</v>
       </c>
       <c r="W487" t="n">
-        <v>18.489</v>
+        <v>14.954</v>
       </c>
     </row>
     <row r="488">
@@ -40329,10 +40329,10 @@
         <v>8.348000000000001</v>
       </c>
       <c r="V488" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="W488" t="n">
-        <v>18.593</v>
+        <v>15.047</v>
       </c>
     </row>
     <row r="489">
@@ -40406,10 +40406,10 @@
         <v>8.066000000000001</v>
       </c>
       <c r="V489" t="n">
-        <v>0</v>
+        <v>2.792</v>
       </c>
       <c r="W489" t="n">
-        <v>18.139</v>
+        <v>14.652</v>
       </c>
     </row>
     <row r="490">
@@ -40483,10 +40483,10 @@
         <v>8.316000000000001</v>
       </c>
       <c r="V490" t="n">
-        <v>0</v>
+        <v>2.878</v>
       </c>
       <c r="W490" t="n">
-        <v>18.547</v>
+        <v>15.006</v>
       </c>
     </row>
     <row r="491">
@@ -40560,10 +40560,10 @@
         <v>8.208</v>
       </c>
       <c r="V491" t="n">
-        <v>0</v>
+        <v>2.841</v>
       </c>
       <c r="W491" t="n">
-        <v>18.374</v>
+        <v>14.855</v>
       </c>
     </row>
     <row r="492">
@@ -40637,10 +40637,10 @@
         <v>7.615</v>
       </c>
       <c r="V492" t="n">
-        <v>0</v>
+        <v>2.636</v>
       </c>
       <c r="W492" t="n">
-        <v>17.422</v>
+        <v>14.027</v>
       </c>
     </row>
     <row r="493">
@@ -40714,10 +40714,10 @@
         <v>8.093</v>
       </c>
       <c r="V493" t="n">
-        <v>0</v>
+        <v>2.801</v>
       </c>
       <c r="W493" t="n">
-        <v>18.197</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="494">
@@ -40791,10 +40791,10 @@
         <v>8.673999999999999</v>
       </c>
       <c r="V494" t="n">
-        <v>0</v>
+        <v>3.002</v>
       </c>
       <c r="W494" t="n">
-        <v>19.102</v>
+        <v>15.493</v>
       </c>
     </row>
     <row r="495">
@@ -40868,10 +40868,10 @@
         <v>8.114000000000001</v>
       </c>
       <c r="V495" t="n">
-        <v>0</v>
+        <v>2.809</v>
       </c>
       <c r="W495" t="n">
-        <v>18.322</v>
+        <v>14.789</v>
       </c>
     </row>
     <row r="496">
@@ -40945,10 +40945,10 @@
         <v>8.151</v>
       </c>
       <c r="V496" t="n">
-        <v>0</v>
+        <v>2.821</v>
       </c>
       <c r="W496" t="n">
-        <v>18.377</v>
+        <v>14.837</v>
       </c>
     </row>
     <row r="497">
@@ -41022,10 +41022,10 @@
         <v>8.56</v>
       </c>
       <c r="V497" t="n">
-        <v>0</v>
+        <v>2.963</v>
       </c>
       <c r="W497" t="n">
-        <v>19.019</v>
+        <v>15.399</v>
       </c>
     </row>
     <row r="498">
@@ -41099,10 +41099,10 @@
         <v>8.358000000000001</v>
       </c>
       <c r="V498" t="n">
-        <v>0</v>
+        <v>2.893</v>
       </c>
       <c r="W498" t="n">
-        <v>18.711</v>
+        <v>15.127</v>
       </c>
     </row>
     <row r="499">
@@ -41176,10 +41176,10 @@
         <v>8.301</v>
       </c>
       <c r="V499" t="n">
-        <v>0</v>
+        <v>2.873</v>
       </c>
       <c r="W499" t="n">
-        <v>18.621</v>
+        <v>15.049</v>
       </c>
     </row>
     <row r="500">
@@ -41253,10 +41253,10 @@
         <v>7.822</v>
       </c>
       <c r="V500" t="n">
-        <v>0</v>
+        <v>2.707</v>
       </c>
       <c r="W500" t="n">
-        <v>17.837</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="501">
@@ -41330,10 +41330,10 @@
         <v>8.378</v>
       </c>
       <c r="V501" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="W501" t="n">
-        <v>18.739</v>
+        <v>15.153</v>
       </c>
     </row>
     <row r="502">
@@ -41407,10 +41407,10 @@
         <v>8.048</v>
       </c>
       <c r="V502" t="n">
-        <v>0</v>
+        <v>2.786</v>
       </c>
       <c r="W502" t="n">
-        <v>18.212</v>
+        <v>14.694</v>
       </c>
     </row>
     <row r="503">
@@ -41484,10 +41484,10 @@
         <v>8.141</v>
       </c>
       <c r="V503" t="n">
-        <v>0</v>
+        <v>2.818</v>
       </c>
       <c r="W503" t="n">
-        <v>18.362</v>
+        <v>14.824</v>
       </c>
     </row>
     <row r="504">
@@ -41561,10 +41561,10 @@
         <v>7.988</v>
       </c>
       <c r="V504" t="n">
-        <v>0</v>
+        <v>2.765</v>
       </c>
       <c r="W504" t="n">
-        <v>18.122</v>
+        <v>14.614</v>
       </c>
     </row>
     <row r="505">
@@ -41638,10 +41638,10 @@
         <v>8.164</v>
       </c>
       <c r="V505" t="n">
-        <v>0</v>
+        <v>2.826</v>
       </c>
       <c r="W505" t="n">
-        <v>18.404</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="506">
@@ -41715,10 +41715,10 @@
         <v>7.58</v>
       </c>
       <c r="V506" t="n">
-        <v>0</v>
+        <v>2.624</v>
       </c>
       <c r="W506" t="n">
-        <v>17.455</v>
+        <v>14.037</v>
       </c>
     </row>
     <row r="507">
@@ -41792,10 +41792,10 @@
         <v>8.619</v>
       </c>
       <c r="V507" t="n">
-        <v>0</v>
+        <v>2.983</v>
       </c>
       <c r="W507" t="n">
-        <v>19.114</v>
+        <v>15.481</v>
       </c>
     </row>
     <row r="508">
@@ -41869,10 +41869,10 @@
         <v>7.964</v>
       </c>
       <c r="V508" t="n">
-        <v>0</v>
+        <v>2.757</v>
       </c>
       <c r="W508" t="n">
-        <v>18.082</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="509">
@@ -41946,10 +41946,10 @@
         <v>8.345000000000001</v>
       </c>
       <c r="V509" t="n">
-        <v>0</v>
+        <v>2.888</v>
       </c>
       <c r="W509" t="n">
-        <v>18.668</v>
+        <v>15.095</v>
       </c>
     </row>
     <row r="510">
@@ -42023,10 +42023,10 @@
         <v>8.1</v>
       </c>
       <c r="V510" t="n">
-        <v>0</v>
+        <v>2.804</v>
       </c>
       <c r="W510" t="n">
-        <v>18.301</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="511">
@@ -42100,10 +42100,10 @@
         <v>8.504</v>
       </c>
       <c r="V511" t="n">
-        <v>0</v>
+        <v>2.944</v>
       </c>
       <c r="W511" t="n">
-        <v>18.937</v>
+        <v>15.326</v>
       </c>
     </row>
     <row r="512">
@@ -42177,10 +42177,10 @@
         <v>7.784</v>
       </c>
       <c r="V512" t="n">
-        <v>0</v>
+        <v>2.694</v>
       </c>
       <c r="W512" t="n">
-        <v>17.791</v>
+        <v>14.327</v>
       </c>
     </row>
     <row r="513">
@@ -42254,10 +42254,10 @@
         <v>8.170999999999999</v>
       </c>
       <c r="V513" t="n">
-        <v>0</v>
+        <v>2.828</v>
       </c>
       <c r="W513" t="n">
-        <v>18.415</v>
+        <v>14.869</v>
       </c>
     </row>
     <row r="514">
@@ -42331,10 +42331,10 @@
         <v>8.445</v>
       </c>
       <c r="V514" t="n">
-        <v>0</v>
+        <v>2.923</v>
       </c>
       <c r="W514" t="n">
-        <v>18.849</v>
+        <v>15.248</v>
       </c>
     </row>
     <row r="515">
@@ -42408,10 +42408,10 @@
         <v>8.195</v>
       </c>
       <c r="V515" t="n">
-        <v>0</v>
+        <v>2.837</v>
       </c>
       <c r="W515" t="n">
-        <v>18.459</v>
+        <v>14.906</v>
       </c>
     </row>
     <row r="516">
@@ -42485,10 +42485,10 @@
         <v>7.514</v>
       </c>
       <c r="V516" t="n">
-        <v>0</v>
+        <v>2.601</v>
       </c>
       <c r="W516" t="n">
-        <v>17.349</v>
+        <v>13.945</v>
       </c>
     </row>
     <row r="517">
@@ -42562,10 +42562,10 @@
         <v>7.979</v>
       </c>
       <c r="V517" t="n">
-        <v>0</v>
+        <v>2.762</v>
       </c>
       <c r="W517" t="n">
-        <v>18.107</v>
+        <v>14.601</v>
       </c>
     </row>
     <row r="518">
@@ -42639,10 +42639,10 @@
         <v>8.257</v>
       </c>
       <c r="V518" t="n">
-        <v>0</v>
+        <v>2.858</v>
       </c>
       <c r="W518" t="n">
-        <v>18.557</v>
+        <v>14.992</v>
       </c>
     </row>
     <row r="519">
@@ -42716,10 +42716,10 @@
         <v>8.237</v>
       </c>
       <c r="V519" t="n">
-        <v>0</v>
+        <v>2.851</v>
       </c>
       <c r="W519" t="n">
-        <v>18.519</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="520">
@@ -42793,10 +42793,10 @@
         <v>8.175000000000001</v>
       </c>
       <c r="V520" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="W520" t="n">
-        <v>18.426</v>
+        <v>14.878</v>
       </c>
     </row>
     <row r="521">
@@ -42870,10 +42870,10 @@
         <v>8.491</v>
       </c>
       <c r="V521" t="n">
-        <v>0</v>
+        <v>2.939</v>
       </c>
       <c r="W521" t="n">
-        <v>18.923</v>
+        <v>15.312</v>
       </c>
     </row>
     <row r="522">
@@ -42947,10 +42947,10 @@
         <v>8.009</v>
       </c>
       <c r="V522" t="n">
-        <v>0</v>
+        <v>2.772</v>
       </c>
       <c r="W522" t="n">
-        <v>18.155</v>
+        <v>14.643</v>
       </c>
     </row>
     <row r="523">
@@ -43024,10 +43024,10 @@
         <v>8.442</v>
       </c>
       <c r="V523" t="n">
-        <v>0</v>
+        <v>2.922</v>
       </c>
       <c r="W523" t="n">
-        <v>18.838</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="524">
@@ -43101,10 +43101,10 @@
         <v>8.395</v>
       </c>
       <c r="V524" t="n">
-        <v>0</v>
+        <v>2.906</v>
       </c>
       <c r="W524" t="n">
-        <v>18.774</v>
+        <v>15.181</v>
       </c>
     </row>
     <row r="525">
@@ -43178,10 +43178,10 @@
         <v>8.220000000000001</v>
       </c>
       <c r="V525" t="n">
-        <v>0</v>
+        <v>2.845</v>
       </c>
       <c r="W525" t="n">
-        <v>18.5</v>
+        <v>14.942</v>
       </c>
     </row>
     <row r="526">
@@ -43255,10 +43255,10 @@
         <v>8.460000000000001</v>
       </c>
       <c r="V526" t="n">
-        <v>0</v>
+        <v>2.928</v>
       </c>
       <c r="W526" t="n">
-        <v>18.867</v>
+        <v>15.265</v>
       </c>
     </row>
     <row r="527">
@@ -43332,10 +43332,10 @@
         <v>8.146000000000001</v>
       </c>
       <c r="V527" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="W527" t="n">
-        <v>18.371</v>
+        <v>14.832</v>
       </c>
     </row>
     <row r="528">
@@ -43409,10 +43409,10 @@
         <v>7.995</v>
       </c>
       <c r="V528" t="n">
-        <v>0</v>
+        <v>2.767</v>
       </c>
       <c r="W528" t="n">
-        <v>18.133</v>
+        <v>14.624</v>
       </c>
     </row>
     <row r="529">
@@ -43486,10 +43486,10 @@
         <v>8.003</v>
       </c>
       <c r="V529" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="W529" t="n">
-        <v>18.212</v>
+        <v>14.678</v>
       </c>
     </row>
     <row r="530">
@@ -43563,10 +43563,10 @@
         <v>7.727</v>
       </c>
       <c r="V530" t="n">
-        <v>0</v>
+        <v>2.675</v>
       </c>
       <c r="W530" t="n">
-        <v>17.765</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="531">
@@ -43640,10 +43640,10 @@
         <v>7.84</v>
       </c>
       <c r="V531" t="n">
-        <v>0</v>
+        <v>2.714</v>
       </c>
       <c r="W531" t="n">
-        <v>17.952</v>
+        <v>14.452</v>
       </c>
     </row>
     <row r="532">
@@ -43717,10 +43717,10 @@
         <v>7.965</v>
       </c>
       <c r="V532" t="n">
-        <v>0</v>
+        <v>2.757</v>
       </c>
       <c r="W532" t="n">
-        <v>18.152</v>
+        <v>14.626</v>
       </c>
     </row>
     <row r="533">
@@ -43794,10 +43794,10 @@
         <v>7.526</v>
       </c>
       <c r="V533" t="n">
-        <v>0</v>
+        <v>2.605</v>
       </c>
       <c r="W533" t="n">
-        <v>17.432</v>
+        <v>14.003</v>
       </c>
     </row>
     <row r="534">
@@ -43871,10 +43871,10 @@
         <v>8.026999999999999</v>
       </c>
       <c r="V534" t="n">
-        <v>0</v>
+        <v>2.778</v>
       </c>
       <c r="W534" t="n">
-        <v>18.251</v>
+        <v>14.712</v>
       </c>
     </row>
     <row r="535">
@@ -43948,10 +43948,10 @@
         <v>7.881</v>
       </c>
       <c r="V535" t="n">
-        <v>0</v>
+        <v>2.728</v>
       </c>
       <c r="W535" t="n">
-        <v>18.018</v>
+        <v>14.509</v>
       </c>
     </row>
     <row r="536">
@@ -44025,10 +44025,10 @@
         <v>7.884</v>
       </c>
       <c r="V536" t="n">
-        <v>0</v>
+        <v>2.729</v>
       </c>
       <c r="W536" t="n">
-        <v>18.021</v>
+        <v>14.512</v>
       </c>
     </row>
     <row r="537">
@@ -44102,10 +44102,10 @@
         <v>7.736</v>
       </c>
       <c r="V537" t="n">
-        <v>0</v>
+        <v>2.678</v>
       </c>
       <c r="W537" t="n">
-        <v>17.779</v>
+        <v>14.303</v>
       </c>
     </row>
     <row r="538">
@@ -44179,10 +44179,10 @@
         <v>7.966</v>
       </c>
       <c r="V538" t="n">
-        <v>0</v>
+        <v>2.757</v>
       </c>
       <c r="W538" t="n">
-        <v>18.157</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="539">
@@ -44256,10 +44256,10 @@
         <v>7.967</v>
       </c>
       <c r="V539" t="n">
-        <v>0</v>
+        <v>2.758</v>
       </c>
       <c r="W539" t="n">
-        <v>18.158</v>
+        <v>14.631</v>
       </c>
     </row>
     <row r="540">
@@ -44333,10 +44333,10 @@
         <v>8.236000000000001</v>
       </c>
       <c r="V540" t="n">
-        <v>0</v>
+        <v>2.851</v>
       </c>
       <c r="W540" t="n">
-        <v>18.59</v>
+        <v>15.006</v>
       </c>
     </row>
     <row r="541">
@@ -44410,10 +44410,10 @@
         <v>7.555</v>
       </c>
       <c r="V541" t="n">
-        <v>0</v>
+        <v>2.615</v>
       </c>
       <c r="W541" t="n">
-        <v>17.48</v>
+        <v>14.045</v>
       </c>
     </row>
     <row r="542">
@@ -44487,10 +44487,10 @@
         <v>8.09</v>
       </c>
       <c r="V542" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="W542" t="n">
-        <v>18.355</v>
+        <v>14.802</v>
       </c>
     </row>
     <row r="543">
@@ -44564,10 +44564,10 @@
         <v>8.007</v>
       </c>
       <c r="V543" t="n">
-        <v>0</v>
+        <v>2.772</v>
       </c>
       <c r="W543" t="n">
-        <v>18.221</v>
+        <v>14.686</v>
       </c>
     </row>
     <row r="544">
@@ -44641,10 +44641,10 @@
         <v>7.948</v>
       </c>
       <c r="V544" t="n">
-        <v>0</v>
+        <v>2.751</v>
       </c>
       <c r="W544" t="n">
-        <v>18.128</v>
+        <v>14.604</v>
       </c>
     </row>
     <row r="545">
@@ -44718,10 +44718,10 @@
         <v>7.878</v>
       </c>
       <c r="V545" t="n">
-        <v>0</v>
+        <v>2.727</v>
       </c>
       <c r="W545" t="n">
-        <v>18.011</v>
+        <v>14.504</v>
       </c>
     </row>
   </sheetData>

--- a/projections/kicker_2026_combined.xlsx
+++ b/projections/kicker_2026_combined.xlsx
@@ -583,10 +583,10 @@
         <v>0.7955</v>
       </c>
       <c r="Q2" t="n">
-        <v>121.42</v>
+        <v>105.7</v>
       </c>
       <c r="R2" t="n">
-        <v>180.83</v>
+        <v>196.56</v>
       </c>
       <c r="S2" t="n">
         <v>171.57</v>
@@ -651,10 +651,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q3" t="n">
-        <v>118.08</v>
+        <v>102.4</v>
       </c>
       <c r="R3" t="n">
-        <v>177.33</v>
+        <v>193.02</v>
       </c>
       <c r="S3" t="n">
         <v>161.71</v>
@@ -719,10 +719,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q4" t="n">
-        <v>116.12</v>
+        <v>101.25</v>
       </c>
       <c r="R4" t="n">
-        <v>172.34</v>
+        <v>187.23</v>
       </c>
       <c r="S4" t="n">
         <v>155.33</v>
@@ -787,10 +787,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q5" t="n">
-        <v>115.69</v>
+        <v>100.8</v>
       </c>
       <c r="R5" t="n">
-        <v>171.98</v>
+        <v>186.88</v>
       </c>
       <c r="S5" t="n">
         <v>159.53</v>
@@ -855,10 +855,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q6" t="n">
-        <v>115.18</v>
+        <v>100.33</v>
       </c>
       <c r="R6" t="n">
-        <v>171.29</v>
+        <v>186.15</v>
       </c>
       <c r="S6" t="n">
         <v>145.85</v>
@@ -923,10 +923,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q7" t="n">
-        <v>114.33</v>
+        <v>99.55</v>
       </c>
       <c r="R7" t="n">
-        <v>170.23</v>
+        <v>185.03</v>
       </c>
       <c r="S7" t="n">
         <v>129.02</v>
@@ -991,10 +991,10 @@
         <v>0.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.05</v>
+        <v>98.3</v>
       </c>
       <c r="R8" t="n">
-        <v>168.73</v>
+        <v>183.46</v>
       </c>
       <c r="S8" t="n">
         <v>158.4</v>
@@ -1059,10 +1059,10 @@
         <v>0.5962</v>
       </c>
       <c r="Q9" t="n">
-        <v>112.48</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>167.45</v>
+        <v>182</v>
       </c>
       <c r="S9" t="n">
         <v>135.76</v>
@@ -1127,10 +1127,10 @@
         <v>0.7391</v>
       </c>
       <c r="Q10" t="n">
-        <v>111.38</v>
+        <v>96.53</v>
       </c>
       <c r="R10" t="n">
-        <v>167.48</v>
+        <v>182.33</v>
       </c>
       <c r="S10" t="n">
         <v>157.69</v>
@@ -1195,10 +1195,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q11" t="n">
-        <v>111.53</v>
+        <v>96.92</v>
       </c>
       <c r="R11" t="n">
-        <v>166.75</v>
+        <v>181.36</v>
       </c>
       <c r="S11" t="n">
         <v>145.83</v>
@@ -1263,10 +1263,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q12" t="n">
-        <v>111.33</v>
+        <v>96.64</v>
       </c>
       <c r="R12" t="n">
-        <v>166.81</v>
+        <v>181.5</v>
       </c>
       <c r="S12" t="n">
         <v>146.71</v>
@@ -1331,10 +1331,10 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>111.72</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>166.43</v>
+        <v>180.92</v>
       </c>
       <c r="S13" t="n">
         <v>136.7</v>
@@ -1399,10 +1399,10 @@
         <v>0.617</v>
       </c>
       <c r="Q14" t="n">
-        <v>111.29</v>
+        <v>96.67</v>
       </c>
       <c r="R14" t="n">
-        <v>166.56</v>
+        <v>181.19</v>
       </c>
       <c r="S14" t="n">
         <v>135.59</v>
@@ -1467,10 +1467,10 @@
         <v>0.5667</v>
       </c>
       <c r="Q15" t="n">
-        <v>111.02</v>
+        <v>96.56</v>
       </c>
       <c r="R15" t="n">
-        <v>165.62</v>
+        <v>180.06</v>
       </c>
       <c r="S15" t="n">
         <v>144.1</v>
@@ -1535,10 +1535,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q16" t="n">
-        <v>110.73</v>
+        <v>96.13</v>
       </c>
       <c r="R16" t="n">
-        <v>165.85</v>
+        <v>180.43</v>
       </c>
       <c r="S16" t="n">
         <v>137.55</v>
@@ -1603,10 +1603,10 @@
         <v>0.8254</v>
       </c>
       <c r="Q17" t="n">
-        <v>109.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>165.62</v>
+        <v>180.42</v>
       </c>
       <c r="S17" t="n">
         <v>142.56</v>
@@ -1671,10 +1671,10 @@
         <v>0.6744</v>
       </c>
       <c r="Q18" t="n">
-        <v>109.78</v>
+        <v>95.16</v>
       </c>
       <c r="R18" t="n">
-        <v>165</v>
+        <v>179.6</v>
       </c>
       <c r="S18" t="n">
         <v>142.04</v>
@@ -1739,10 +1739,10 @@
         <v>0.6604</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.54</v>
+        <v>94.83</v>
       </c>
       <c r="R19" t="n">
-        <v>165.12</v>
+        <v>179.83</v>
       </c>
       <c r="S19" t="n">
         <v>148.39</v>
@@ -1807,10 +1807,10 @@
         <v>0.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>108.29</v>
+        <v>93.94</v>
       </c>
       <c r="R20" t="n">
-        <v>162.52</v>
+        <v>176.87</v>
       </c>
       <c r="S20" t="n">
         <v>144.41</v>
@@ -1875,10 +1875,10 @@
         <v>0.8431</v>
       </c>
       <c r="Q21" t="n">
-        <v>108.15</v>
+        <v>93.77</v>
       </c>
       <c r="R21" t="n">
-        <v>162.47</v>
+        <v>176.85</v>
       </c>
       <c r="S21" t="n">
         <v>142.2</v>
@@ -1943,10 +1943,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q22" t="n">
-        <v>107.52</v>
+        <v>93.25</v>
       </c>
       <c r="R22" t="n">
-        <v>161.45</v>
+        <v>175.73</v>
       </c>
       <c r="S22" t="n">
         <v>132.79</v>
@@ -2011,10 +2011,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q23" t="n">
-        <v>106.9</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>161.59</v>
+        <v>176.07</v>
       </c>
       <c r="S23" t="n">
         <v>142.14</v>
@@ -2079,10 +2079,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q24" t="n">
-        <v>104.75</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>159.36</v>
+        <v>173.81</v>
       </c>
       <c r="S24" t="n">
         <v>127.36</v>
@@ -2147,10 +2147,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q25" t="n">
-        <v>103.75</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>156.57</v>
+        <v>170.54</v>
       </c>
       <c r="S25" t="n">
         <v>141.17</v>
@@ -2215,10 +2215,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q26" t="n">
-        <v>103.17</v>
+        <v>89.17</v>
       </c>
       <c r="R26" t="n">
-        <v>156.07</v>
+        <v>170.07</v>
       </c>
       <c r="S26" t="n">
         <v>128.46</v>
@@ -2283,10 +2283,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q27" t="n">
-        <v>102.91</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="R27" t="n">
-        <v>156.26</v>
+        <v>170.39</v>
       </c>
       <c r="S27" t="n">
         <v>139.26</v>
@@ -2351,10 +2351,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q28" t="n">
-        <v>96.61</v>
+        <v>82.88</v>
       </c>
       <c r="R28" t="n">
-        <v>148.51</v>
+        <v>162.24</v>
       </c>
       <c r="S28" t="n">
         <v>121.38</v>
@@ -2419,10 +2419,10 @@
         <v>0.7255</v>
       </c>
       <c r="Q29" t="n">
-        <v>96.11</v>
+        <v>82.34</v>
       </c>
       <c r="R29" t="n">
-        <v>148.16</v>
+        <v>161.94</v>
       </c>
       <c r="S29" t="n">
         <v>125.18</v>
@@ -2487,10 +2487,10 @@
         <v>0.6923</v>
       </c>
       <c r="Q30" t="n">
-        <v>95.54000000000001</v>
+        <v>81.94</v>
       </c>
       <c r="R30" t="n">
-        <v>146.89</v>
+        <v>160.48</v>
       </c>
       <c r="S30" t="n">
         <v>122.33</v>
@@ -2555,10 +2555,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q31" t="n">
-        <v>96.25</v>
+        <v>83.13</v>
       </c>
       <c r="R31" t="n">
-        <v>145.84</v>
+        <v>158.97</v>
       </c>
       <c r="S31" t="n">
         <v>121.74</v>
@@ -2623,10 +2623,10 @@
         <v>0.6364</v>
       </c>
       <c r="Q32" t="n">
-        <v>95.8</v>
+        <v>82.45</v>
       </c>
       <c r="R32" t="n">
-        <v>146.24</v>
+        <v>159.59</v>
       </c>
       <c r="S32" t="n">
         <v>123.07</v>
@@ -2691,10 +2691,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q33" t="n">
-        <v>94.91</v>
+        <v>81.37</v>
       </c>
       <c r="R33" t="n">
-        <v>146.04</v>
+        <v>159.57</v>
       </c>
       <c r="S33" t="n">
         <v>124.16</v>

--- a/projections/kicker_2026_combined.xlsx
+++ b/projections/kicker_2026_combined.xlsx
@@ -510,12 +510,12 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>espn_fpts</t>
+          <t>draft_sharks_fpts</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>diff_vs_espn</t>
+          <t>fpts_gap</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
@@ -589,10 +589,10 @@
         <v>194.31</v>
       </c>
       <c r="S2" t="n">
-        <v>159.53</v>
+        <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>-9.23</v>
+        <v>-5.7</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -656,12 +656,8 @@
       <c r="R3" t="n">
         <v>189.83</v>
       </c>
-      <c r="S3" t="n">
-        <v>129.02</v>
-      </c>
-      <c r="T3" t="n">
-        <v>17.57</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
     </row>
@@ -725,10 +721,10 @@
         <v>189.53</v>
       </c>
       <c r="S4" t="n">
-        <v>171.57</v>
+        <v>177</v>
       </c>
       <c r="T4" t="n">
-        <v>-26.61</v>
+        <v>-32.04</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -793,10 +789,10 @@
         <v>185.69</v>
       </c>
       <c r="S5" t="n">
-        <v>145.85</v>
+        <v>156</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.99</v>
+        <v>-13.14</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
@@ -861,10 +857,10 @@
         <v>184.66</v>
       </c>
       <c r="S6" t="n">
-        <v>155.33</v>
+        <v>158</v>
       </c>
       <c r="T6" t="n">
-        <v>-13.39</v>
+        <v>-16.06</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -929,10 +925,10 @@
         <v>183.57</v>
       </c>
       <c r="S7" t="n">
-        <v>158.4</v>
+        <v>156</v>
       </c>
       <c r="T7" t="n">
-        <v>-17.46</v>
+        <v>-15.06</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -997,10 +993,10 @@
         <v>184.78</v>
       </c>
       <c r="S8" t="n">
-        <v>161.71</v>
+        <v>170</v>
       </c>
       <c r="T8" t="n">
-        <v>-21.13</v>
+        <v>-29.42</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -1065,10 +1061,10 @@
         <v>183.61</v>
       </c>
       <c r="S9" t="n">
-        <v>142.56</v>
+        <v>150</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.06</v>
+        <v>-9.5</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
@@ -1133,10 +1129,10 @@
         <v>182.43</v>
       </c>
       <c r="S10" t="n">
-        <v>146.71</v>
+        <v>158</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.88</v>
+        <v>-18.17</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1201,10 +1197,10 @@
         <v>181.29</v>
       </c>
       <c r="S11" t="n">
-        <v>136.7</v>
+        <v>148</v>
       </c>
       <c r="T11" t="n">
-        <v>2.68</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
@@ -1269,10 +1265,10 @@
         <v>181.37</v>
       </c>
       <c r="S12" t="n">
-        <v>145.83</v>
+        <v>153</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.71</v>
+        <v>-13.88</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1337,10 +1333,10 @@
         <v>180.49</v>
       </c>
       <c r="S13" t="n">
-        <v>148.39</v>
+        <v>154</v>
       </c>
       <c r="T13" t="n">
-        <v>-10.47</v>
+        <v>-16.08</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
@@ -1405,10 +1401,10 @@
         <v>179.57</v>
       </c>
       <c r="S14" t="n">
-        <v>135.76</v>
+        <v>148</v>
       </c>
       <c r="T14" t="n">
-        <v>2.09</v>
+        <v>-10.15</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -1473,10 +1469,10 @@
         <v>179.92</v>
       </c>
       <c r="S15" t="n">
-        <v>135.59</v>
+        <v>154</v>
       </c>
       <c r="T15" t="n">
-        <v>2.23</v>
+        <v>-16.18</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1541,10 +1537,10 @@
         <v>179.86</v>
       </c>
       <c r="S16" t="n">
-        <v>157.69</v>
+        <v>161</v>
       </c>
       <c r="T16" t="n">
-        <v>-20.34</v>
+        <v>-23.65</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1609,10 +1605,10 @@
         <v>179.01</v>
       </c>
       <c r="S17" t="n">
-        <v>139.26</v>
+        <v>147</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.24</v>
+        <v>-9.98</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1677,10 +1673,10 @@
         <v>177.55</v>
       </c>
       <c r="S18" t="n">
-        <v>132.79</v>
+        <v>144</v>
       </c>
       <c r="T18" t="n">
-        <v>3.29</v>
+        <v>-7.92</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -1745,10 +1741,10 @@
         <v>177.73</v>
       </c>
       <c r="S19" t="n">
-        <v>142.2</v>
+        <v>150</v>
       </c>
       <c r="T19" t="n">
-        <v>-6.15</v>
+        <v>-13.95</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -1813,10 +1809,10 @@
         <v>177.32</v>
       </c>
       <c r="S20" t="n">
-        <v>144.1</v>
+        <v>155</v>
       </c>
       <c r="T20" t="n">
-        <v>-8.19</v>
+        <v>-19.09</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -1881,10 +1877,10 @@
         <v>177.45</v>
       </c>
       <c r="S21" t="n">
-        <v>142.04</v>
+        <v>157</v>
       </c>
       <c r="T21" t="n">
-        <v>-6.6</v>
+        <v>-21.56</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -1949,10 +1945,10 @@
         <v>177.08</v>
       </c>
       <c r="S22" t="n">
-        <v>137.55</v>
+        <v>146</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.19</v>
+        <v>-10.64</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2017,10 +2013,10 @@
         <v>175.9</v>
       </c>
       <c r="S23" t="n">
-        <v>144.41</v>
+        <v>158</v>
       </c>
       <c r="T23" t="n">
-        <v>-9.82</v>
+        <v>-23.41</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
@@ -2085,10 +2081,10 @@
         <v>173.18</v>
       </c>
       <c r="S24" t="n">
-        <v>128.46</v>
+        <v>145</v>
       </c>
       <c r="T24" t="n">
-        <v>3.83</v>
+        <v>-12.71</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
@@ -2153,10 +2149,10 @@
         <v>173.4</v>
       </c>
       <c r="S25" t="n">
-        <v>142.14</v>
+        <v>155</v>
       </c>
       <c r="T25" t="n">
-        <v>-10.2</v>
+        <v>-23.06</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -2221,10 +2217,10 @@
         <v>170.7</v>
       </c>
       <c r="S26" t="n">
-        <v>127.36</v>
+        <v>131</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>-1.65</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
@@ -2289,10 +2285,10 @@
         <v>168.17</v>
       </c>
       <c r="S27" t="n">
-        <v>141.17</v>
+        <v>142</v>
       </c>
       <c r="T27" t="n">
-        <v>-13.12</v>
+        <v>-13.95</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
@@ -2357,10 +2353,10 @@
         <v>165.21</v>
       </c>
       <c r="S28" t="n">
-        <v>121.38</v>
+        <v>137</v>
       </c>
       <c r="T28" t="n">
-        <v>3.74</v>
+        <v>-11.88</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
@@ -2425,10 +2421,10 @@
         <v>161.8</v>
       </c>
       <c r="S29" t="n">
-        <v>121.74</v>
+        <v>141</v>
       </c>
       <c r="T29" t="n">
-        <v>1.78</v>
+        <v>-17.48</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2493,10 +2489,10 @@
         <v>162.71</v>
       </c>
       <c r="S30" t="n">
-        <v>125.18</v>
+        <v>140</v>
       </c>
       <c r="T30" t="n">
-        <v>-2.39</v>
+        <v>-17.21</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
@@ -2561,10 +2557,10 @@
         <v>161.46</v>
       </c>
       <c r="S31" t="n">
-        <v>124.16</v>
+        <v>146</v>
       </c>
       <c r="T31" t="n">
-        <v>-2.04</v>
+        <v>-23.88</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -2629,10 +2625,10 @@
         <v>160.42</v>
       </c>
       <c r="S32" t="n">
-        <v>122.33</v>
+        <v>137</v>
       </c>
       <c r="T32" t="n">
-        <v>-1.13</v>
+        <v>-15.8</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
@@ -2697,10 +2693,10 @@
         <v>158.02</v>
       </c>
       <c r="S33" t="n">
-        <v>123.07</v>
+        <v>140</v>
       </c>
       <c r="T33" t="n">
-        <v>-3.39</v>
+        <v>-20.32</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>

--- a/projections/kicker_2026_combined.xlsx
+++ b/projections/kicker_2026_combined.xlsx
@@ -656,8 +656,12 @@
       <c r="R3" t="n">
         <v>189.83</v>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>151</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-4.41</v>
+      </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
     </row>

--- a/projections/kicker_2026_combined.xlsx
+++ b/projections/kicker_2026_combined.xlsx
@@ -589,10 +589,10 @@
         <v>194.31</v>
       </c>
       <c r="S2" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.7</v>
+        <v>1.3</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -657,10 +657,10 @@
         <v>189.83</v>
       </c>
       <c r="S3" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="T3" t="n">
-        <v>-4.41</v>
+        <v>0.59</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -725,10 +725,10 @@
         <v>189.53</v>
       </c>
       <c r="S4" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="T4" t="n">
-        <v>-32.04</v>
+        <v>-37.04</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -793,10 +793,10 @@
         <v>185.69</v>
       </c>
       <c r="S5" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="T5" t="n">
-        <v>-13.14</v>
+        <v>-2.14</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
@@ -861,10 +861,10 @@
         <v>184.66</v>
       </c>
       <c r="S6" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="T6" t="n">
-        <v>-16.06</v>
+        <v>-8.06</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -929,10 +929,10 @@
         <v>183.57</v>
       </c>
       <c r="S7" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="T7" t="n">
-        <v>-15.06</v>
+        <v>-7.06</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         <v>183.61</v>
       </c>
       <c r="S9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="T9" t="n">
-        <v>-9.5</v>
+        <v>0.5</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         <v>182.43</v>
       </c>
       <c r="S10" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="T10" t="n">
-        <v>-18.17</v>
+        <v>-8.17</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         <v>181.29</v>
       </c>
       <c r="S11" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="T11" t="n">
-        <v>-8.619999999999999</v>
+        <v>-1.62</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         <v>181.37</v>
       </c>
       <c r="S12" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="T12" t="n">
-        <v>-13.88</v>
+        <v>-6.88</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         <v>180.49</v>
       </c>
       <c r="S13" t="n">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="T13" t="n">
-        <v>-16.08</v>
+        <v>-7.08</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         <v>179.57</v>
       </c>
       <c r="S14" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.15</v>
+        <v>-1.15</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         <v>179.92</v>
       </c>
       <c r="S15" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="T15" t="n">
-        <v>-16.18</v>
+        <v>-10.18</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         <v>179.86</v>
       </c>
       <c r="S16" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="T16" t="n">
-        <v>-23.65</v>
+        <v>-19.65</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         <v>179.01</v>
       </c>
       <c r="S17" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.98</v>
+        <v>1.02</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1677,10 +1677,10 @@
         <v>177.55</v>
       </c>
       <c r="S18" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="T18" t="n">
-        <v>-7.92</v>
+        <v>5.08</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         <v>177.73</v>
       </c>
       <c r="S19" t="n">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.95</v>
+        <v>-4.95</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         <v>177.32</v>
       </c>
       <c r="S20" t="n">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="T20" t="n">
-        <v>-19.09</v>
+        <v>-10.09</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         <v>177.45</v>
       </c>
       <c r="S21" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="T21" t="n">
-        <v>-21.56</v>
+        <v>-12.56</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         <v>177.08</v>
       </c>
       <c r="S22" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="T22" t="n">
-        <v>-10.64</v>
+        <v>-4.64</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         <v>175.9</v>
       </c>
       <c r="S23" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="T23" t="n">
-        <v>-23.41</v>
+        <v>-15.41</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         <v>173.18</v>
       </c>
       <c r="S24" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="T24" t="n">
-        <v>-12.71</v>
+        <v>-1.71</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         <v>173.4</v>
       </c>
       <c r="S25" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="T25" t="n">
-        <v>-23.06</v>
+        <v>-13.06</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         <v>170.7</v>
       </c>
       <c r="S26" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.65</v>
+        <v>12.35</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
@@ -2289,10 +2289,10 @@
         <v>168.17</v>
       </c>
       <c r="S27" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="T27" t="n">
-        <v>-13.95</v>
+        <v>-6.95</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         <v>165.21</v>
       </c>
       <c r="S28" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="T28" t="n">
-        <v>-11.88</v>
+        <v>-5.88</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         <v>161.8</v>
       </c>
       <c r="S29" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="T29" t="n">
-        <v>-17.48</v>
+        <v>-10.48</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2493,10 +2493,10 @@
         <v>162.71</v>
       </c>
       <c r="S30" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="T30" t="n">
-        <v>-17.21</v>
+        <v>-10.21</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         <v>161.46</v>
       </c>
       <c r="S31" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="T31" t="n">
-        <v>-23.88</v>
+        <v>-15.88</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         <v>160.42</v>
       </c>
       <c r="S32" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="T32" t="n">
-        <v>-15.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
@@ -2697,10 +2697,10 @@
         <v>158.02</v>
       </c>
       <c r="S33" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="T33" t="n">
-        <v>-20.32</v>
+        <v>-14.32</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
